--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,19 +413,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="49" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -436,20 +436,20 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="56" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="46" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +621,2836 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>raw_text_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260536964</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>273,450.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6852 W LINDA LANE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85226</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>308-14-039</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(200) 735-6403</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260536964.pdf</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260536964.pdf</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260536964.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260537007</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>165,000.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1001 E GRISWOLD RD UNIT 37</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85020</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>160-08-099</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(202) 400-0614</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260537007.pdf</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260537007.pdf</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260537007.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260537023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>456,000.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4732 W DAVIS RD</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85306</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>207-28-145</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>inaneiaNne. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(202) 205-6424</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260537023.pdf</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260537023.pdf</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260537023.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260538230</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Noe Moran Guerra, a married man</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>360,000.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>501-62</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(202) 605-3823</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Noe Moran Guerra, a married</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538230.pdf</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538230.pdf</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538230.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260538326</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(s): Fernando P. Jaramillo, a married man, as his sole and</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>169,493.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3115 W ALTA VISTA RD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>105-88-752</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(201) 604-5000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>(s): Fernando P. Jaramillo, a married man, as his sole</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538326.pdf</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538326.pdf</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538326.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260538386</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>John B. Hart, a married man as his sole and separate</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>99,000.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>328 E. Thunderbird Trail</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85042</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>122-42-077</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Statewide Foreclosure Services, Inc., a</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(920) 100-0300</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>John B. Hart, a married man as his</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>sole</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538386.pdf</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538386.pdf</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538386.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260538762</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Joseph E. Raimondi and Maureen Raimondi, husband and wife</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>145,000.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2941 E La Costa Dr</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85249</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>303-56-903</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(201) 806-1345</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Joseph E.</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Raimondi</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Maureen Raimondi, husband and</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538762.pdf</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538762.pdf</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538762.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260538831</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Britney Starr Margheim and Christopher Robert Link, wife and husband</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>429,385.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11012 W Harrison St</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>101-09-075</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(200) 743-1493</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Britney Starr</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Margheim</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Christopher Robert Link, wife and</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538831.pdf</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538831.pdf</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538831.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260538846</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rita Medina, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>224,000.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>135-37-207</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(202) 503-7855</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Rita Medina, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538846.pdf</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538846.pdf</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538846.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260538852</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>521,250.00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10728 North 154th Lane</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85379</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>501-96-482</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(672) 321-4239</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538852.pdf</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538852.pdf</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538852.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260538857</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Robert Edward Daniel Evans and Bernadette Joyce Evans, husband and wife</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>207,178.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11824 W Monte Lindo Ln</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Sun City</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85373</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>503-97-078</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>(201) 502-6689</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Robert Edward Daniel</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Bernadette Joyce Evans, husband and</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538857.pdf</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538857.pdf</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538857.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260538879</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Keith Don Blakslee and Tracy Jean Blakslee, husband and wife</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>244,800.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1923 West Ashland Avenue</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>110-45-072</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(202) 605-3887</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Keith Don</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Blakslee</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Tracy Jean Blakslee, husband and</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538879.pdf</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538879.pdf</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538879.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260538900</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tyree Thompson</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>361,000.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 2405 W DARREL RD</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>105-86-276</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Tyree</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538900.pdf</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538900.pdf</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538900.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260538915</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rafael Torres</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>303,825.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 12401 W VALENTINE AVE</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>El Mirage</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>509-07-485</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538915.pdf</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538915.pdf</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538915.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260538933</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>394,644.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>or identifiable location: 4730 W GARY WAY</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Laveen</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85339</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>300-84-140</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(202) 406-4285</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538933.pdf</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538933.pdf</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538933.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260538999</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>258,750.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2036 West Atlanta Avenue</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>105-65-199</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(672) 321-5680</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538999.pdf</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538999.pdf</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538999.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260539046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Arthur Mills, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>240,000.00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>12004 S Tonopah Dr</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85044</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>301-54-607</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(202) 009-8999</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Arthur Mills, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539046.pdf</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539046.pdf</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539046.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260539071</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Richard L Saunders Jr, a single person</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>188,000.00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18025 N 46th Dr</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>207-22-045</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(201) 500-9858</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Richard L Saunders Jr, a single</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539071.pdf</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539071.pdf</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539071.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260539101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Manuel Valdivia and Joyce Pike, husband and wife</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>88,000.00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>657 South Arrowwood Way</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>218-67-778</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(201) 300-0837</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Joyce Pike, husband and</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539101.pdf</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539101.pdf</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539101.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260539106</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Arnulfo Duran Jr. an unmarried man and Heidy Duran, a married woman as her sole and separate</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>52,400.00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>500-05-586</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(202) 403-4543</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Arnulfo Duran Jr. an unmarried</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Heidy Duran, a married woman as her sole and</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539106.pdf</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539106.pdf</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee, missing_address</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539106.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260539158</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Albert Abramov, an unmarried man as his sole and separate property and</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>399,000.00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>16515 N. 71 Drive</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85382</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>231-25-187</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(202) 605-3915</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Albert Abramov, an unmarried man as his</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>sole</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>separate property</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539158.pdf</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539158.pdf</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539158.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260539159</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Anthony J. Tricoci and Barbara J. Tricoci, husband and wife</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>150,000.00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>301-40-515</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>(202) 605-3915</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Anthony J.</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Tricoci</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Barbara J. Tricoci, husband and</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539159.pdf</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539159.pdf</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539159.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260539398</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>(s): Brieann Gaylord, A Single Woman</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>214,051.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2225 E SHERRI DR</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Gilbert</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85296</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>304-26-065</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(200) 747-8072</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>(s): Brieann Gaylord, A Single</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Woman</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539398.pdf</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539398.pdf</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539398.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -425,7 +425,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="56" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="46" customWidth="1" min="27" max="27"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="49" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260536964</t>
+          <t>20260539845</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,22 +650,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(s): Nikki Fernando, an unmarried woman, and Ryan</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>273,450.00</t>
+          <t>391,500.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6852 W LINDA LANE</t>
+          <t>2839 E MERCER LN</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,7 +679,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85226</t>
+          <t>85028</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -689,59 +693,71 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>308-14-039</t>
+          <t>166-47-010</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(200) 735-6403</t>
+          <t>(202) 001-2814</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>(s): Nikki Fernando, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>woman,</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260536964.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539845.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260536964.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539845.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260536964.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539845.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260537007</t>
+          <t>20260539851</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -751,7 +767,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -764,34 +780,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>165,000.00</t>
+          <t>378,000.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1001 E GRISWOLD RD UNIT 37</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>85020</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -801,61 +805,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>160-08-099</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 400-0614</t>
+          <t>(202) 205-6862</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260537007.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539851.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260537007.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539851.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address, missing_apn</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260537007.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539851.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260537023</t>
+          <t>20260539853</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -865,7 +869,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -878,22 +882,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(s): Abel G Lopez</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>456,000.00</t>
+          <t>280,000.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4732 W DAVIS RD</t>
+          <t>10913 W SELLS DR</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -903,7 +911,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>85037</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -917,59 +925,67 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>207-28-145</t>
+          <t>102-58-299</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>inaneiaNne. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 205-6424</t>
+          <t>(202) 110-7276</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>(s): Abel G</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Lopez</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260537023.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539853.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260537023.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539853.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260537023.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539853.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260538230</t>
+          <t>20260539882</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -992,22 +1008,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Noe Moran Guerra, a married man</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>360,000.00</t>
+          <t>142,276.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>735 E Gardenia Dr</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85020</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1019,67 +1047,51 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>501-62</t>
+          <t>160-19-093</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(202) 605-3823</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
+          <t>(201) 907-0648</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Noe Moran Guerra, a married</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538230.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539882.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538230.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539882.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_owner, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538230.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539882.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260538326</t>
+          <t>20260539887</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1089,7 +1101,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1104,24 +1116,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(s): Fernando P. Jaramillo, a married man, as his sole and</t>
+          <t>Margaret B. Zufelt, a single woman</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>169,493.00</t>
+          <t>156,170.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3115 W ALTA VISTA RD</t>
+          <t>10523 W Coggins Dr</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1131,7 +1143,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1145,34 +1157,30 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>105-88-752</t>
+          <t>200-83-484</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(201) 604-5000</t>
+          <t>(202) 106-4673</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>(s): Fernando P. Jaramillo, a married man, as his sole</t>
+          <t>Margaret B. Zufelt, a single</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
@@ -1180,32 +1188,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538326.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539887.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538326.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539887.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538326.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539887.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260538386</t>
+          <t>20260540090</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1215,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,26 +1236,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>John B. Hart, a married man as his sole and separate</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>99,000.00</t>
+          <t>33,577.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>328 E. Thunderbird Trail</t>
+          <t>3301 EAST UNIVERSITY DRIVE #206</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1257,7 +1261,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85042</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1271,71 +1275,59 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>122-42-077</t>
+          <t>140-24-284</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Statewide Foreclosure Services, Inc., a</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(920) 100-0300</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>John B. Hart, a married man as his</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>sole</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>separate</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538386.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540090.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538386.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540090.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538386.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540090.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260538762</t>
+          <t>20260540309</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1345,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1358,26 +1350,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Joseph E. Raimondi and Maureen Raimondi, husband and wife</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>145,000.00</t>
+          <t>257,718.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2941 E La Costa Dr</t>
+          <t>4231 E DECATUR ST</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1387,7 +1375,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>85205</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1401,71 +1389,59 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>303-56-903</t>
+          <t>140-14-0460</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(201) 806-1345</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Joseph E.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Raimondi</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Maureen Raimondi, husband and</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538762.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540309.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538762.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540309.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538762.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540309.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260538831</t>
+          <t>20260540480</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1475,7 +1451,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1488,26 +1464,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Britney Starr Margheim and Christopher Robert Link, wife and husband</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>429,385.00</t>
+          <t>363,171.06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11012 W Harrison St</t>
+          <t>23862 W LUMBEE ST</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1517,7 +1489,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1531,71 +1503,59 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>101-09-075</t>
+          <t>504-28-071</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(200) 743-1493</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Britney Starr</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Margheim</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Christopher Robert Link, wife and</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>husband</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538831.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540480.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538831.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540480.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538831.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540480.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260538846</t>
+          <t>20260540597</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1605,7 +1565,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1618,26 +1578,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rita Medina, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>224,000.00</t>
+          <t>345,950.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>or identifiable location: 11808 W MONTE LINDO LN</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1647,7 +1603,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1661,67 +1617,63 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>135-37-207</t>
+          <t>503-97-082</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(202) 503-7855</t>
+          <t>(866) 539-4173</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Rita Medina, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538846.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540597.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538846.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540597.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538846.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540597.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260538852</t>
+          <t>20260540865</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1731,7 +1683,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1746,24 +1698,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Daniel Alston, a single man, 10325 West Reade Avenue, Glendale, Az 85307</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>521,250.00</t>
+          <t>155,000.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10728 North 154th Lane</t>
+          <t>10325 West Reade Avenue</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1773,7 +1725,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>85307</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1787,63 +1739,63 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>501-96-482</t>
+          <t>102-89-245</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(672) 321-4239</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>and</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+          <t>Daniel Alston, a single man, 10325 West Reade Avenue, Glendale, Az</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>85307</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538852.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540865.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538852.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540865.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538852.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540865.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260538857</t>
+          <t>20260541208</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,7 +1805,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1866,26 +1818,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Robert Edward Daniel Evans and Bernadette Joyce Evans, husband and wife</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>207,178.00</t>
+          <t>61,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11824 W Monte Lindo Ln</t>
+          <t>15041 W RIVIERA DR</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1895,7 +1843,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85373</t>
+          <t>85379</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1909,71 +1857,63 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>503-97-078</t>
+          <t>509-14-194</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(201) 502-6689</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Robert Edward Daniel</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Evans</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Bernadette Joyce Evans, husband and</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2022-11-23</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538857.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541208.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538857.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541208.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538857.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541208.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260538879</t>
+          <t>20260541221</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1983,7 +1923,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1996,38 +1936,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Keith Don Blakslee and Tracy Jean Blakslee, husband and wife</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>244,800.00</t>
+          <t>60,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1923 West Ashland Avenue</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -2039,67 +1959,63 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>110-45-072</t>
+          <t>303-27-826</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(202) 605-3887</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Keith Don</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Blakslee</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Tracy Jean Blakslee, husband and</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538879.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541221.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538879.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541221.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538879.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541221.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260538900</t>
+          <t>20260541472</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2109,7 +2025,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2122,26 +2038,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tyree Thompson</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>361,000.00</t>
+          <t>348,750.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 2405 W DARREL RD</t>
+          <t>238 N CENTER ST</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2151,7 +2063,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>85201</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2165,67 +2077,59 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>105-86-276</t>
+          <t>138-59-048</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 200-9397</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Tyree</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Thompson</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538900.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541472.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538900.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541472.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538900.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541472.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260538915</t>
+          <t>20260541500</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2235,7 +2139,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2250,24 +2154,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rafael Torres</t>
+          <t>Kylie Gallegos, an unmarried woman, and Jacob Bowman, an unmarried man</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>303,825.00</t>
+          <t>208,550.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 12401 W VALENTINE AVE</t>
+          <t>3646 N 67th Avenue Unit 64</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>El Mirage</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2277,7 +2181,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2291,67 +2195,71 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>509-07-485</t>
+          <t>102-84-421</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(200) 738-6112</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Kylie Gallegos, an unmarried</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Torres</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+          <t>woman,</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Jacob Bowman, an unmarried</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538915.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541500.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538915.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541500.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538915.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541500.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260538933</t>
+          <t>20260541674</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2361,7 +2269,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2374,22 +2282,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(s): Christine Brockman, a single woman</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>394,644.00</t>
+          <t>116,961.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>or identifiable location: 4730 W GARY WAY</t>
+          <t>915 S 96TH PL</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Laveen</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2399,7 +2311,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2413,63 +2325,67 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>300-84-140</t>
+          <t>220-70-881</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(202) 406-4285</t>
+          <t>(201) 807-7528</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2024-12-02</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>2024-12-16</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>(s): Christine Brockman, a single</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538933.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541674.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538933.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541674.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538933.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541674.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260538999</t>
+          <t>20260541787</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2479,7 +2395,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2492,26 +2408,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>258,750.00</t>
+          <t>274,928.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2036 West Atlanta Avenue</t>
+          <t>or identifiable location: 12238 W LARKSPUR RD</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>El Mirage</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2521,7 +2433,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>85335</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2535,63 +2447,63 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>105-65-199</t>
+          <t>509-05-110</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(672) 321-5680</t>
+          <t>(202) 204-9594</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260538999.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541787.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260538999.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541787.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260538999.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541787.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260539046</t>
+          <t>20260542090</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2601,7 +2513,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2616,19 +2528,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arthur Mills, an unmarried man</t>
+          <t>Eric Swanson an unmarried man</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>240,000.00</t>
+          <t>456,000.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12004 S Tonopah Dr</t>
+          <t>6617 W Molly Ln</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2643,7 +2555,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85044</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2657,25 +2569,21 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>301-54-607</t>
+          <t>201-07-076</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 009-8999</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+          <t>(202) 112-5833</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Arthur Mills, an unmarried</t>
+          <t>Eric Swanson an unmarried</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2688,32 +2596,32 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539046.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542090.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539046.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542090.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539046.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542090.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260539071</t>
+          <t>20260542650</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2723,7 +2631,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2738,24 +2646,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Richard L Saunders Jr, a single person</t>
+          <t>(s): Terry Horning, a single person; as sole ownership</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>188,000.00</t>
+          <t>40,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18025 N 46th Dr</t>
+          <t>10652 W COGGINS DR</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2765,7 +2673,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85308</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2779,30 +2687,34 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>207-22-045</t>
+          <t>200-93-820</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(201) 500-9858</t>
+          <t>(202) 104-0794</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Richard L Saunders Jr, a single</t>
+          <t>(s): Terry Horning, a single person; as sole</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>ownership</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -2810,32 +2722,32 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539071.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542650.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539071.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542650.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539071.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542650.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260539101</t>
+          <t>20260542651</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2845,7 +2757,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2860,24 +2772,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manuel Valdivia and Joyce Pike, husband and wife</t>
+          <t>(s): Anniel Susanna Hidrogo, a married woman, and</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>88,000.00</t>
+          <t>301,600.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>657 South Arrowwood Way</t>
+          <t>4511 ESAINT CATHERINE AVE</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2887,7 +2799,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>85042</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2901,71 +2813,67 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>218-67-778</t>
+          <t>123-58-412</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(201) 300-0837</t>
+          <t>(202) 202-5012</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>(s): Anniel Susanna Hidrogo, a married woman,</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Joyce Pike, husband and</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539101.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542651.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539101.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542651.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539101.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542651.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260539106</t>
+          <t>20260542760</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2975,7 +2883,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2988,15 +2896,11 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Arnulfo Duran Jr. an unmarried man and Heidy Duran, a married woman as her sole and separate</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>52,400.00</t>
+          <t>5003,</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3013,73 +2917,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>500-05-586</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(202) 403-4543</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Arnulfo Duran Jr. an unmarried</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Heidy Duran, a married woman as her sole and</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>separate</t>
-        </is>
-      </c>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539106.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542760.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539106.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542760.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_address</t>
+          <t>ocr_used, missing_owner, missing_address, missing_apn</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539106.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542760.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260539158</t>
+          <t>20260542781</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3089,7 +2981,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3102,26 +2994,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Albert Abramov, an unmarried man as his sole and separate property and</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>399,000.00</t>
+          <t>356,125.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16515 N. 71 Drive</t>
+          <t>18166 WSUNNYSLOPE LANE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Waddell</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3131,7 +3019,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85382</t>
+          <t>85355</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3145,75 +3033,59 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>231-25-187</t>
+          <t>502-914-090</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(202) 605-3915</t>
+          <t>(202) 207-8384</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Albert Abramov, an unmarried man as his</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>sole</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>separate property</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539158.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542781.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539158.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542781.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539158.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542781.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260539159</t>
+          <t>20260542831</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3223,7 +3095,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3238,20 +3110,36 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anthony J. Tricoci and Barbara J. Tricoci, husband and wife</t>
+          <t>(s)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>150,000.00</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2332 West Citrus Way</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85015</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3261,77 +3149,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>301-40-515</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(202) 605-3915</t>
+          <t>(202) 303-5277</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Anthony J.</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Tricoci</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Barbara J. Tricoci, husband and</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539159.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542831.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539159.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542831.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539159.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542831.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260539398</t>
+          <t>20260542832</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3341,7 +3213,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3356,24 +3228,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(s): Brieann Gaylord, A Single Woman</t>
+          <t>(s)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>214,051.00</t>
+          <t>432,030.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2225 E SHERRI DR</t>
+          <t>17733 W CAROL AVE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Waddell</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3383,7 +3255,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>85296</t>
+          <t>85355</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3395,11 +3267,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>304-26-065</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
@@ -3408,49 +3276,45 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(200) 747-8072</t>
+          <t>(202) 404-9171</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>(s): Brieann Gaylord, A Single</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Woman</t>
-        </is>
-      </c>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539398.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542832.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539398.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542832.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539398.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542832.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH24"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -423,10 +423,10 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="47" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -442,7 +442,7 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="60" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
+    <col width="52" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260539845</t>
+          <t>20260543018</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -652,24 +652,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(s): Nikki Fernando, an unmarried woman, and Ryan</t>
+          <t>Jose L Chavez, Jr. a married man as his sole and separate property</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>391,500.00</t>
+          <t>395,934.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2839 E MERCER LN</t>
+          <t>15873 W Jenan Dr</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85028</t>
+          <t>85379</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,71 +693,71 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>166-47-010</t>
+          <t>501-46-790</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 001-2814</t>
+          <t>(202) 113-4495</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>(s): Nikki Fernando, an unmarried</t>
+          <t>Jose L Chavez, Jr. a married man as his</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>woman,</t>
+          <t>sole</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Ryan</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539845.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543018.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539845.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543018.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539845.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543018.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260539851</t>
+          <t>20260543114</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,22 +780,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(s)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>378,000.00</t>
+          <t>345,624.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>861 EOAKLAND ST</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85225</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -805,61 +817,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>302-69-046</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 205-6862</t>
+          <t>(202) 203-3923</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>(s)</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539851.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543114.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539851.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543114.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539851.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543114.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260539853</t>
+          <t>20260543151</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -869,7 +881,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -882,21 +894,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(s): Abel G Lopez</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>280,000.00</t>
+          <t>122,637.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10913 W SELLS DR</t>
+          <t>or identifiable location: 3161 W WALTANN LANE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -911,7 +919,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85037</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -925,67 +933,59 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>102-58-299</t>
+          <t>207-39-852</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>before a trustee’s deed will be issued for covered</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 110-7276</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>(s): Abel G</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Lopez</t>
-        </is>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539853.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543151.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539853.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543151.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539853.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543151.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260539882</t>
+          <t>20260543318</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1012,18 +1012,18 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>142,276.00</t>
+          <t>449,328.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>735 E Gardenia Dr</t>
+          <t>or identifiable location: 14853 S 178th Dr</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Goodyear</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85020</t>
+          <t>85338</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1047,17 +1047,25 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>160-19-093</t>
+          <t>400-56-807</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(201) 907-0648</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
@@ -1066,32 +1074,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539882.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543318.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539882.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543318.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539882.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543318.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260539887</t>
+          <t>20260543492</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1101,7 +1109,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1114,26 +1122,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Margaret B. Zufelt, a single woman</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>156,170.00</t>
+          <t>419,826.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10523 W Coggins Dr</t>
+          <t>or identifiable location: 24330 W JONES AVE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1143,7 +1147,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1157,63 +1161,59 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>200-83-484</t>
+          <t>504-24-800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(202) 106-4673</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Margaret B. Zufelt, a single</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260539887.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543492.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260539887.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543492.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260539887.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543492.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260540090</t>
+          <t>20260543510</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1240,18 +1240,18 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>33,577.00</t>
+          <t>337,565.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3301 EAST UNIVERSITY DRIVE #206</t>
+          <t>10233 N 46TH DR</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85213</t>
+          <t>85302</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1275,23 +1275,23 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>140-24-284</t>
+          <t>148-06-059</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(844) 693-4761</t>
+          <t>(202) 012-6144</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1302,12 +1302,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540090.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543510.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540090.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543510.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1320,14 +1320,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540090.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543510.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260540309</t>
+          <t>20260543748</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1354,18 +1354,18 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>257,718.00</t>
+          <t>408,500.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4231 E DECATUR ST</t>
+          <t>3608 WMARSHALLAVE</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>85019</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>140-14-0460</t>
+          <t>145-11-135</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(844) 693-4761</t>
+          <t>(202) 505-5409</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1416,12 +1416,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540309.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543748.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540309.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543748.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1434,14 +1434,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540309.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543748.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260540480</t>
+          <t>20260543923</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1468,18 +1468,18 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>363,171.06</t>
+          <t>445,480.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23862 W LUMBEE ST</t>
+          <t>5415 W POINSETTIA DR</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85304</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1503,23 +1503,23 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>504-28-071</t>
+          <t>148-27-321</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>inancial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(844) 693-4761</t>
+          <t>(202) 207-3928</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1530,12 +1530,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540480.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543923.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540480.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543923.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1548,14 +1548,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540480.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543923.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260540597</t>
+          <t>20260543955</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1582,18 +1582,18 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>345,950.00</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>or identifiable location: 11808 W MONTE LINDO LN</t>
+          <t>7304 S 48TH GLN</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Laveen</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85373</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1617,30 +1617,26 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>503-97-082</t>
+          <t>104-89-093</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(866) 539-4173</t>
+          <t>(202) 301-2724</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1648,12 +1644,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540597.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543955.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540597.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543955.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1666,14 +1662,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540597.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543955.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260540865</t>
+          <t>20260544162</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1698,36 +1694,20 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Daniel Alston, a single man, 10325 West Reade Avenue, Glendale, Az 85307</t>
+          <t>Alis Gerardo Ramirez (a single man)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>155,000.00</t>
+          <t>98,900.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10325 West Reade Avenue</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>85307</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1739,30 +1719,34 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>102-89-245</t>
+          <t>506-40</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
+          <t>(202) 605-4416</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Daniel Alston, a single man, 10325 West Reade Avenue, Glendale, Az</t>
+          <t>Alis Gerardo Ramirez (a single</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>85307</t>
+          <t>man)</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -1770,32 +1754,32 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260540865.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544162.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260540865.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544162.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260540865.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544162.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260541208</t>
+          <t>20260544166</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1805,7 +1789,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1818,34 +1802,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Daniel Uriarte Lozano and Ana Evelia Felix (a married couple)</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>61,000.00</t>
+          <t>25,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>15041 W RIVIERA DR</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>85379</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1857,63 +1829,75 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>509-14-194</t>
+          <t>504-33</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(202) 605-4416</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Daniel Uriarte</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Lozano</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Ana Evelia Felix (a married</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>couple)</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541208.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544166.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541208.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544166.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541208.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544166.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260541221</t>
+          <t>20260544171</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1923,7 +1907,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1936,11 +1920,15 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jose Adolfo Zazueta (a single man)</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60,000.00</t>
+          <t>30,900.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,63 +1947,67 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>303-27-826</t>
+          <t>504-32-311</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(202) 605-4417</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Jose Adolfo Zazueta (a single</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>man)</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541221.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544171.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541221.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544171.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541221.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544171.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260541472</t>
+          <t>20260544191</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2025,7 +2017,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2038,34 +2030,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ryan Edgin and Ashtyn Edgin, husband and wife</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>348,750.00</t>
+          <t>150,000.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>238 N CENTER ST</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>85201</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2077,59 +2057,75 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>138-59-048</t>
+          <t>506-05-075</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 200-9397</t>
+          <t>(202) 605-4419</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Edgin</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Ashtyn Edgin, husband and</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541472.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544191.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541472.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544191.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541472.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544191.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260541500</t>
+          <t>20260544217</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2139,7 +2135,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2154,36 +2150,20 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kylie Gallegos, an unmarried woman, and Jacob Bowman, an unmarried man</t>
+          <t>Esteban Jovanni Calvillo (a single man)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>208,550.00</t>
+          <t>58,000.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>3646 N 67th Avenue Unit 64</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>85033</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2195,71 +2175,67 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>102-84-421</t>
+          <t>506-41</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(200) 738-6112</t>
+          <t>(202) 605-4421</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Kylie Gallegos, an unmarried</t>
+          <t>Esteban Jovanni Calvillo (a single</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>woman,</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Jacob Bowman, an unmarried</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+          <t>man)</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541500.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544217.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541500.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544217.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541500.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544217.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260541674</t>
+          <t>20260544226</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2269,7 +2245,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2284,24 +2260,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(s): Christine Brockman, a single woman</t>
+          <t>Ricardo Hernandez Ramirez and Lina Laura Balmaceda Vazquez (a</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>116,961.00</t>
+          <t>42,400.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>915 S 96TH PL</t>
+          <t>3914 W Palm Ln</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2311,7 +2287,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2325,47 +2301,55 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>220-70-881</t>
+          <t>504-32</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(201) 807-7528</t>
+          <t>(202) 605-4422</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>(s): Christine Brockman, a single</t>
+          <t>Ricardo Hernandez</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Lina Laura Balmaceda Vazquez</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>(a</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541674.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544226.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541674.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544226.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2378,14 +2362,14 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541674.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544226.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260541787</t>
+          <t>20260544230</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2395,7 +2379,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2408,22 +2392,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Guadalupe Pina Padilla (a single man)</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>274,928.00</t>
+          <t>29,700.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>or identifiable location: 12238 W LARKSPUR RD</t>
+          <t>3633 W Grant St</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>El Mirage</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2433,7 +2421,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2447,63 +2435,67 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>509-05-110</t>
+          <t>506-43-145</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(202) 204-9594</t>
+          <t>(202) 605-4423</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Guadalupe Pina Padilla (a single</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>man)</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260541787.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544230.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260541787.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544230.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260541787.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544230.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260542090</t>
+          <t>20260544235</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2513,7 +2505,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2528,36 +2520,20 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eric Swanson an unmarried man</t>
+          <t>Veronica Almontes (a single woman) and Yasmin Guadalupe Angelino</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>456,000.00</t>
+          <t>93,500.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>6617 W Molly Ln</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>85083</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2569,44 +2545,60 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>201-07-076</t>
+          <t>506-43-147</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 112-5833</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
+          <t>(202) 605-4423</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Eric Swanson an unmarried</t>
+          <t>Veronica Almontes (a single</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+          <t>woman)</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yasmin Guadalupe</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Angelino</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542090.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544235.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542090.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544235.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2614,14 +2606,14 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542090.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544235.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260542650</t>
+          <t>20260544310</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2631,7 +2623,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2646,24 +2638,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(s): Terry Horning, a single person; as sole ownership</t>
+          <t>Stephen Stewart, Jr, a single man</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>40,000.00</t>
+          <t>338,751.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10652 W COGGINS DR</t>
+          <t>3727 W Gardenia Ave</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2673,7 +2665,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2687,34 +2679,30 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>200-93-820</t>
+          <t>151-25-116</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 104-0794</t>
+          <t>(202) 502-4929</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>(s): Terry Horning, a single person; as sole</t>
+          <t>Stephen Stewart, Jr, a single</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>ownership</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -2722,32 +2710,32 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542650.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544310.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542650.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544310.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542650.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544310.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260542651</t>
+          <t>20260544385</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2757,7 +2745,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2772,24 +2760,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(s): Anniel Susanna Hidrogo, a married woman, and</t>
+          <t>Marsha Bohn, a married woman as her sole and separate property</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>301,600.00</t>
+          <t>432,000.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4511 ESAINT CATHERINE AVE</t>
+          <t>4561 S Ranger Trail</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2799,7 +2787,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85042</t>
+          <t>85297</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2813,47 +2801,55 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>123-58-412</t>
+          <t>313-02-905</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>for Current Trustee</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(202) 202-5012</t>
+          <t>(202) 605-4438</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>(s): Anniel Susanna Hidrogo, a married woman,</t>
+          <t>Marsha Bohn, a married woman as her</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>and</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+          <t>sole</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542651.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544385.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542651.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544385.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2866,14 +2862,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542651.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544385.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260542760</t>
+          <t>20260544400</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2883,7 +2879,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2896,18 +2892,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Terresha Peten, an unmarried woman</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5003,</t>
+          <t>472,000.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>12205 West Harrison Street</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -2917,61 +2933,65 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>500-29-301</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Prestige Default Services, Llc</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(202) 202-9041</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2024-04-26</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Terresha Peten, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542760.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544400.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542760.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544400.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address, missing_apn</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542760.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544400.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260542781</t>
+          <t>20260544573</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2981,7 +3001,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2994,22 +3014,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Aaron Keith Morrison, an unmarried man, 4622 E. Red</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>356,125.00</t>
+          <t>150,000.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18166 WSUNNYSLOPE LANE</t>
+          <t>4622 E. Red Range Way</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Waddell</t>
+          <t>Cave Creek</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3019,7 +3043,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85355</t>
+          <t>85331</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3033,59 +3057,67 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>502-914-090</t>
+          <t>211-60-343</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Statewide Foreclosure Services, Inc., a</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(202) 207-8384</t>
+          <t>(632) 954-7523</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Aaron Keith Morrison, an unmarried man, 4622 E.</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542781.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544573.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542781.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544573.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542781.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544573.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260542831</t>
+          <t>20260544593</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3095,7 +3127,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3110,24 +3142,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(s)</t>
+          <t>Home Invest Hdr Llc, an Arizona limited liability</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>32,000.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2332 West Citrus Way</t>
+          <t>2150 E. Brown Road, Ste 2 60</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3137,7 +3169,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85015</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3149,61 +3181,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>137-05-010</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Statewide Foreclosure Services, Inc., a</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(202) 303-5277</t>
+          <t>(202) 109-3909</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>(s)</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr"/>
+          <t>Home Invest Hdr Llc, an Arizona limited</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>liability</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542831.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544593.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542831.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544593.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542831.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544593.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260542832</t>
+          <t>20260544788</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3213,7 +3253,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3228,24 +3268,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(s)</t>
+          <t>Jesus A Lopez Padilla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>432,030.00</t>
+          <t>286,900.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17733 W CAROL AVE</t>
+          <t>or IDENTIFIABLE LOCATION: 4449 N 48TH AVE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Waddell</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3255,7 +3295,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>85355</t>
+          <t>85031</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3267,54 +3307,1526 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>145-22-071</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(202) 404-9171</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>(s)</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr"/>
+          <t>Jesus A Lopez</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Padilla</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260542832.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544788.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260542832.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544788.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260542832.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544788.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260544831</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mountain Town Homes, Llc, an Arizona limited liability company</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>391,000.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>580 E Wilcox Drive</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Sierra Vista</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85635</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>219-60-462</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(520) 458-3500</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Mountain Town Homes, Llc, an Arizona limited liability</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544831.pdf</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544831.pdf</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544831.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260544849</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ike S Paik, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>199,500.00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4212 N 113th Dr</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85037</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>102-90-089</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(202) 107-2941</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Ike S Paik, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544849.pdf</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544849.pdf</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544849.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260544856</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jason Patterson, a single man</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>114,000.00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4226 North 22nd Street #13</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85016</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>163-32</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(201) 301-4480</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Jason Patterson, a single</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544856.pdf</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544856.pdf</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544856.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260544875</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ida M. Lee</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>487,500.00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 11921 W ASTER DR</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>El Mirage</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>509-06-030</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Ida M.</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544875.pdf</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544875.pdf</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544875.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260544882</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jason Bolen And Leslie Bolen</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>322,746.00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 2344 W MELODY DR</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>300-17-330</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Jason Bolen And Leslie</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Bolen</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544882.pdf</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544882.pdf</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544882.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260545004</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jesse Dee Irvine, an unmarried man, 11462 W Roanoke Dr, Avondale, Az 85392</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>306,776.00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>11462 W Roanoke Drive</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85392</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>102-30-889</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Jesse Dee Irvine, an unmarried man, 11462 W Roanoke Dr, Avondale, Az</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>85392</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545004.pdf</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545004.pdf</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545004.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260545056</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ramses A. Romo Mendez</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>230,000.00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 20334 W HUBBARD RD</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>400-82-100</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Ramses A. Romo</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Mendez</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545056.pdf</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545056.pdf</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545056.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260545237</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>332,000.00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>42909 N 46TH AVE</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>New River</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85087</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>202-30-051</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(201) 609-4476</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545237.pdf</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545237.pdf</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545237.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260545354</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>J&amp;M Brothers Llc, an Arizona limited liability company</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>260,000.00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>11515 N 91st St Unit 209</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>85260</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>217-48-511</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>(202) 505-9680</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>J&amp;M Brothers Llc, an Arizona limited liability</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545354.pdf</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545354.pdf</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545354.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260545356</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>J&amp;M Brothers Llc, an Arizona limited liability company</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>408,000.00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2702 N 2ist St</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85006</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>117-02-033</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(202) 505-5859</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>J&amp;M Brothers Llc, an Arizona limited liability</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545356.pdf</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545356.pdf</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545356.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260545359</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/TR SALE+</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>’s Stated Name and Address: Rpc Phx N 4th, Llc, 1705 South Capital of Texas</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1,185,000.00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>(202) 207-3248</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>’s Stated</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Address: Rpc Phx N 4th, Llc, 1705 South Capital of</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545359.pdf</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545359.pdf</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545359.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260545373</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jameson Campbell, an unmarried man, and Clifford Campbell, an unmarried man, as joint tenants</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>353,479.00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1818 S 78th St</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>85209</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>218-57-863</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(202) 304-5932</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Jameson Campbell, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>man,</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Clifford Campbell, an unmarried man, as joint</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>tenants</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545373.pdf</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545373.pdf</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545373.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH36"/>
+  <dimension ref="A1:AH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="47" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="52" customWidth="1" min="27" max="27"/>
+    <col width="58" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="36" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260543018</t>
+          <t>20260545704</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,26 +650,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Jose L Chavez, Jr. a married man as his sole and separate property</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>395,934.00</t>
+          <t>04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15873 W Jenan Dr</t>
+          <t>30959 W. FAIRMOUNT AVE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -679,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -691,73 +687,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>501-46-790</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 113-4495</t>
+          <t>(202) 204-4471</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Jose L Chavez, Jr. a married man as his</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>sole</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>separate</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>property</t>
-        </is>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543018.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545704.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543018.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545704.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543018.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545704.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260543114</t>
+          <t>20260545869</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -767,7 +747,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,22 +760,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>or</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>345,624.00</t>
+          <t>259,000.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>861 EOAKLAND ST</t>
+          <t>4608 W KRALL ST.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -805,7 +789,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -819,59 +803,59 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>302-69-046</t>
+          <t>156-45-184</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Unofficial Document</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 203-3923</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
+          <t>(202) 000-3240</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>or</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543114.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545869.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543114.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545869.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543114.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545869.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260543151</t>
+          <t>20260545931</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -881,7 +865,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -898,18 +882,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>122,637.00</t>
+          <t>325,000.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>or identifiable location: 3161 W WALTANN LANE</t>
+          <t>2045 S LAROSA DR</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -919,7 +903,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85023</t>
+          <t>85282</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -933,23 +917,23 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>207-39-852</t>
+          <t>133-25-064</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>before a trustee’s deed will be issued for covered</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 103-0870</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -960,12 +944,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543151.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545931.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543151.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545931.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -978,14 +962,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543151.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545931.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260543318</t>
+          <t>20260546069</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1012,30 +996,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>449,328.00</t>
+          <t>125,000.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>or identifiable location: 14853 S 178th Dr</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Goodyear</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>85338</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1047,26 +1015,30 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>400-56-807</t>
+          <t>103-12-549</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>may require entity or trust bidders at this trustee's sale to provide</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(226) 080-6114</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1074,32 +1046,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543318.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546069.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543318.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546069.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543318.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546069.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260543492</t>
+          <t>20260546721</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1109,7 +1081,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1122,22 +1094,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Michael Paul Kaufman And Meryl Lisa Kaufman</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>419,826.00</t>
+          <t>75,800.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>or identifiable location: 24330 W JONES AVE</t>
+          <t>or IDENTIFIABLE LOCATION: 8830 W CORRINE DR</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1147,7 +1123,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85381</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,59 +1137,67 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>504-24-800</t>
+          <t>200-79-930</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Michael Paul Kaufman And Meryl Lisa</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Kaufman</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543492.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546721.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543492.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546721.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543492.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546721.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260543510</t>
+          <t>20260546723</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1207,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1236,22 +1220,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Unofficial Document</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>337,565.00</t>
+          <t>137,144.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10233 N 46TH DR</t>
+          <t>901 W LIBRA DR</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1261,7 +1249,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85302</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1275,7 +1263,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>148-06-059</t>
+          <t>301-05-229</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1286,7 +1274,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(202) 012-6144</t>
+          <t>(201) 507-1356</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1295,39 +1283,47 @@
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Unofficial</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543510.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546723.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543510.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546723.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543510.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546723.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260543748</t>
+          <t>20260546765</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1337,7 +1333,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1350,22 +1346,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>an unmarried woman</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>408,500.00</t>
+          <t>238,500.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3608 WMARSHALLAVE</t>
+          <t>25396 W Ellis Dr</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85019</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1387,61 +1387,65 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>145-11-135</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>4915 E. Baseline Rd., Suite #105</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(202) 505-5409</t>
+          <t>(480) 305-7007</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-08-21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>an unmarried</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543748.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546765.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543748.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546765.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543748.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546765.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260543923</t>
+          <t>20260546821</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1451,7 +1455,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1464,22 +1468,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Eduardo Arguelles Landaverde, a single man, and Carmen Felicitas Verduzco Parra, a single</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>445,480.00</t>
+          <t>208,000.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5415 W POINSETTIA DR</t>
+          <t>16025 North Church Street</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1489,7 +1497,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>85378</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1503,59 +1511,75 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>148-27-321</t>
+          <t>501-20-042</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>inancial Inc. dba Trustee Corps</t>
+          <t>for Current Trustee</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(202) 207-3928</t>
+          <t>(202) 306-2312</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Eduardo Arguelles Landaverde, a single</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>man,</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Carmen Felicitas Verduzco Parra, a</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543923.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546821.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543923.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546821.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543923.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546821.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260543955</t>
+          <t>20260546849</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1565,7 +1589,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1578,22 +1602,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kirk Lomawaima</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>74,800.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7304 S 48TH GLN</t>
+          <t>or IDENTIFIABLE LOCATION: 3526 WEST DUNLAP AVENUE UNIT 149</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Laveen</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1603,7 +1631,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1617,59 +1645,67 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>104-89-093</t>
+          <t>149-39-515</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(202) 301-2724</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Kirk</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Lomawaima</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260543955.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546849.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260543955.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546849.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260543955.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546849.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260544162</t>
+          <t>20260546851</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1679,7 +1715,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1694,20 +1730,36 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alis Gerardo Ramirez (a single man)</t>
+          <t>(s), in favor of Sun American Mortgage Company, as beneficiary, and was</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>98,900.00</t>
+          <t>412,942.81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17823 N CONQUISTADOR DR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Sun City West</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1719,67 +1771,71 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>506-40</t>
+          <t>232-08-081</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>you should contact the Foreclosure Commissioner, Quality Loan Service Corporation, at the</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(202) 605-4416</t>
+          <t>(200) 603-9931</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Alis Gerardo Ramirez (a single</t>
+          <t>(s), in favor of Sun American Mortgage Company, as</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>man)</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
+          <t>beneficiary,</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>was</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544162.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546851.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544162.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546851.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544162.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546851.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260544166</t>
+          <t>20260546858</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1789,7 +1845,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1802,22 +1858,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Daniel Uriarte Lozano and Ana Evelia Felix (a married couple)</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>25,000.00</t>
+          <t>100,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10128 W HIGHLAND AVE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85037</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1829,75 +1897,59 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>504-33</t>
+          <t>102-82-039</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(202) 605-4416</t>
+          <t>(685) 202-6054</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Daniel Uriarte</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Lozano</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Ana Evelia Felix (a married</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>couple)</t>
-        </is>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544166.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546858.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544166.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546858.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544166.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546858.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260544171</t>
+          <t>20260546866</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1907,7 +1959,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1922,20 +1974,36 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jose Adolfo Zazueta (a single man)</t>
+          <t>(s): Luke E. Bourns Aka Luke Bournes, As Co</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30,900.00</t>
+          <t>140,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14328 N 66TH DR</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85306</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1947,34 +2015,34 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>504-32-311</t>
+          <t>200-70-015</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(202) 605-4417</t>
+          <t>(200) 740-1125</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Jose Adolfo Zazueta (a single</t>
+          <t>(s): Luke E. Bourns Aka Luke Bournes, As</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>man)</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -1982,32 +2050,32 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544171.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546866.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544171.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546866.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544171.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546866.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260544191</t>
+          <t>20260546978</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2017,7 +2085,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2032,13 +2100,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ryan Edgin and Ashtyn Edgin, husband and wife</t>
+          <t>Esmeralda Investments Remodeling Llc, an Arizona limited liability</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>150,000.00</t>
+          <t>335,000.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2125,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>506-05-075</t>
+          <t>504-28-367</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2068,44 +2136,36 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 605-4419</t>
+          <t>(202) 605-4697</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Esmeralda Investments Remodeling Llc, an Arizona limited</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Edgin</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Ashtyn Edgin, husband and</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>liability</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544191.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546978.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544191.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546978.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2118,14 +2178,14 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544191.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546978.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260544217</t>
+          <t>20260547167</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2135,7 +2195,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2150,20 +2210,36 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Esteban Jovanni Calvillo (a single man)</t>
+          <t>Patrick Daniel Alexander, a single man</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58,000.00</t>
+          <t>96,000.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>109 N Los Robles Dr</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Goodyear</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2175,34 +2251,30 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>506-41</t>
+          <t>500-15-110</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 605-4421</t>
+          <t>(202) 405-1670</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Esteban Jovanni Calvillo (a single</t>
+          <t>Patrick Daniel Alexander, a single</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>man)</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -2210,32 +2282,32 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544217.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547167.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544217.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547167.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544217.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547167.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260544226</t>
+          <t>20260547170</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2245,7 +2317,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2260,24 +2332,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ricardo Hernandez Ramirez and Lina Laura Balmaceda Vazquez (a</t>
+          <t>Diane Cali, widow</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>42,400.00</t>
+          <t>164,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3914 W Palm Ln</t>
+          <t>8437 W Audrey Ln</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2287,7 +2359,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2301,75 +2373,63 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>504-32</t>
+          <t>233-04-214</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(202) 605-4422</t>
+          <t>(201) 910-2008</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Ricardo Hernandez</t>
+          <t>Diane Cali,</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Ramirez</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Lina Laura Balmaceda Vazquez</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>(a</t>
-        </is>
-      </c>
+          <t>widow</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544226.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547170.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544226.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547170.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544226.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547170.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260544230</t>
+          <t>20260547177</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2379,7 +2439,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2394,24 +2454,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guadalupe Pina Padilla (a single man)</t>
+          <t>Janet R. Miller, an unmarried woman</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29,700.00</t>
+          <t>63,741.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3633 W Grant St</t>
+          <t>1809 W Cheyenne Dr</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Chandler</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2421,7 +2481,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>85224</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2435,34 +2495,26 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>506-43-145</t>
+          <t>302-25-697</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(202) 605-4423</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
+          <t>(201) 211-2224</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Guadalupe Pina Padilla (a single</t>
+          <t>Janet R. Miller, an unmarried</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>man)</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2470,32 +2522,32 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544230.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547177.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544230.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547177.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544230.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547177.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260544235</t>
+          <t>20260547526</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2505,7 +2557,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2518,22 +2570,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Veronica Almontes (a single woman) and Yasmin Guadalupe Angelino</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>93,500.00</t>
+          <t>9,052,445.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>or identifiable 2326 E Washington Street</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85034</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2545,75 +2609,63 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>506-43-147</t>
+          <t>115-01</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>appointed here qualifies as a Trustee</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 605-4423</t>
+          <t>(202) 400-8127</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Veronica Almontes (a single</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>woman)</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yasmin Guadalupe</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Angelino</t>
-        </is>
-      </c>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544235.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547526.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544235.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547526.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544235.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547526.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260544310</t>
+          <t>20260547535</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2623,7 +2675,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2636,21 +2688,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Stephen Stewart, Jr, a single man</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>338,751.00</t>
+          <t>9,052,445.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3727 W Gardenia Ave</t>
+          <t>or identifiable 2326 E Washington Street</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2665,7 +2713,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85051</t>
+          <t>85034</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2679,63 +2727,63 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>151-25-116</t>
+          <t>115-01</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>appointed here qualifies as a Trustee</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 502-4929</t>
+          <t>(202) 400-8127</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Stephen Stewart, Jr, a single</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544310.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547535.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544310.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547535.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544310.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547535.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260544385</t>
+          <t>20260547549</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2745,7 +2793,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2760,24 +2808,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marsha Bohn, a married woman as her sole and separate property</t>
+          <t>(s): Glenn Alan Brandt, an unmarried man</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>432,000.00</t>
+          <t>327,228.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4561 S Ranger Trail</t>
+          <t>3746 E DRAGOON AVE</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2787,7 +2835,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85297</t>
+          <t>85206</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2801,55 +2849,47 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>313-02-905</t>
+          <t>140-38-072</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>for Current Trustee</t>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(202) 605-4438</t>
+          <t>(202) 106-4989</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Marsha Bohn, a married woman as her</t>
+          <t>(s): Glenn Alan Brandt, an unmarried</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>sole</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>separate</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>property</t>
-        </is>
-      </c>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544385.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547549.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544385.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547549.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2862,14 +2902,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544385.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547549.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260544400</t>
+          <t>20260547731</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2879,7 +2919,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2892,26 +2932,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Terresha Peten, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>472,000.00</t>
+          <t>455,280.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12205 West Harrison Street</t>
+          <t>6721 S LAKESHORE DR</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2921,7 +2957,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2933,65 +2969,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>500-29-301</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(202) 202-9041</t>
+          <t>(202) 200-3342</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Terresha Peten, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544400.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547731.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544400.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547731.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544400.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547731.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260544573</t>
+          <t>20260547776</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3001,7 +3029,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3014,26 +3042,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Aaron Keith Morrison, an unmarried man, 4622 E. Red</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>150,000.00</t>
+          <t>51,563.80</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4622 E. Red Range Way</t>
+          <t>5548 N 9TH AVE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Cave Creek</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3043,7 +3067,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85331</t>
+          <t>85013</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3055,1778 +3079,50 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>211-60-343</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Statewide Foreclosure Services, Inc., a</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(632) 954-7523</t>
+          <t>(201) 500-0899</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Aaron Keith Morrison, an unmarried man, 4622 E.</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544573.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547776.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544573.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547776.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544573.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20260544593</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Home Invest Hdr Llc, an Arizona limited liability</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>32,000.00</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2150 E. Brown Road, Ste 2 60</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85213</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>137-05-010</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Statewide Foreclosure Services, Inc., a</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>(202) 109-3909</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Home Invest Hdr Llc, an Arizona limited</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>liability</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544593.pdf</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544593.pdf</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544593.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20260544788</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Jesus A Lopez Padilla</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>286,900.00</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>or IDENTIFIABLE LOCATION: 4449 N 48TH AVE</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>85031</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>145-22-071</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Jesus A Lopez</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Padilla</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544788.pdf</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544788.pdf</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544788.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20260544831</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Mountain Town Homes, Llc, an Arizona limited liability company</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>391,000.00</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>580 E Wilcox Drive</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Sierra Vista</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85635</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>219-60-462</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>(520) 458-3500</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Mountain Town Homes, Llc, an Arizona limited liability</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544831.pdf</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544831.pdf</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_auction_date</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544831.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20260544849</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ike S Paik, an unmarried man</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>199,500.00</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>4212 N 113th Dr</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>85037</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>102-90-089</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>(202) 107-2941</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Ike S Paik, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544849.pdf</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544849.pdf</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_trustee</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544849.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20260544856</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Jason Patterson, a single man</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>114,000.00</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>4226 North 22nd Street #13</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>85016</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>163-32</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>(201) 301-4480</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Jason Patterson, a single</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544856.pdf</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544856.pdf</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_trustee</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544856.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20260544875</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Ida M. Lee</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>487,500.00</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>or IDENTIFIABLE LOCATION: 11921 W ASTER DR</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>El Mirage</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85335</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>509-06-030</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Ida M.</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544875.pdf</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544875.pdf</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544875.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20260544882</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Jason Bolen And Leslie Bolen</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>322,746.00</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>or IDENTIFIABLE LOCATION: 2344 W MELODY DR</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>300-17-330</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Jason Bolen And Leslie</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Bolen</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260544882.pdf</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260544882.pdf</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260544882.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20260545004</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Jesse Dee Irvine, an unmarried man, 11462 W Roanoke Dr, Avondale, Az 85392</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>306,776.00</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>11462 W Roanoke Drive</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Avondale</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85392</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>102-30-889</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Jesse Dee Irvine, an unmarried man, 11462 W Roanoke Dr, Avondale, Az</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>85392</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545004.pdf</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545004.pdf</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_auction_date</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>90</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545004.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>20260545056</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Ramses A. Romo Mendez</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>230,000.00</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>or IDENTIFIABLE LOCATION: 20334 W HUBBARD RD</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Buckeye</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>400-82-100</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Ramses A. Romo</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Mendez</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545056.pdf</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545056.pdf</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545056.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20260545237</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>332,000.00</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>42909 N 46TH AVE</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>New River</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>85087</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>202-30-051</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>(201) 609-4476</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545237.pdf</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545237.pdf</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545237.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20260545354</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>J&amp;M Brothers Llc, an Arizona limited liability company</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>260,000.00</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>11515 N 91st St Unit 209</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Scottsdale</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>85260</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>217-48-511</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>(202) 505-9680</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>J&amp;M Brothers Llc, an Arizona limited liability</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545354.pdf</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545354.pdf</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_auction_date</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>90</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545354.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260545356</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>J&amp;M Brothers Llc, an Arizona limited liability company</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>408,000.00</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2702 N 2ist St</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>85006</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>117-02-033</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>(202) 505-5859</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>J&amp;M Brothers Llc, an Arizona limited liability</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545356.pdf</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545356.pdf</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_auction_date</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545356.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>20260545359</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>N/TR SALE+</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>’s Stated Name and Address: Rpc Phx N 4th, Llc, 1705 South Capital of Texas</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1,185,000.00</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>(202) 207-3248</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>’s Stated</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Address: Rpc Phx N 4th, Llc, 1705 South Capital of</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545359.pdf</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545359.pdf</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>45</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545359.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>20260545373</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Jameson Campbell, an unmarried man, and Clifford Campbell, an unmarried man, as joint tenants</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>353,479.00</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>1818 S 78th St</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>85209</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>218-57-863</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>(202) 304-5932</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Jameson Campbell, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>man,</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Clifford Campbell, an unmarried man, as joint</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>tenants</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545373.pdf</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545373.pdf</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_trustee</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545373.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547776.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH22"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -423,10 +423,10 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="58" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="36" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="49" customWidth="1" min="32" max="32"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260545704</t>
+          <t>20260548168</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -654,18 +654,18 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>348,655.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30959 W. FAIRMOUNT AVE</t>
+          <t>14912 N 158TH LANE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>85379</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -687,21 +687,25 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>501-79-607</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>iba Trustee Corps</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 204-4471</t>
+          <t>(201) 906-4492</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -712,32 +716,32 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545704.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260548168.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545704.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260548168.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545704.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260548168.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260545869</t>
+          <t>20260548175</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -747,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -760,26 +764,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>259,000.00</t>
+          <t>210,000.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4608 W KRALL ST.</t>
+          <t>10753 WEST DEL RIO LANE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -803,59 +803,59 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>156-45-184</t>
+          <t>101-54-689</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Unofficial Document</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 000-3240</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
+          <t>(200) 617-0453</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545869.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260548175.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545869.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260548175.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545869.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260548175.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260545931</t>
+          <t>20260548742</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -882,30 +882,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>325,000.00</t>
+          <t>292,000.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2045 S LAROSA DR</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Tempe</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>85282</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -917,18 +901,18 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>133-25-064</t>
+          <t>303-49-118</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 103-0870</t>
+          <t>(200) 601-9760</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -944,32 +928,32 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260545931.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260548742.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260545931.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260548742.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260545931.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260548742.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260546069</t>
+          <t>20260548773</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,7 +963,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -994,16 +978,28 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>125,000.00</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1827 W EL MONTE PL</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85224</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1015,30 +1011,26 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>103-12-549</t>
+          <t>302-89-734</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>may require entity or trust bidders at this trustee's sale to provide</t>
+          <t>'s deed upon sale. No trustee's deed will be issued for a covered transfer until all required</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(226) 080-6114</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1046,32 +1038,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546069.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260548773.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546069.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260548773.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546069.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260548773.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260546721</t>
+          <t>20260548855</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,7 +1073,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1094,26 +1086,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Michael Paul Kaufman And Meryl Lisa Kaufman</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>75,800.00</t>
+          <t>200,000.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 8830 W CORRINE DR</t>
+          <t>3025 E Minton St</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1123,7 +1111,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85381</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1137,67 +1125,63 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>200-79-930</t>
+          <t>102-09-250</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>may require entity or trust bidders at this trustee's sale to provide</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(226) 081-3118</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Michael Paul Kaufman And Meryl Lisa</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Kaufman</t>
-        </is>
-      </c>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546721.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260548855.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546721.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260548855.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546721.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260548855.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260546723</t>
+          <t>20260548873</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1207,7 +1191,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1220,26 +1204,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unofficial Document</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>137,144.00</t>
+          <t>494,000.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>901 W LIBRA DR</t>
+          <t>2447 E HAZELTINE WAY</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1249,7 +1229,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>85298</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1263,67 +1243,59 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>301-05-229</t>
+          <t>304-86-672</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(201) 507-1356</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Unofficial</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Document</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546723.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260548873.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546723.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260548873.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546723.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260548873.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260546765</t>
+          <t>20260549116</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1333,7 +1305,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1346,26 +1318,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>238,500.00</t>
+          <t>636,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>25396 W Ellis Dr</t>
+          <t>11423 N 12TH PL</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1375,7 +1343,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1391,61 +1359,53 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4915 E. Baseline Rd., Suite #105</t>
+          <t>herein qualifies as Trustee of the Trtist Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(480) 305-7007</t>
+          <t>(202) 204-1909</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2027-08-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>an unmarried</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546765.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549116.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546765.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549116.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546765.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549116.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260546821</t>
+          <t>20260549141</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1455,7 +1415,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1468,26 +1428,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Eduardo Arguelles Landaverde, a single man, and Carmen Felicitas Verduzco Parra, a single</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>208,000.00</t>
+          <t>318,250.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16025 North Church Street</t>
+          <t>181 S 221ST DR</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1497,7 +1453,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85378</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1511,75 +1467,59 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>501-20-042</t>
+          <t>504-20-298</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>for Current Trustee</t>
+          <t>ancial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(202) 306-2312</t>
+          <t>(200) 724-9552</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Eduardo Arguelles Landaverde, a single</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>man,</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Carmen Felicitas Verduzco Parra, a</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546821.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549141.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546821.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549141.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546821.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549141.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260546849</t>
+          <t>20260549266</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1589,7 +1529,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1604,24 +1544,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kirk Lomawaima</t>
+          <t>(s): Faten Amar, a married woman as her sole and</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>74,800.00</t>
+          <t>548,250.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 3526 WEST DUNLAP AVENUE UNIT 149</t>
+          <t>9525 E YUCCA ST</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1631,7 +1571,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85051</t>
+          <t>85260</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1645,34 +1585,34 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>149-39-515</t>
+          <t>217-48-685</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 104-9155</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Kirk</t>
+          <t>(s): Faten Amar, a married woman as her sole</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Lomawaima</t>
+          <t>and</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -1680,12 +1620,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546849.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549266.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546849.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549266.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1698,14 +1638,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546849.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549266.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260546851</t>
+          <t>20260549316</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1715,7 +1655,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1730,24 +1670,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(s), in favor of Sun American Mortgage Company, as beneficiary, and was</t>
+          <t>Susan Novak and Chad Novak, wife and husband</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>412,942.81</t>
+          <t>276,892.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17823 N CONQUISTADOR DR</t>
+          <t>4156 W Michelle Dr</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Sun City West</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1757,7 +1697,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85375</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1771,71 +1711,71 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>232-08-081</t>
+          <t>207-21-337</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>you should contact the Foreclosure Commissioner, Quality Loan Service Corporation, at the</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(200) 603-9931</t>
+          <t>(200) 746-4233</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>(s), in favor of Sun American Mortgage Company, as</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>beneficiary,</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>Chad Novak, wife and</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546851.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549316.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546851.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549316.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546851.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549316.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260546858</t>
+          <t>20260549342</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1845,7 +1785,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1858,22 +1798,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Guy U Martinez and Natalie M Martinez, husband and wife as community property with right of</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>100,000.00</t>
+          <t>132,600.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10128 W HIGHLAND AVE</t>
+          <t>2658 West Naranja Avenue</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1883,7 +1827,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85037</t>
+          <t>85202</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1897,59 +1841,71 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>102-82-039</t>
+          <t>305-04-695</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(685) 202-6054</t>
+          <t>(200) 901-7826</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Guy U</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Natalie M Martinez, husband and wife as community property with right</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546858.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549342.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546858.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549342.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546858.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549342.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260546866</t>
+          <t>20260549383</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1959,7 +1915,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1972,21 +1928,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>(s): Luke E. Bourns Aka Luke Bournes, As Co</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>140,000.00</t>
+          <t>422,211.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14328 N 66TH DR</t>
+          <t>or identifiable location: 10650 N 49TH AVE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2001,7 +1953,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>85304</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2015,67 +1967,63 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>200-70-015</t>
+          <t>148-04-358</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(200) 740-1125</t>
+          <t>(202) 504-2009</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>(s): Luke E. Bourns Aka Luke Bournes, As</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546866.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549383.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546866.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549383.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546866.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549383.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260546978</t>
+          <t>20260549876</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2085,7 +2033,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2100,20 +2048,36 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Esmeralda Investments Remodeling Llc, an Arizona limited liability</t>
+          <t>Osmyn Aaron Martinez, an unmarried man</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>335,000.00</t>
+          <t>313,500.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2125,34 +2089,30 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>504-28-367</t>
+          <t>105-70-090</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 605-4697</t>
+          <t>(202) 205-7135</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Esmeralda Investments Remodeling Llc, an Arizona limited</t>
+          <t>Osmyn Aaron Martinez, an unmarried</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -2160,32 +2120,32 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260546978.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549876.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260546978.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549876.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260546978.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549876.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260547167</t>
+          <t>20260549877</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2195,7 +2155,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2210,24 +2170,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Patrick Daniel Alexander, a single man</t>
+          <t>Kathreen Limin Canlas,, and Jason Aguilar. a married couple, as community property with right of</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>96,000.00</t>
+          <t>312,240.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>109 N Los Robles Dr</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Goodyear</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2237,7 +2197,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85338</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2251,43 +2211,51 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>500-15-110</t>
+          <t>104-91-364</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 405-1670</t>
+          <t>(202) 005-8119</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Patrick Daniel Alexander, a single</t>
+          <t>Kathreen Limin</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+          <t>Canlas,,</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Jason Aguilar. a married couple, as community property with right</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547167.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549877.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547167.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549877.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2300,14 +2268,14 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547167.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549877.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260547170</t>
+          <t>20260549892</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2317,7 +2285,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2332,24 +2300,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diane Cali, widow</t>
+          <t>Martin Alday-Borjas, a married man as his sole and separate</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>164,000.00</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8437 W Audrey Ln</t>
+          <t>6222 S 2nd Ave</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2359,7 +2327,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85382</t>
+          <t>85041</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2373,43 +2341,47 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>233-04-214</t>
+          <t>114-03-045</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(201) 910-2008</t>
+          <t>(201) 702-1047</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Diane Cali,</t>
+          <t>Martin Alday-Borjas, a married man as his</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>widow</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
+          <t>sole</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>separate</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547170.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549892.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547170.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549892.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2422,14 +2394,14 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547170.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549892.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260547177</t>
+          <t>20260549906</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2439,7 +2411,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2454,24 +2426,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Janet R. Miller, an unmarried woman</t>
+          <t>Elisabeth M. Weedman, a single woman</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>63,741.00</t>
+          <t>105,000.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1809 W Cheyenne Dr</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2481,7 +2453,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85224</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2495,21 +2467,25 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>302-25-697</t>
+          <t>142-72-684</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(201) 211-2224</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>(202) 005-5852</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Janet R. Miller, an unmarried</t>
+          <t>Elisabeth M. Weedman, a single</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2522,32 +2498,32 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547177.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549906.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547177.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549906.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547177.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549906.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260547526</t>
+          <t>20260549911</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2557,7 +2533,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2574,18 +2550,18 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9,052,445.00</t>
+          <t>234,000.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>or identifiable 2326 E Washington Street</t>
+          <t>629 W PLATAAVE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2595,7 +2571,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2609,30 +2585,26 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>115-01</t>
+          <t>302-77-598</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>appointed here qualifies as a Trustee</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 400-8127</t>
+          <t>(202) 202-5141</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -2640,12 +2612,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547526.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549911.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547526.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549911.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2658,14 +2630,14 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547526.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549911.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260547535</t>
+          <t>20260549913</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2675,7 +2647,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2688,17 +2660,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Michael W Johnson, an unmarried man</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9,052,445.00</t>
+          <t>244,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>or identifiable 2326 E Washington Street</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2713,7 +2689,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2727,63 +2703,63 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>115-01</t>
+          <t>138-23</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>appointed here qualifies as a Trustee</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 400-8127</t>
+          <t>(202) 109-2594</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Michael W Johnson, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547535.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549913.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547535.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549913.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547535.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549913.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260547549</t>
+          <t>20260549922</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2793,7 +2769,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2808,24 +2784,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(s): Glenn Alan Brandt, an unmarried man</t>
+          <t>Matthew James Hobbs and Christina M. Hobbs, a married couple as community property with right</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>327,228.00</t>
+          <t>229,000.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3746 E DRAGOON AVE</t>
+          <t>2810 West Windsong Drive</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2835,7 +2811,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>85045</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2849,67 +2825,71 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>140-38-072</t>
+          <t>300-05-428</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(202) 106-4989</t>
+          <t>(202) 206-1212</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>(s): Glenn Alan Brandt, an unmarried</t>
+          <t>Matthew James</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+          <t>Hobbs</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Christina M. Hobbs, a married couple as community property with</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547549.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549922.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547549.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549922.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547549.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549922.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260547731</t>
+          <t>20260549937</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2919,7 +2899,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2932,22 +2912,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Miami Real Estate Holdings, Llc a Wyoming Limited Liability Company</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>455,280.00</t>
+          <t>461,500.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6721 S LAKESHORE DR</t>
+          <t>1326 W Cove Drive</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2957,7 +2941,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>85233</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2969,160 +2953,62 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>302-30-533</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(202) 200-3342</t>
+          <t>(202) 206-5651</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Miami Real Estate Holdings, Llc a Wyoming Limited Liability</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547731.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260549937.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547731.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260549937.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547731.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20260547776</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>51,563.80</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>5548 N 9TH AVE</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>85013</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>(201) 500-0899</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026-12-24</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260547776.pdf</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260547776.pdf</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260547776.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260549937.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,19 +413,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="49" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -436,20 +436,20 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
+    <col width="50" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="55" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +621,2774 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>raw_text_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260550745</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550745.pdf</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>pdf_blocked</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260550791</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>331,987.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>or identifiable location: | 23996 W Hidalgo Ave</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>504-75-495</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550791.pdf</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260550791.pdf</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260550791.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260550880</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550880.pdf</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>pdf_blocked</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260550890</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550890.pdf</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>pdf_blocked</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260551191</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>299,145.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>or identifiable location: 4653 NORTH 99TH DRIVE</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85037</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>102-82-678</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551191.pdf</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551191.pdf</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551191.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260551199</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>427,500.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>or identifiable location: 25616 W NANCY LN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>504-57-435</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551199.pdf</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551199.pdf</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551199.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260551207</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>296,495.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>or identifiable location: 5129 W THRESHER WAY</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Laveen</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85339</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>300-03-479</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551207.pdf</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551207.pdf</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551207.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260551904</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>296,384.48</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3140 W WOOD DR.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85029</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(312) 357-1125</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551904.pdf</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551904.pdf</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_trustee, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551904.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260551969</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stacia E Holmes, a single person</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>184,005.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>312-03-739</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(200) 749-6961</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Stacia E Holmes, a single</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551969.pdf</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551969.pdf</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551969.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260552056</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nicholas E. Carroll, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>208,000.00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>207-21-023</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Current Trustee</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(200) 739-3261</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Nicholas E. Carroll, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552056.pdf</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552056.pdf</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552056.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260552085</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Angel Moreno, a single man</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>249,332.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8644 W Diana Ave</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85345</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>142-34-199</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>(202) 201-2588</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Angel Moreno, a single</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552085.pdf</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552085.pdf</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552085.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260552108</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Paul C. Ruzycki-Shinabarger and Amy Dawn Ruzycki-Shinabarger, husband and wife</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>125,250.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>312-01-175</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Current Trustee</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(200) 749-7195</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Paul C.</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Ruzycki-Shinabarger</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Amy Dawn Ruzycki-Shinabarger, husband and</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552108.pdf</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552108.pdf</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552108.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260552176</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Andrew T Swafford, a single man</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>260,000.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>12029 S Mandan Street</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85044</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>301-55-700</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(200) 758-0650</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Andrew T Swafford, a single</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552176.pdf</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552176.pdf</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552176.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260552247</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Emerald Villa Properties Llc, an Illinois limited liability company</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>385,000.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3131 N Central Ave Unit 5010</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85012</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>118-34-584</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(202) 502-2603</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Emerald Villa Properties Llc, an Illinois limited liability</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552247.pdf</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552247.pdf</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552247.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260552399</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jerrick Brambila And Kevin Brambila</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>294,566.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 4444 N SOTH AVENUE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85031</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>145-21-111</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Jerrick Brambila And Kevin</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Brambila</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552399.pdf</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552399.pdf</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552399.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260552462</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>George J Baca And Georgia G Baca</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>247,900.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 8956 W ALEX AVE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85382</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>200-16-215</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>George J Baca And Georgia G</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Baca</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552462.pdf</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552462.pdf</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552462.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260552626</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Susan M Wilkinson And Lonnie L Wilkinson</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>382,580.00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 18227 W PURDUE AVE</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Waddell</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85355</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>502-91-272</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Susan M Wilkinson And Lonnie L</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Wilkinson</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552626.pdf</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552626.pdf</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552626.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260552643</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kieran J Elia, a single man</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>108,000.00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>110-46-168</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(201) 706-0731</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Kieran J Elia, a single</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552643.pdf</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552643.pdf</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552643.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260552648</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kischa Lajoi Rushing, an unmarried woman and Louis A. Armstrong, Jr., an unmarried man, as</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>77,000.00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>11604 W Marguerite Ave</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>500-67-088</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(202) 303-7501</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Kischa Lajoi Rushing, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Louis A. Armstrong, Jr., an unmarried man,</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552648.pdf</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552648.pdf</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552648.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260552661</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>(s): Steven Phillip Parmenter And Sherri L.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>203,841.97</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1421 E KERRY LN</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85024</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>213-24-224</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(200) 751-6780</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>(s): Steven Phillip Parmenter And Sherri</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552661.pdf</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552661.pdf</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552661.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260552665</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Evelyn Kabage, an unmarried woman, and Paul F. Landsberg, a married man as his sole and separate</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>100,000.00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>232-09-846</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(201) 801-5053</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Evelyn Kabage, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>woman,</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Paul F. Landsberg, a married man as his sole and</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552665.pdf</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552665.pdf</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552665.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260552691</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jacquelyn Franco, a single woman</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>191,468.00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>139-30-071</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>(201) 704-6221</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Jacquelyn Franco, a single</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552691.pdf</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552691.pdf</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552691.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260552849</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Alejandro Valenzuela and Maria F. Alarcon, husband and wife</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>527,946.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>304-63-918</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(202) 208-8170</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Valenzuela</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Maria F. Alarcon, husband and</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552849.pdf</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552849.pdf</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552849.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260552880</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>25,000.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>8804 S 10th Dr</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>300-51-101</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552880.pdf</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552880.pdf</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552880.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH25"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -423,10 +423,10 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="49" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="21" customWidth="1" min="26" max="26"/>
-    <col width="50" customWidth="1" min="27" max="27"/>
+    <col width="56" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260550745</t>
+          <t>20260553430</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,14 +650,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Donna Y. Hickman, an unmarried woman</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>250,000.00</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -667,37 +691,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>501-39-511</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(202) 200-6136</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Donna Y. Hickman, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550745.pdf</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553430.pdf</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553430.pdf</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>pdf_blocked</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553430.txt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260550791</t>
+          <t>20260553539</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -707,7 +755,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -724,18 +772,18 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>331,987.00</t>
+          <t>200,084.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>or identifiable location: | 23996 W Hidalgo Ave</t>
+          <t>or identifiable location: 3850 W Villa Maria Dr</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -745,7 +793,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -759,13 +807,13 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>504-75-495</t>
+          <t>207-21-091</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -775,7 +823,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -786,12 +834,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550791.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553539.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260550791.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553539.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -804,14 +852,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260550791.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553539.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260550880</t>
+          <t>20260553553</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,7 +869,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -836,12 +884,32 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>359,330.00</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>or identifiable location: 23577 W MOHAVE ST</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -851,11 +919,27 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>504-28-396</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
@@ -864,24 +948,32 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550880.pdf</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553553.pdf</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553553.pdf</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>pdf_blocked</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553553.txt</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260550890</t>
+          <t>20260553554</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -891,7 +983,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +998,32 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>333,398.00</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4828 S 17TH ST</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -923,9 +1035,21 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(202) 305-3525</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
@@ -934,24 +1058,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260550890.pdf</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553554.pdf</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553554.pdf</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>pdf_blocked</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553554.txt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260551191</t>
+          <t>20260553791</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -961,7 +1093,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -974,17 +1106,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosa Maria De La Torre an unmarried woman</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>299,145.00</t>
+          <t>213,592.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>or identifiable location: 4653 NORTH 99TH DRIVE</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -999,7 +1135,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85037</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1013,59 +1149,63 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>102-82-678</t>
+          <t>135-60-193</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 300-9980</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Rosa Maria De La Torre an unmarried</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551191.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553791.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551191.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553791.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551191.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553791.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260551199</t>
+          <t>20260553807</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1075,7 +1215,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1092,18 +1232,18 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>427,500.00</t>
+          <t>35,000.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>or identifiable location: 25616 W NANCY LN</t>
+          <t>4616 N 30th Drive</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1113,7 +1253,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85017</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1127,26 +1267,30 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>504-57-435</t>
+          <t>154-10-093</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>may require entity or trust bidders at this trustee's sale to provide</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(226) 091-1132</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1154,12 +1298,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551199.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553807.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551199.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553807.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1172,14 +1316,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551199.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553807.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260551207</t>
+          <t>20260553836</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1189,7 +1333,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1206,30 +1350,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>296,495.00</t>
+          <t>75,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>or identifiable location: 5129 W THRESHER WAY</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Laveen</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>85339</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1241,18 +1369,18 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>300-03-479</t>
+          <t>309-05-147</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>may require entity or trust bidders at this trustee's sale to provide</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(226) 082-1124</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1260,7 +1388,11 @@
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1268,32 +1400,32 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551207.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553836.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551207.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553836.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551207.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553836.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260551904</t>
+          <t>20260553935</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1303,7 +1435,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1320,13 +1452,13 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>296,384.48</t>
+          <t>324,022.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3140 W WOOD DR.</t>
+          <t>8239 W ILLINI ST</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1341,7 +1473,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>85043</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1355,15 +1487,19 @@
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(312) 357-1125</t>
+          <t>(202) 106-9096</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1374,32 +1510,32 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551904.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260553935.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551904.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260553935.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_trustee, missing_apn</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551904.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260553935.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260551969</t>
+          <t>20260554002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1409,7 +1545,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1422,21 +1558,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Stacia E Holmes, a single person</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>184,005.00</t>
+          <t>538,720.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>17625 N. 5TH PLACE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1451,7 +1583,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1463,65 +1595,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>312-03-739</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(200) 749-6961</t>
+          <t>(202) 301-1091</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Stacia E Holmes, a single</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260551969.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554002.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260551969.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554002.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260551969.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554002.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260552056</t>
+          <t>20260554136</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1531,7 +1655,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1544,26 +1668,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Nicholas E. Carroll, an unmarried man</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>208,000.00</t>
+          <t>134,310.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>4517 W MCLELLAN RD</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1573,7 +1693,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1585,69 +1705,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>207-21-023</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Current Trustee</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(200) 739-3261</t>
+          <t>(202) 108-9224</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Nicholas E. Carroll, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552056.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554136.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552056.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554136.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552056.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554136.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260552085</t>
+          <t>20260554149</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1657,7 +1765,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1672,24 +1780,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Angel Moreno, a single man</t>
+          <t>Lantino Luna &amp; Amber S Luna, Husband and</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>249,332.00</t>
+          <t>40,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8644 W Diana Ave</t>
+          <t>1126 W Portland St</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1699,7 +1807,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85345</t>
+          <t>85007</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1713,43 +1821,51 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>142-34-199</t>
+          <t>111-20-062</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(202) 201-2588</t>
+          <t>(202) 507-4801</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Angel Moreno, a single</t>
+          <t>Lantino</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Amber S Luna, Husband</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552085.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554149.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552085.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554149.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1762,14 +1878,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552085.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554149.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260552108</t>
+          <t>20260554203</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1779,7 +1895,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1792,21 +1908,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Paul C. Ruzycki-Shinabarger and Amy Dawn Ruzycki-Shinabarger, husband and wife</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>125,250.00</t>
+          <t>540,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>27713 N 57TH DR</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1821,7 +1933,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1835,75 +1947,59 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>312-01-175</t>
+          <t>201-41-179</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Current Trustee</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(200) 749-7195</t>
+          <t>(202) 303-2750</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Paul C.</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Ruzycki-Shinabarger</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Amy Dawn Ruzycki-Shinabarger, husband and</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552108.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554203.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552108.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554203.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552108.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554203.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260552176</t>
+          <t>20260554241</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1913,7 +2009,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1926,26 +2022,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Andrew T Swafford, a single man</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>260,000.00</t>
+          <t>315,425.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12029 S Mandan Street</t>
+          <t>17818 N 45TH AVE</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1955,7 +2047,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85044</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1969,63 +2061,59 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>301-55-700</t>
+          <t>207-22-057</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>efal ins, dba Trustee Corps</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(200) 758-0650</t>
+          <t>(200) 749-5467</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Andrew T Swafford, a single</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552176.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554241.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552176.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554241.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552176.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554241.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260552247</t>
+          <t>20260554761</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2035,7 +2123,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2048,38 +2136,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Emerald Villa Properties Llc, an Illinois limited liability company</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>385,000.00</t>
+          <t>222,000.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>3131 N Central Ave Unit 5010</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>85012</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2091,59 +2159,59 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>118-34-584</t>
+          <t>122-96-828</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 502-2603</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>(200) 731-7170</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Emerald Villa Properties Llc, an Illinois limited liability</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552247.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554761.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552247.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554761.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552247.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554761.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260552399</t>
+          <t>20260554778</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2153,7 +2221,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2166,21 +2234,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Jerrick Brambila And Kevin Brambila</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>294,566.00</t>
+          <t>179,200.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 4444 N SOTH AVENUE</t>
+          <t>3033 W CORRINE DR</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2195,7 +2259,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85031</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2209,67 +2273,59 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>145-21-111</t>
+          <t>149-22-077</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(200) 747-0643</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Jerrick Brambila And Kevin</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Brambila</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552399.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554778.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552399.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554778.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552399.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554778.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260552462</t>
+          <t>20260554869</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2279,7 +2335,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2294,24 +2350,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>George J Baca And Georgia G Baca</t>
+          <t>(s): Shamim A Rehman, unmarried person</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>247,900.00</t>
+          <t>389,500.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 8956 W ALEX AVE</t>
+          <t>1130 N 2ND STREET UNIT 401</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2321,7 +2377,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85382</t>
+          <t>85004</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2335,34 +2391,34 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>200-16-215</t>
+          <t>141-36-165</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 012-4812</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>George J Baca And Georgia G</t>
+          <t>(s): Shamim A Rehman, unmarried</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Baca</t>
+          <t>person</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2370,12 +2426,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552462.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554869.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552462.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554869.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2388,14 +2444,14 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552462.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554869.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260552626</t>
+          <t>20260554870</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2405,7 +2461,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2420,24 +2476,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Susan M Wilkinson And Lonnie L Wilkinson</t>
+          <t>(s): Camillia R Diaz, an unmarried woman</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>382,580.00</t>
+          <t>127,645.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 18227 W PURDUE AVE</t>
+          <t>1520 E GARY WAY</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Waddell</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2447,7 +2503,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85355</t>
+          <t>85042</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2461,34 +2517,34 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>502-91-272</t>
+          <t>300-23-091</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(201) 703-5606</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Susan M Wilkinson And Lonnie L</t>
+          <t>(s): Camillia R Diaz, an unmarried</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr"/>
@@ -2496,12 +2552,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552626.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554870.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552626.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554870.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2514,14 +2570,14 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552626.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554870.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260552643</t>
+          <t>20260554871</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2531,7 +2587,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2546,19 +2602,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kieran J Elia, a single man</t>
+          <t>(s): Yoanna Galindo, a married woman as her sole and</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>108,000.00</t>
+          <t>234,025.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>4124 W ENCANTO BLVD</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2573,7 +2629,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2587,34 +2643,34 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>110-46-168</t>
+          <t>108-33-160</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(201) 706-0731</t>
+          <t>(202) 205-6255</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Kieran J Elia, a single</t>
+          <t>(s): Yoanna Galindo, a married woman as her sole</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>and</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -2622,12 +2678,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552643.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260554871.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552643.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260554871.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2640,14 +2696,14 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552643.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260554871.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260552648</t>
+          <t>20260555048</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2657,7 +2713,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2670,21 +2726,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Kischa Lajoi Rushing, an unmarried woman and Louis A. Armstrong, Jr., an unmarried man, as</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>77,000.00</t>
+          <t>227,500.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11604 W Marguerite Ave</t>
+          <t>11301 W CITRUS GROVE WAY</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2713,71 +2765,59 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>500-67-088</t>
+          <t>102-28-526</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(202) 303-7501</t>
+          <t>(200) 713-2145</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Kischa Lajoi Rushing, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Louis A. Armstrong, Jr., an unmarried man,</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552648.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555048.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552648.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555048.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552648.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555048.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260552661</t>
+          <t>20260555323</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2787,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2802,24 +2842,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(s): Steven Phillip Parmenter And Sherri L.</t>
+          <t>Maria Del Rosario Medina Sanchez, an</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>203,841.97</t>
+          <t>49,941.45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1421 E KERRY LN</t>
+          <t>19040 N. Dinero Road</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2829,7 +2869,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85024</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2841,36 +2881,28 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>213-24-224</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
+          <t>Michael J. Aboud, a member of the State Bar</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(200) 751-6780</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
+          <t>(202) 506-7618</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>(s): Steven Phillip Parmenter And Sherri</t>
+          <t>Maria Del Rosario Medina Sanchez,</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>an</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -2878,32 +2910,32 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552661.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555323.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552661.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555323.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_apn, missing_auction_date</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552661.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555323.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260552665</t>
+          <t>20260555350</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2913,7 +2945,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2928,24 +2960,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Evelyn Kabage, an unmarried woman, and Paul F. Landsberg, a married man as his sole and separate</t>
+          <t>Christian Engineering &amp; Design Llc</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>100,000.00</t>
+          <t>255,000.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>19221 W Indian School Rd</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Litchfield Park</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2955,7 +2987,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85340</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2969,71 +3001,75 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>232-09-846</t>
+          <t>502-63</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(201) 801-5053</t>
+          <t>(202) 605-5535</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Evelyn Kabage, an unmarried</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>woman,</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Paul F. Landsberg, a married man as his sole and</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>separate</t>
+          <t>Llc</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552665.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555350.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552665.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555350.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552665.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555350.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260552691</t>
+          <t>20260555354</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3043,7 +3079,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3058,36 +3094,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jacquelyn Franco, a single woman</t>
+          <t>Humberto Suarez, a single man</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>191,468.00</t>
+          <t>215,000.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3099,30 +3119,34 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>139-30-071</t>
+          <t>302-02-144</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(201) 704-6221</t>
+          <t>(202) 605-5535</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Jacquelyn Franco, a single</t>
+          <t>Humberto Suarez, a single</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3130,32 +3154,32 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552691.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555354.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552691.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555354.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552691.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555354.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260552849</t>
+          <t>20260555362</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3165,7 +3189,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3180,36 +3204,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alejandro Valenzuela and Maria F. Alarcon, husband and wife</t>
+          <t>Maria C. Zavala, unmarried woman</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>527,946.00</t>
+          <t>357,500.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -3221,52 +3229,52 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>304-63-918</t>
+          <t>140-58-135</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(202) 208-8170</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
+          <t>(202) 605-5536</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>Maria C. Zavala, unmarried</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Valenzuela</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Maria F. Alarcon, husband and</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552849.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555362.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552849.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555362.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG24" t="n">
@@ -3274,14 +3282,14 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552849.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555362.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260552880</t>
+          <t>20260555364</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3291,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3304,22 +3312,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thor E. Erickson, an unmarried man</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25,000.00</t>
+          <t>185,000.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8804 S 10th Dr</t>
+          <t>1737 E. Starlight Way</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3329,7 +3341,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3343,52 +3355,2090 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>300-51-101</t>
+          <t>135-55-201</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 605-5536</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Thor E. Erickson, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260552880.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555364.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260552880.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555364.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555364.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260555366</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Safe Haven Sanctuary Llc, an Arizona limited liability company</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>300,000.00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>104-48-575</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(202) 605-5536</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Safe Haven Sanctuary Llc, an Arizona limited liability</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555366.pdf</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555366.pdf</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555366.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260555374</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pcc Construction and Inv. Llc, an Arizona limited liability company</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>200,000.00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9006 W Avalon Dr</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85037</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>102-24-644</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(202) 605-5537</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Pcc</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Inv. Llc, an Arizona limited liability</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555374.pdf</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555374.pdf</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555374.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260555377</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>David Galindo Perez, a single man</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>205,000.00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3135 W Berkeley Rd</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>108-26-051</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(202) 605-5537</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>David Galindo Perez, a single</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555377.pdf</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555377.pdf</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555377.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260555418</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Atlanta Ave Llc</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>215,000.00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1345 W. Mohave St</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85007</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>105-33-148</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(202) 605-5541</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Atlanta Ave</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Llc</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555418.pdf</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555418.pdf</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555418.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260555423</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>208,000.00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>154-08-039</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(202) 605-5542</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555423.pdf</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555423.pdf</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555423.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260555449</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Victoria D Claytor, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>195,000.00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>539 North Center St</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85201</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>137-25</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(202) 605-5544</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Victoria D Claytor, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555449.pdf</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555449.pdf</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555449.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260555452</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Carlos C Landin, an unmarried man, and Erika E Beltran, an unmarried</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>130,000.00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3530 W Abraham Ln</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>206-20-199</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(202) 605-5545</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Carlos C Landin, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>man,</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Erika E Beltran, an</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>unmarried</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555452.pdf</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555452.pdf</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555452.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260555594</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Justin E. Diede</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>285,000.00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 20618 N 29TH DRIVE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>85027</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>206-08-310</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Justin E.</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Diede</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555594.pdf</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555594.pdf</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555594.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260555653</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>152,021.00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>4422 E ANNETTE DR</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>215-12-083</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(201) 805-6771</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555653.pdf</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555653.pdf</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
           <t>ocr_used, missing_owner</t>
         </is>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG34" t="n">
         <v>75</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260552880.txt</t>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555653.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260555663</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>186,558.00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>4743 N 70TH DR</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85033</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>144-77-092</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>(200) 747-0605</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555663.pdf</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555663.pdf</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555663.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260555738</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>9,052,445.00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>or identifiable 2326 E Washington Street</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>85034</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>115-01</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(202) 400-8127</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555738.pdf</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555738.pdf</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555738.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260555748</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>9,052,445.00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>or identifiable 2312 E Washington Street</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>85034</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>115-01</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>appointed here qualifies as a Trustee</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>(202) 303-4795</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555748.pdf</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555748.pdf</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555748.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260555923</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>300,000.00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5105 WEST GELDING DRIVE</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>85306</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>(202) 403-8247</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555923.pdf</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555923.pdf</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555923.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260555924</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(s): Joseph D Domurat And Rosemary L</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>65,743.00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>10202 N 97TH DR APT B</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>85345</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>(200) 906-8118</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>(s): Joseph D Domurat And Rosemary</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555924.pdf</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555924.pdf</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555924.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260555926</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>(s): Jonathan Ramos, A Single Man</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>175,757.00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>102-20-665</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>(200) 747-9017</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>(s): Jonathan Ramos, A Single</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555926.pdf</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555926.pdf</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555926.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260555927</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>(s): Ricardo Valdez Jr, An Unmarried Man</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>445,496.00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5154 N 90TH DR</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>85305</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>102-12-587</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>(202) 402-9772</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>(s): Ricardo Valdez Jr, An Unmarried</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555927.pdf</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555927.pdf</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555927.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260555957</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>238,520.00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3001 WEST LAUREL LANE</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>85029</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>149-20-110</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc, dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>(201) 902-1385</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260555957.pdf</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260555957.pdf</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260555957.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="47" customWidth="1" min="25" max="25"/>
+    <col width="54" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="41" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="49" customWidth="1" min="32" max="32"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260556035</t>
+          <t>20260558742</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,26 +650,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>(s): Roberta Manriquez, A Married Woman</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>133,000.00</t>
+          <t>900,000.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3840 W BETTY ELYSE LN</t>
+          <t>9702 W BRANDING IRON DRIVE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -679,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85053</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,67 +689,59 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>207-15-058</t>
+          <t>230-09-020</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(200) 401-8549</t>
+          <t>(202) 300-4478</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>(s): Roberta Manriquez, A Married</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Woman</t>
-        </is>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260556035.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260558742.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260556035.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260558742.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260556035.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260558742.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260556124</t>
+          <t>20260558863</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -763,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,18 +768,18 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>422,660.00</t>
+          <t>417,302.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25449 W GRAHAM TRAIL</t>
+          <t>16720 N 182ND LANE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -801,7 +789,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85388</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -815,23 +803,23 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>504-43-786</t>
+          <t>502-02-4108</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 504-4006</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -842,12 +830,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260556124.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260558863.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260556124.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260558863.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -860,14 +848,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260556124.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260558863.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260556387</t>
+          <t>20260559089</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -877,7 +865,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -890,22 +878,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Israel Lira Sanchez (a single man)</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>51,200.00</t>
+          <t>358,388.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>or identifiable location: 3635 W CORTEZ ST</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85029</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -917,67 +917,59 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>506-36</t>
+          <t>149-32-557</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 605-5638</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Israel Lira Sanchez (a single</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>man)</t>
-        </is>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260556387.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559089.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260556387.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559089.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260556387.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559089.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260557146</t>
+          <t>20260559225</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -987,7 +979,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1002,24 +994,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nilda Franco, an unmarried woman</t>
+          <t>in favor of Bank Of</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2,539,450.00</t>
+          <t>527,174.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6321 N Camelback Manor Dr</t>
+          <t>6741 SOUTH STANLEY PLACE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paradise Valley</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1029,7 +1021,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85253</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1043,30 +1035,38 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>169-27</t>
+          <t>301-48-487</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>before a trustee’s deed upon sale will be issued</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(202) 401-8646</t>
+          <t>(200) 911-6614</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2012-03-16</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Nilda Franco, an unmarried</t>
+          <t>in favor of Bank</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>Of</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -1074,32 +1074,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557146.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559225.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557146.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559225.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557146.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559225.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260557153</t>
+          <t>20260559435</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1122,26 +1122,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rigo’s Construction Llc, an Arizona limited liability</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>125,000.00</t>
+          <t>242,526.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4005 N. Pinnacle Hills Circle</t>
+          <t>or identifiable location: 11202 W OREGON AVE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Youngtown</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1151,7 +1147,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85207</t>
+          <t>85363</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1165,67 +1161,59 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>506-44</t>
+          <t>142-64-232</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Statewide Foreclosure Services, Inc., a</t>
+          <t>before a trustee’s deed will be issued for covered</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(202) 601-4523</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Rigo’s Construction Llc, an Arizona limited</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>liability</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557153.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559435.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557153.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559435.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557153.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559435.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260557410</t>
+          <t>20260559468</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1235,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1248,38 +1236,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Leah C Delozier</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>510,400.00</t>
+          <t>20,750.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>or IDENTIFIABLE LOCATION: 5443 E SKINNER DR</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Cave Creek</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85331</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1291,67 +1259,63 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>211-42</t>
+          <t>144-01-399</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Leah C</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Delozier</t>
-        </is>
-      </c>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557410.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559468.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557410.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559468.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557410.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559468.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260557565</t>
+          <t>20260559476</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1361,7 +1325,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1374,26 +1338,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Rudy Carrillo, Doris Carrillo, husband and wife</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>136,900.00</t>
+          <t>60,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2027 W Osborn Road</t>
+          <t>630 W GALVESTON ST</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1403,7 +1363,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85015</t>
+          <t>85233</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1417,63 +1377,63 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>110-25-013</t>
+          <t>302-83</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(200) 759-6848</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Rudy Carrillo, Doris Carrillo,</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>husband</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557565.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559476.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557565.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559476.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557565.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559476.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260557574</t>
+          <t>20260559501</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1483,7 +1443,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1496,38 +1456,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>William Anguiz, unmarried man, and Manuel Anguiz, unmarried man</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>396,583.00</t>
+          <t>368,207.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1539,71 +1479,63 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>140-25-126</t>
+          <t>142-88-752</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(200) 751-0427</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>William Anguiz, unmarried</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>man,</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Manuel Anguiz, unmarried</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557574.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559501.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557574.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559501.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557574.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559501.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260557591</t>
+          <t>20260559562</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1613,7 +1545,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1626,26 +1558,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Andrea Williams, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>380,101.00</t>
+          <t>224,852.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>20113 N 259TH LN</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1655,7 +1583,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1669,63 +1597,59 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>158-06-580</t>
+          <t>503-85-108</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(202) 207-9103</t>
+          <t>(201) 504-6039</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Andrea Williams, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557591.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559562.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557591.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559562.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557591.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559562.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260557612</t>
+          <t>20260559703</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1735,7 +1659,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1750,24 +1674,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kathleen Reynolds, a married woman as her sole and separate property</t>
+          <t>Christopher Allen and Patrina Wilson, husband and wife</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>104,069.00</t>
+          <t>269,440.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60 East 14th Street</t>
+          <t>8917 W Jefferson St</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Tolleson</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1777,7 +1701,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85201</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1791,67 +1715,75 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>136-22</t>
+          <t>101-12-711</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(200) 747-0583</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
+          <t>(202) 003-4953</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Kathleen Reynolds, a married woman as her</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>sole</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>separate</t>
+          <t>Patrina Wilson, husband and</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>wife</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557612.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559703.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557612.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559703.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557612.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559703.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260557624</t>
+          <t>20260559893</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1861,7 +1793,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1874,26 +1806,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>(s): James R Long, Nantana Long</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>100,000.00</t>
+          <t>339,733.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>960 E 7TH ST</t>
+          <t>2649 E LIBBY STREET</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1903,7 +1831,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85203</t>
+          <t>85032</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1917,67 +1845,59 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>137-08-036</t>
+          <t>214-06-090</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(200) 759-2672</t>
+          <t>(202) 110-0075</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>(s): James R Long, Nantana</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557624.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559893.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557624.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559893.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557624.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559893.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260557730</t>
+          <t>20260559970</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1987,7 +1907,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2002,24 +1922,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(s): John Adams and Futami O Adams, husband and wife</t>
+          <t>(s): Shahin Dabestani And Asal Rafie</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>235,966.00</t>
+          <t>1,575,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16363 W POST DR</t>
+          <t>13955 E YUCCA ST</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2029,7 +1949,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85388</t>
+          <t>85259</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2043,7 +1963,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>509-04-317</t>
+          <t>217-69-028</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2054,44 +1974,36 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(201) 803-2431</t>
+          <t>(200) 738-8048</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>(s): John</t>
+          <t>(s): Shahin Dabestani And Asal</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Adams</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Futami O Adams, husband and</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>Rafie</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557730.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559970.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557730.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559970.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2104,14 +2016,14 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557730.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559970.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260557902</t>
+          <t>20260559984</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2121,7 +2033,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2136,24 +2048,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Matthew Shapiro, an unmarried man</t>
+          <t>(s): James Galvan, an unmarried man</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>245,471.00</t>
+          <t>190,000.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>2548 W OSAGE CIR</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2163,7 +2075,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85202</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2177,25 +2089,29 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>200-13-307</t>
+          <t>302-05-017</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(201) 909-2413</t>
+          <t>(202) 107-9693</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Matthew Shapiro, an unmarried</t>
+          <t>(s): James Galvan, an unmarried</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2208,32 +2124,32 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557902.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559984.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557902.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559984.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557902.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559984.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260557909</t>
+          <t>20260559998</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2243,7 +2159,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2258,24 +2174,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabriel Miranda Brito and Rubisel Garcia Villamontes, husband and wife</t>
+          <t>(s): Josias E. Melendez, an unmarried man</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>316,800.00</t>
+          <t>215,033.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11353 W Ruth Ave</t>
+          <t>3022 W SANDS DRIVE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2285,7 +2201,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85345</t>
+          <t>85027</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2299,71 +2215,67 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>142-73-705</t>
+          <t>206-04-302</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 206-5171</t>
+          <t>(201) 808-0881</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Gabriel Miranda</t>
+          <t>(s): Josias E. Melendez, an unmarried</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Brito</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Rubisel Garcia Villamontes, husband and</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557909.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559998.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557909.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559998.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557909.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559998.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260557926</t>
+          <t>20260560000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2373,7 +2285,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2388,24 +2300,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vean Simon Iii, a married man</t>
+          <t>(s): Perla Janette Rios Soto, a married woman as her sole</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>708,689.00</t>
+          <t>139,918.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2312 W Sunrise Place</t>
+          <t>3010 W ALMERIA RD</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2415,7 +2327,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85248</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2429,30 +2341,34 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>303-55-699</t>
+          <t>108-27</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(202) 009-9098</t>
+          <t>(201) 705-1864</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Vean Simon Iii, a married</t>
+          <t>(s): Perla Janette Rios Soto, a married woman as her</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>sole</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
@@ -2460,32 +2376,32 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557926.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560000.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557926.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560000.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557926.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560000.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260557941</t>
+          <t>20260560054</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2495,7 +2411,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2510,19 +2426,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Keristian Denise Edwards and Cory Darnell Dugar, wife and husband</t>
+          <t>Dorem, Llc, a California Limited Liability Company</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>354,162.00</t>
+          <t>468,750.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>2801 East Paradise Lane</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2537,7 +2453,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85032</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2551,18 +2467,14 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>104-58-511</t>
+          <t>214-39</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>/Successor Trustee, is regulated by and</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(202) 303-9203</t>
+          <t>(200) 760-9281</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2573,53 +2485,45 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Keristian Denise</t>
+          <t>Dorem, Llc, a California Limited Liability</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Edwards</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Cory Darnell Dugar, wife and</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>husband</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260557941.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560054.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260557941.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560054.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260557941.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560054.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260558214</t>
+          <t>20260560063</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2629,7 +2533,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2644,24 +2548,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>(s): Michael Eastman and Melissa Eastman, husband and</t>
+          <t>John S Dignoti</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>292,500.00</t>
+          <t>393,680.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10853 W ADAM AVE</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2671,7 +2575,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85373</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2685,75 +2589,63 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>200-12-585</t>
+          <t>149-44-122</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(201) 904-4884</t>
+          <t>(200) 744-8636</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>(s): Michael</t>
+          <t>John S</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Eastman</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Melissa Eastman, husband</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
+          <t>Dignoti</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260558214.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560063.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260558214.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560063.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260558214.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560063.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260558431</t>
+          <t>20260560148</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2763,7 +2655,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2776,38 +2668,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>J&amp;M Brothers Llc, an Arizona limited lability company</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>260,000.00</t>
+          <t>352,500.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>11515 N 91st St Unit 209</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Scottsdale</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>85260</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2819,56 +2691,2172 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>217-48-511</t>
+          <t>206-13-007</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 505-9680</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>J&amp;M Brothers Llc, an Arizona limited lability</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260558431.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560148.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260558431.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560148.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560148.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260560391</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Richard Allan Diaz</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>176,000.00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 2010 N 17th Ave</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>85007</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>111-06-181</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(470) 321-7112</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Richard Allan</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Diaz</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560391.pdf</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560391.pdf</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560391.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260560393</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>David Galindo Perez, a single man</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>205,000.00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3135 W Berkeley Rd</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>108-26-051</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(202) 605-6039</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>David Galindo Perez, a single</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560393.pdf</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560393.pdf</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560393.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260560480</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jose E. Martinez and Ruth P. Martinez, husband and wife as joint tenants with right of survivorship</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>78,700.00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>500-18-079</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(201) 602-6218</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Jose E.</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Ruth P. Martinez, husband and wife as joint tenants with right of</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>survivorship</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560480.pdf</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560480.pdf</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560480.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260560536</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>John O Duran, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>304,000.00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>125 S Alberta Cir</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85206</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>140-29-282</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>(202) 010-8249</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>John O Duran, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560536.pdf</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560536.pdf</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560536.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260560589</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>49,596.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>231-03-016</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560589.pdf</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560589.pdf</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560589.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260560613</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>148,000.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>215-66-270</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560613.pdf</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560613.pdf</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560613.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260560730</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kays Homecare Llc</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>450,000.00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>721 1 W ST. CHARLES AVE</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Laveen</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85339</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>304-19-651</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(983) 626-1213</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Kays Homecare</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Llc</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560730.pdf</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560730.pdf</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
-      <c r="AG19" t="n">
+      <c r="AG26" t="n">
         <v>90</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260558431.txt</t>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560730.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260560738</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>375,000.00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4623 WEST COUNTRY GABLES DRIVE</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85306</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>207-30</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(202) 000-6938</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560738.pdf</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560738.pdf</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560738.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260560779</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>250,000.00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6112 W PARKSIDE LN</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85310</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>200-02</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(202) 304-4790</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560779.pdf</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560779.pdf</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560779.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260560783</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>100,000.00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1108 EAST CALDWELL STREET</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85042</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(200) 753-2429</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560783.pdf</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560783.pdf</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560783.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260560795</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>484,030.00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>18436 W JESSIE LN</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85387</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(202) 302-4947</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560795.pdf</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560795.pdf</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560795.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260560838</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>394,650.00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5396 N 82ND AVE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85303</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(201) 909-0958</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560838.pdf</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560838.pdf</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560838.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260560860</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>540,038.00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>37628 N 22ND STREET</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85086</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(202) 502-2909</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560860.pdf</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560860.pdf</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560860.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260560871</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>222,000.00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10960 E MONTE AVE, #214</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>85209</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>(201) 405-7140</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560871.pdf</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560871.pdf</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560871.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260560983</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(s): Saul Alejandro Rojas Valenzuela And</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>353,469.00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>25282 W HIDALGO AVE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>504-41-749</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(262) 403-8512</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>(s): Saul Alejandro Rojas Valenzuela</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>And</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560983.pdf</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560983.pdf</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560983.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260560985</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>(s): Anthony Coronado Lopez, An</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>397,232.00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5425 W PIERSON ST</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85031</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>144-53-051</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>(202) 405-1657</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>(s): Anthony Coronado Lopez,</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>An</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560985.pdf</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560985.pdf</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560985.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260560987</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>(s): Timothy J Flynn Jr, A Married Man As</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>171,950.00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1731 E ALAMEDA DRIVE</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Tempe</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>85282</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>133-33-3839</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(201) 609-0981</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>(s): Timothy J Flynn Jr, A Married Man</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560987.pdf</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560987.pdf</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560987.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260560988</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>(s): Julio Cesar Acosta, a single man</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>170,300.00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1942 N 69TH AVE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>85035</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>102-76-142</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>(202) 106-9816</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>(s): Julio Cesar Acosta, a single</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560988.pdf</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560988.pdf</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560988.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH37"/>
+  <dimension ref="A1:AH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="54" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="60" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="42" customWidth="1" min="32" max="32"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260558742</t>
+          <t>20260561254</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -654,18 +654,18 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>900,000.00</t>
+          <t>95,733.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9702 W BRANDING IRON DRIVE</t>
+          <t>8509 W GLENROSA AVE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>85037</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -689,23 +689,23 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>230-09-020</t>
+          <t>102-74-029</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 300-4478</t>
+          <t>(201) 600-9948</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -716,12 +716,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260558742.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260561254.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260558742.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260561254.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -734,14 +734,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260558742.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260561254.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260558863</t>
+          <t>20260561606</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -768,18 +768,18 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>417,302.00</t>
+          <t>156,000.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16720 N 182ND LANE</t>
+          <t>5016 N 86TH AVE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85388</t>
+          <t>85305</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -801,25 +801,21 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>502-02-4108</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>herein qualifies as Trustee of the Ti Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(844) 693-4761</t>
+          <t>(200) 758-0740</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -830,32 +826,32 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260558863.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260561606.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260558863.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260561606.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260558863.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260561606.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260559089</t>
+          <t>20260561670</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -865,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -882,18 +878,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>358,388.00</t>
+          <t>553,006.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>or identifiable location: 3635 W CORTEZ ST</t>
+          <t>1171 EAST BELL DE MAR DRIVE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -903,7 +899,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -915,25 +911,21 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>149-32-557</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(200) 755-3587</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -944,32 +936,32 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559089.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260561670.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559089.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260561670.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559089.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260561670.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260559225</t>
+          <t>20260561712</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,7 +971,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -992,26 +984,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>in favor of Bank Of</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>527,174.53</t>
+          <t>217,745.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6741 SOUTH STANLEY PLACE</t>
+          <t>1520 SOUTH CHESTNUT CIRCLE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1021,7 +1009,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1033,73 +1021,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>301-48-487</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>before a trustee’s deed upon sale will be issued</t>
+          <t>Sale Or iF You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(200) 911-6614</t>
+          <t>(202) 208-2570</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2012-03-16</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>in favor of Bank</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Of</t>
-        </is>
-      </c>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559225.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260561712.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559225.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260561712.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559225.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260561712.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260559435</t>
+          <t>20260561901</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1109,7 +1081,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1126,18 +1098,18 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>242,526.00</t>
+          <t>9,596,269.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>or identifiable location: 11202 W OREGON AVE</t>
+          <t>312 E Windsor Ave</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Youngtown</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1147,7 +1119,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85363</t>
+          <t>85004</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,25 +1133,21 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>142-64-232</t>
+          <t>118-45-396</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>before a trustee’s deed will be issued for covered</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
+          <t>(202) 301-8490</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -1188,32 +1156,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559435.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260561901.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559435.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260561901.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_auction_date</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559435.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260561901.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260559468</t>
+          <t>20260562180</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1191,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1240,14 +1208,30 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20,750.00</t>
+          <t>275,900.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>or identifiable location: 24054 N 165th Dr</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85387</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1259,30 +1243,26 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>144-01-399</t>
+          <t>503-74-888</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>before a trustee’s deed will be issued for covered</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1290,32 +1270,32 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559468.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562180.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559468.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562180.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559468.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562180.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260559476</t>
+          <t>20260562211</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1325,7 +1305,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1342,30 +1322,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>60,000.00</t>
+          <t>135,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>630 W GALVESTON ST</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Gilbert</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>85233</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1377,30 +1341,26 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>302-83</t>
+          <t>200-82-591</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(200) 743-7308</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1408,32 +1368,32 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559476.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562211.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559476.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562211.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559476.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562211.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260559501</t>
+          <t>20260562246</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1443,7 +1403,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1460,14 +1420,30 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>368,207.00</t>
+          <t>196,000.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>248 EAST HEATHER AVENUE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Gilbert</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85234</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1479,30 +1455,26 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>142-88-752</t>
+          <t>304-12-150</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(200) 706-9327</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1510,32 +1482,32 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559501.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562246.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559501.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562246.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559501.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562246.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260559562</t>
+          <t>20260562346</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1545,7 +1517,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1558,22 +1530,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Marshall G. Smith</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>224,852.00</t>
+          <t>222,300.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20113 N 259TH LN</t>
+          <t>or IDENTIFIABLE LOCATION: 32305 N. 224TH DRIVE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Wittmann</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1583,7 +1559,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>85361</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1597,59 +1573,67 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>503-85-108</t>
+          <t>503-39</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(201) 504-6039</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Marshall G.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559562.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562346.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559562.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562346.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559562.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562346.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260559703</t>
+          <t>20260562365</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1659,7 +1643,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1672,26 +1656,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Christopher Allen and Patrina Wilson, husband and wife</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>269,440.00</t>
+          <t>366,400.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8917 W Jefferson St</t>
+          <t>16935 W CENTRAL ST</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tolleson</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1701,7 +1681,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>85388</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1713,77 +1693,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>101-12-711</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>herein qualifies as Trustee of the T: eed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(202) 003-4953</t>
+          <t>(202) 200-3170</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Christopher</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Allen</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Patrina Wilson, husband and</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559703.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562365.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559703.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562365.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559703.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562365.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260559893</t>
+          <t>20260562395</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1793,7 +1753,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1810,18 +1770,18 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>339,733.00</t>
+          <t>604,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2649 E LIBBY STREET</t>
+          <t>31 INNER CIRCLE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1831,7 +1791,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85032</t>
+          <t>85258</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1845,18 +1805,18 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>214-06-090</t>
+          <t>174-08-040</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(202) 110-0075</t>
+          <t>(202) 106-5250</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1872,12 +1832,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559893.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562395.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559893.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562395.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1890,14 +1850,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559893.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562395.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260559970</t>
+          <t>20260562398</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1907,7 +1867,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1920,26 +1880,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>(s): Shahin Dabestani And Asal Rafie</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1,575,000.00</t>
+          <t>315,425.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13955 E YUCCA ST</t>
+          <t>15247 N 52ND AVE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1949,7 +1905,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85259</t>
+          <t>85306</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1961,69 +1917,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>217-69-028</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>herein qualifies as Trustee of the Tru</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(200) 738-8048</t>
+          <t>(202) 201-3663</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>(s): Shahin Dabestani And Asal</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Rafie</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559970.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562398.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559970.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562398.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559970.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562398.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260559984</t>
+          <t>20260562444</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2033,7 +1977,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2048,24 +1992,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(s): James Galvan, an unmarried man</t>
+          <t>(s): Michelle Diaz, a single woman</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>190,000.00</t>
+          <t>299,669.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2548 W OSAGE CIR</t>
+          <t>3906 E TURLEY ST</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2075,7 +2019,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85202</t>
+          <t>85295</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2089,7 +2033,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>302-05-017</t>
+          <t>313-22-099</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2100,7 +2044,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 107-9693</t>
+          <t>(201) 800-5334</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2111,12 +2055,12 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>(s): James Galvan, an unmarried</t>
+          <t>(s): Michelle Diaz, a single</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -2124,12 +2068,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559984.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562444.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559984.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562444.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2142,14 +2086,14 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559984.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562444.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260559998</t>
+          <t>20260562462</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2159,7 +2103,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2172,26 +2116,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>(s): Josias E. Melendez, an unmarried man</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>215,033.00</t>
+          <t>570,250.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3022 W SANDS DRIVE</t>
+          <t>or identifiable location: 3236 West Ansell Road</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Laveen</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2201,7 +2141,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85027</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2215,67 +2155,63 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>206-04-302</t>
+          <t>300-06-150</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(201) 808-0881</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>(s): Josias E. Melendez, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260559998.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562462.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260559998.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562462.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260559998.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562462.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260560000</t>
+          <t>20260562463</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2285,7 +2221,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2298,21 +2234,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>(s): Perla Janette Rios Soto, a married woman as her sole</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>139,918.00</t>
+          <t>392,755.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3010 W ALMERIA RD</t>
+          <t>3032 N 45th Dr</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2327,7 +2259,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>85031</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2341,67 +2273,63 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>108-27</t>
+          <t>142-74-017</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(201) 705-1864</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>(s): Perla Janette Rios Soto, a married woman as her</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>sole</t>
-        </is>
-      </c>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560000.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562463.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560000.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562463.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560000.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562463.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260560054</t>
+          <t>20260562689</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2411,7 +2339,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2426,24 +2354,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dorem, Llc, a California Limited Liability Company</t>
+          <t>(s): Jerry Nelson, An Unmarried Man</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>468,750.00</t>
+          <t>168,000.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2801 East Paradise Lane</t>
+          <t>3638 W MICHELLE DR</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2453,7 +2381,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85032</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2467,30 +2395,34 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>214-39</t>
+          <t>207-20-021</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(200) 760-9281</t>
+          <t>(200) 601-9913</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Dorem, Llc, a California Limited Liability</t>
+          <t>(s): Jerry Nelson, An Unmarried</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2498,32 +2430,32 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560054.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562689.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560054.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562689.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560054.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562689.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260560063</t>
+          <t>20260562861</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2533,7 +2465,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2548,24 +2480,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>John S Dignoti</t>
+          <t>Monique Pellam</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>393,680.00</t>
+          <t>234,617.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>or IDENTIFIABLE LOCATION: 20704 W LEGEND TRAIL</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2575,7 +2507,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2589,30 +2521,34 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>149-44-122</t>
+          <t>502-80-746</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(200) 744-8636</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>John S</t>
+          <t>Monique</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Dignoti</t>
+          <t>Pellam</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr"/>
@@ -2620,32 +2556,32 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560063.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562861.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560063.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562861.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560063.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562861.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260560148</t>
+          <t>20260562885</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2655,7 +2591,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2668,18 +2604,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Inas Al Obaidi, an unmarried woman</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>352,500.00</t>
+          <t>401,591.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19323 N 75th Dr</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2691,63 +2647,63 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>206-13-007</t>
+          <t>200-30-018</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Prestige Default Services, Llc</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(200) 728-4657</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2021-03-26</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Inas Al Obaidi, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560148.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562885.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560148.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562885.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560148.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562885.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260560391</t>
+          <t>20260562988</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2757,7 +2713,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2770,21 +2726,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Richard Allan Diaz</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>176,000.00</t>
+          <t>524,400.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 2010 N 17th Ave</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2799,7 +2751,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85007</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2813,63 +2765,59 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>111-06-181</t>
+          <t>160-08-036</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(470) 321-7112</t>
+          <t>(202) 306-5095</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Richard Allan</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Diaz</t>
-        </is>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560391.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260562988.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560391.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260562988.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560391.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260562988.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260560393</t>
+          <t>20260563008</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2879,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,19 +2842,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>David Galindo Perez, a single man</t>
+          <t>Manuel Amado Villa Sr and Herlinda Ronquillo Villa, husband and wife as community property</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>205,000.00</t>
+          <t>107,500.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3135 W Berkeley Rd</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2921,7 +2869,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2935,47 +2883,55 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>108-26-051</t>
+          <t>122-91-053</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(202) 605-6039</t>
+          <t>(202) 002-5148</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>David Galindo Perez, a single</t>
+          <t>Manuel Amado Villa</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Herlinda Ronquillo Villa, husband and wife as community</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560393.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563008.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560393.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563008.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2988,14 +2944,14 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560393.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563008.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260560480</t>
+          <t>20260563017</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3005,7 +2961,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3020,13 +2976,13 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jose E. Martinez and Ruth P. Martinez, husband and wife as joint tenants with right of survivorship</t>
+          <t>Patrick Randall Ming and Victoria L Mendoza, husband and wife</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>78,700.00</t>
+          <t>512,636.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3061,14 +3017,18 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>500-18-079</t>
+          <t>502-92-633</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(201) 602-6218</t>
+          <t>(202) 102-2196</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3079,53 +3039,53 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Jose E.</t>
+          <t>Patrick Randall</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Ming</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Ruth P. Martinez, husband and wife as joint tenants with right of</t>
+          <t>Victoria L Mendoza, husband and</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>survivorship</t>
+          <t>wife</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560480.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563017.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560480.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563017.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560480.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563017.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260560536</t>
+          <t>20260563103</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3135,7 +3095,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3148,26 +3108,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>John O Duran, an unmarried man</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>304,000.00</t>
+          <t>275,000.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>125 S Alberta Cir</t>
+          <t>12007 S 184TH AVE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Goodyear</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3177,7 +3133,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>85338</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3189,65 +3145,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>140-29-282</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(202) 010-8249</t>
+          <t>(202) 205-2318</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>John O Duran, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560536.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563103.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560536.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563103.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560536.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563103.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260560589</t>
+          <t>20260563126</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3257,7 +3205,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3270,18 +3218,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Guadalupe Diaz, a single woman and Socorro Diaz and Ramon Diaz, wife and</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>49,596.00</t>
+          <t>171,448.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>306 North 3rd Avenue</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -3293,63 +3261,71 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>231-03-016</t>
+          <t>500-16-114</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2021-10-01</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Guadalupe Diaz, a single</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Socorro Diaz and Ramon Diaz, wife</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560589.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563126.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560589.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563126.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560589.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563126.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260560613</t>
+          <t>20260563129</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3359,7 +3335,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3372,18 +3348,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Guadalupe Diaz, a single woman and Socorro Diaz and Ramon Diaz, wife and</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>148,000.00</t>
+          <t>171,448.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>306 North 3rd Avenue</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3395,63 +3391,71 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>215-66-270</t>
+          <t>500-16-114</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>2027-01-12</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Guadalupe Diaz, a single</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Socorro Diaz and Ramon Diaz, wife</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560613.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563129.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560613.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563129.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560613.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563129.txt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260560730</t>
+          <t>20260563193</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3461,7 +3465,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3474,21 +3478,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Kays Homecare Llc</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>450,000.00</t>
+          <t>440,857.00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>721 1 W ST. CHARLES AVE</t>
+          <t>6418 W MAGDALENA LN</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3517,63 +3517,59 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>304-19-651</t>
+          <t>300-09-141</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Mtc Finangra ba Trustee Corps</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>(983) 626-1213</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>(202) 203-7523</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Kays Homecare</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Llc</t>
-        </is>
-      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560730.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563193.pdf</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560730.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563193.pdf</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560730.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563193.txt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260560738</t>
+          <t>20260563211</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3583,7 +3579,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3596,17 +3592,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Alberto Silverio Alvarez, an unmarried man, and Stacy Fentanes, an unmarried</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>375,000.00</t>
+          <t>294,566.00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4623 WEST COUNTRY GABLES DRIVE</t>
+          <t>6613 North 62nd Avenue</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3635,59 +3635,71 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>207-30</t>
+          <t>144-12-030</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>(202) 000-6938</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Alberto Silverio Alvarez, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>man,</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Stacy Fentanes, an</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>unmarried</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560738.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563211.pdf</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560738.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563211.pdf</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560738.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563211.txt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260560779</t>
+          <t>20260563219</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3697,7 +3709,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3712,24 +3724,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(s)</t>
+          <t>Cruz M. Holguin and Jo Marie Holguin, husband and wife as joint tenants with right of survivorship</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>250,000.00</t>
+          <t>110,000.00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6112 W PARKSIDE LN</t>
+          <t>4220 E Ponca St</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3739,7 +3751,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>85310</t>
+          <t>85044</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3753,63 +3765,67 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>200-02</t>
+          <t>301-55-666</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>(202) 304-4790</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
+          <t>(200) 760-3591</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>(s)</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+          <t>Cruz M.</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Holguin</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Jo Marie Holguin, husband and wife as joint tenants with right of</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>survivorship</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560779.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563219.pdf</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560779.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563219.pdf</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560779.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563219.txt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260560783</t>
+          <t>20260563239</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3819,7 +3835,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3832,17 +3848,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Maria D. Galvan, a single woman</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>100,000.00</t>
+          <t>108,007.00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1108 EAST CALDWELL STREET</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3857,7 +3877,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>85042</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3869,57 +3889,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>137-21-152</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>(200) 753-2429</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>2027-01-12</t>
-        </is>
-      </c>
+          <t>(200) 752-9396</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Maria D. Galvan, a single</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560783.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563239.pdf</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560783.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563239.pdf</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560783.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563239.txt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260560795</t>
+          <t>20260563252</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3929,7 +3953,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3942,22 +3966,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Thacianne Kayitesi</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>484,030.00</t>
+          <t>442,500.00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18436 W JESSIE LN</t>
+          <t>or IDENTIFIABLE LOCATION: 9410 W MEADOWBROOK AVE</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3967,7 +3995,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85037</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3979,57 +4007,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>102-25-130</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>(202) 302-4947</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Thacianne</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Kayitesi</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560795.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563252.pdf</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560795.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563252.pdf</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560795.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563252.txt</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260560838</t>
+          <t>20260563260</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4039,7 +4079,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4052,22 +4092,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Oanh Huynh</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>394,650.00</t>
+          <t>702</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5396 N 82ND AVE</t>
+          <t>or IDENTIFIABLE LOCATION: 5702 N LESLIE CT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Litchfield Park</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4077,7 +4121,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>85303</t>
+          <t>85340</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4089,16 +4133,20 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>508-12-110</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>(201) 909-0958</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4107,39 +4155,47 @@
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Oanh</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Huynh</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560838.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563260.pdf</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560838.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563260.pdf</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560838.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563260.txt</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260560860</t>
+          <t>20260563343</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4149,7 +4205,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4166,18 +4222,18 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>540,038.00</t>
+          <t>461,600.00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>37628 N 22ND STREET</t>
+          <t>10315 E KINETIC DR</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4187,7 +4243,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>85086</t>
+          <t>85212</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4199,21 +4255,25 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>304-50-562</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>( inancial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>(202) 502-2909</t>
+          <t>(202) 202-0050</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -4224,639 +4284,25 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560860.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563343.pdf</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560860.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563343.pdf</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560860.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20260560871</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>222,000.00</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>10960 E MONTE AVE, #214</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>85209</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>(201) 405-7140</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560871.pdf</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560871.pdf</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560871.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260560983</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>(s): Saul Alejandro Rojas Valenzuela And</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>353,469.00</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>25282 W HIDALGO AVE</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Buckeye</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>504-41-749</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>(262) 403-8512</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>(s): Saul Alejandro Rojas Valenzuela</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>And</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560983.pdf</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560983.pdf</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560983.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>20260560985</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>(s): Anthony Coronado Lopez, An</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>397,232.00</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>5425 W PIERSON ST</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>85031</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>144-53-051</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>(202) 405-1657</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>(s): Anthony Coronado Lopez,</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>An</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560985.pdf</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560985.pdf</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560985.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>20260560987</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>(s): Timothy J Flynn Jr, A Married Man As</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>171,950.00</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>1731 E ALAMEDA DRIVE</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Tempe</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>85282</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>133-33-3839</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>(201) 609-0981</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>(s): Timothy J Flynn Jr, A Married Man</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560987.pdf</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560987.pdf</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560987.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>20260560988</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>(s): Julio Cesar Acosta, a single man</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>170,300.00</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>1942 N 69TH AVE</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>85035</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>102-76-142</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>(202) 106-9816</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>(s): Julio Cesar Acosta, a single</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260560988.pdf</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260560988.pdf</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>ocr_used</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260560988.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563343.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,20 +413,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -436,20 +436,20 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="48" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +621,3484 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>raw_text_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260563857</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>— unomvatoocimn” Julia Owner, Llc</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>75,270,000.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>134-09</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bryan Cave Leighton Paisner Llp</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(202) 111-4219</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>— unomvatoocimn” Julia Owner,</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Llc</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563857.pdf</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563857.pdf</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563857.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260563862</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Azura Owner, Llc</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>73,390,000.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>149-17-151</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bryan Cave Leighton Paisner Llp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(202) 204-6763</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Azura Owner,</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Llc</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563862.pdf</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563862.pdf</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563862.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260563983</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>374,440.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>or identifiable location: 3790 W BARCELONA DR</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85226</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>308-06-900</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563983.pdf</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563983.pdf</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563983.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260564000</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>432,162.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>or identifiable location: 3392 S 180TH AVE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Goodyear</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>502-48-724</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>before a trustee’s deed will be issued</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564000.pdf</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564000.pdf</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564000.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260564019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>See Schedule “1”</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>15,395.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15620 North Clubgate Drive</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85254</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>sale or if you have an objection to the trustee sale, you must</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(702) 304-7509</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>See Schedule</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>“1”</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564019.pdf</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564019.pdf</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564019.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260564032</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>174,699.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>or identifiable location: 651 N MAPLE ST</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85226</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>308-03-326</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564032.pdf</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564032.pdf</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564032.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260564037</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>244,496.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>or identifiable location: 14854 NORTH 36TH DRIVE</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85053</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>207-10-489</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564037.pdf</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564037.pdf</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564037.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260564293</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>458,541.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>or identifiable location: 2502 E HOPI AVE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85204</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>140-60-168</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564293.pdf</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564293.pdf</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564293.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260564308</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>438,109.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>or identifiable location: 21254 W ALMERIA RD</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85396</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>502-61-153</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(202) 507-0197</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564308.pdf</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564308.pdf</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564308.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260564637</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>296,000.00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>134-47-135</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Fiqancial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(202) 202-0573</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564637.pdf</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564637.pdf</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564637.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260565020</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Eduardo Morgan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>225,000.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3707 East Southern Avenue</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85206</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>504-57-432</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Morgan</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565020.pdf</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565020.pdf</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565020.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260565021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rattan Mansaor Marqus and Dalya Waleed Jameel, husband and wife, 6517 West</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>560,500.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6517 West Red Fox Road</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85083</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>201-28-295</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Rattan Mansaor</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Marqus</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Dalya Waleed Jameel, husband and wife, 6517</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565021.pdf</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565021.pdf</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565021.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260565033</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Patrick Kelly</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>327,000.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 12629 N 28TH WAY</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>166-05-381</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565033.pdf</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565033.pdf</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565033.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260565034</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Zeb Hanks Fullmer, a married man, as his Sole and Separate Property, 1460</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>480,000.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22948 East Desert Spoon Drive</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Queen Creek</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>314-11-431</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Zeb Hanks Fullmer, a married man, as his</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Sole</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Separate Property,</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565034.pdf</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565034.pdf</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565034.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260565035</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Karl Forsthoefel, a single person, 5005 East Adobe Street, Mesa, Az 85205</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>347,999.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5005 East Adobe Street</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85205</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>140-16-021</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Karl Forsthoefel, a single person, 5005 East Adobe Street, Mesa, Az</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>85205</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565035.pdf</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565035.pdf</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565035.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260565036</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Richard D. Howell and Diane N. Howell, husband and wife, 15268 North 63rd</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>187,000.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15268 North 63rd Drive</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85306</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>231-07-988</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Richard D.</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Howell</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Diane N. Howell, husband and wife, 15268 North</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>63rd</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565036.pdf</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565036.pdf</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565036.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260565054</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Danienne Johnson, an unmarried woman, 1024 East Frye Road Unit 1100, Phoenix</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>280,000.00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1024 East Frye Road Unit 1100</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85048</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>300-96-645</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Danienne Johnson, an unmarried woman, 1024 East Frye Road Unit 1100,</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565054.pdf</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565054.pdf</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565054.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260565435</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>343,900.00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>29223 N 46TH PL</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Cave Creek</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85331</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(201) 604-9023</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565435.pdf</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565435.pdf</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565435.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260565503</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>373,117.00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3900 E BASELINE RD 158</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>85042</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(200) 747-0621</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565503.pdf</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565503.pdf</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565503.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260565556</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Reed B. Hopkin And Janat Hopkin</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>354,000.00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 10818 W. CAMPANA DR.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Sun City</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>230-02-624</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Reed B. Hopkin And Janat</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Hopkin</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565556.pdf</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565556.pdf</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565556.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260565574</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Austin James Scott, single man</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>301,536.00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>8251 N 22nd Drive</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85021</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>158-06-670</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(200) 749-7060</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Austin James Scott, single</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565574.pdf</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565574.pdf</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565574.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260565579</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Othoneil Baca and Candace M Marquez, husband and wife</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>484,912.00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>313-24-872</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>(202) 012-3584</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Othoneil</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Baca</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Candace M Marquez, husband and</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565579.pdf</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565579.pdf</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565579.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260565590</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Angela Coleman</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>419,210.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3707 East Southern Avenue</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85206</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>220-80-710</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Coleman</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565590.pdf</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565590.pdf</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565590.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260565613</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Michael Winklepleck</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>173,655.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>3707 East Southern Avenue</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85206</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>103-08</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Winklepleck</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565613.pdf</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565613.pdf</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565613.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260565712</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Teresa J. Gutierrez, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>166,920.00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>258 E 9th Dr</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85210</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>139-51-135</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(202) 204-4183</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Teresa J. Gutierrez, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565712.pdf</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565712.pdf</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565712.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260565722</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Juan Andrade and Alyssa Andrade, husband and wife</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>185,000.00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>104-84-596</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(201) 604-6356</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Andrade</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Alyssa Andrade, husband and</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565722.pdf</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565722.pdf</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565722.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260565790</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>817,500.00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>28725 North 210th Avenue</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Wittmann</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>503-47-052</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(672) 318-2409</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565790.pdf</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565790.pdf</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565790.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260566139</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>(s): Mark Lawrence And Jennifer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>209,817.49</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4124 W TUCKEY LN</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>152-31-097</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(200) 745-2074</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>(s): Mark Lawrence And</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566139.pdf</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566139.pdf</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566139.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260566141</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>225,000.00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1223 EAST SUNLAND AVENUE</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>113-59-159</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(200) 758-0628</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566141.pdf</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566141.pdf</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566141.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -423,10 +423,10 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -441,8 +441,8 @@
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="48" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260563857</t>
+          <t>20260566403</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,22 +650,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>— unomvatoocimn” Julia Owner, Llc</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>75,270,000.00</t>
+          <t>397,500.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6145 WALVARADO ROAD</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85035</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -677,63 +689,59 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>134-09</t>
+          <t>103-13-259</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Bryan Cave Leighton Paisner Llp</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 111-4219</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr"/>
+          <t>(202) 406-8845</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>— unomvatoocimn” Julia Owner,</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Llc</t>
-        </is>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563857.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566403.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563857.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566403.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563857.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566403.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260563862</t>
+          <t>20260566575</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -743,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -756,22 +764,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Azura Owner, Llc</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>73,390,000.00</t>
+          <t>716,750.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12755 W HIGHLAND AVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Litchfield Park</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85340</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -783,63 +803,59 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>149-17-151</t>
+          <t>508-07-775</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Bryan Cave Leighton Paisner Llp</t>
+          <t>Mfc Fittancial Inc, dba Trustee Corps</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 204-6763</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
+          <t>(202) 505-8361</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Azura Owner,</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Llc</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563862.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566575.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563862.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566575.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563862.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566575.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260563983</t>
+          <t>20260566584</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -849,7 +865,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -866,18 +882,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>374,440.00</t>
+          <t>378,026.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>or identifiable location: 3790 W BARCELONA DR</t>
+          <t>10438 W ORCHID LN</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -887,7 +903,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85226</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -901,23 +917,23 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>308-06-900</t>
+          <t>142-61-3943</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 405-4790</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -928,12 +944,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260563983.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566584.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260563983.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566584.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -946,14 +962,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260563983.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566584.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260564000</t>
+          <t>20260567413</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -963,7 +979,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -976,22 +992,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>and Orange Coast Title Company, a licensed</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>432,162.00</t>
+          <t>273,000.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>or identifiable location: 3392 S 180TH AVE</t>
+          <t>4442 W. SIERRA ST</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Goodyear</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1001,7 +1021,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85338</t>
+          <t>85304</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1013,61 +1033,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>502-48-724</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>before a trustee’s deed will be issued</t>
+          <t>or Successor Trustee has occurred. The nature of such breach of non-performance is as</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 205-0596</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2022-06-15</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>and Orange Coast Title Company, a</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>licensed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564000.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260567413.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564000.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260567413.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564000.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260567413.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260564019</t>
+          <t>20260567712</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1077,7 +1105,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1092,24 +1120,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>See Schedule “1”</t>
+          <t>Robert Defrancesco And Jayme Defrancesco, 2508 East Villa Rita Drive, Phoenix</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15,395.00</t>
+          <t>266,000.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15620 North Clubgate Drive</t>
+          <t>2508 East Villa Rita Drive</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1119,7 +1147,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85254</t>
+          <t>85032</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1131,32 +1159,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>214-06-047</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>sale or if you have an objection to the trustee sale, you must</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(702) 304-7509</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2027-01-12</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>See Schedule</t>
+          <t>Robert Defrancesco And Jayme Defrancesco, 2508 East Villa Rita Drive,</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>“1”</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
@@ -1164,32 +1192,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564019.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260567712.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564019.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260567712.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564019.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260567712.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260564032</t>
+          <t>20260567977</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1199,7 +1227,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1212,34 +1240,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Matthew Hines, an unmarried man, 7950 East Starlight Way, Unit 235, Scottsdale</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>174,699.00</t>
+          <t>389,500.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>or identifiable location: 651 N MAPLE ST</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Chandler</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85226</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1251,59 +1267,63 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>308-03-326</t>
+          <t>173-03-590</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Matthew Hines, an unmarried man, 7950 East Starlight Way, Unit 235,</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564032.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260567977.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564032.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260567977.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address, missing_auction_date</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564032.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260567977.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260564037</t>
+          <t>20260568003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1313,7 +1333,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1326,17 +1346,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(s): Michael Nguyen and Anh Nguyet Ho, husband and</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>244,496.00</t>
+          <t>240,463.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>or identifiable location: 14854 NORTH 36TH DRIVE</t>
+          <t>8236 W ILLINI STREET</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1351,7 +1375,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85053</t>
+          <t>85043</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1365,59 +1389,75 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>207-10-489</t>
+          <t>104-52-586</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(201) 903-1710</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>(s): Michael</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Anh Nguyet Ho, husband</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564037.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568003.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564037.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568003.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564037.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568003.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260564293</t>
+          <t>20260568004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1427,7 +1467,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1440,22 +1480,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Malorie Magill, a single woman, as her Sole and Separate Property, 11073 West</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>458,541.00</t>
+          <t>75,000.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>or identifiable location: 2502 E HOPI AVE</t>
+          <t>11073 West Coggins Drive</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1465,7 +1509,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1479,59 +1523,71 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>140-60-168</t>
+          <t>200-86</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Malorie Magill, a single woman, as her</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Sole</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Separate Property, 11073</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564293.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568004.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564293.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568004.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564293.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568004.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260564308</t>
+          <t>20260568035</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1541,7 +1597,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1554,22 +1610,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pedro Cruz-Roman and Adrienne T Peshlakai-Cruz, husband and wife as</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>438,109.00</t>
+          <t>349,000.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>or identifiable location: 21254 W ALMERIA RD</t>
+          <t>3005 West Claremont Street</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1579,7 +1639,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>85017</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1593,63 +1653,71 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>502-61-153</t>
+          <t>152-24-142</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(202) 507-0197</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Cruz-Roman</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Adrienne T Peshlakai-Cruz, husband and wife</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564308.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568035.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564308.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568035.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564308.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568035.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260564637</t>
+          <t>20260568098</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1659,7 +1727,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1672,18 +1740,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Timothy L. Bea and Kimberly M. Bea, husband and wife as community property</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>296,000.00</t>
+          <t>145,500.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1822 South 39th Street Unit 45</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85206</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1695,59 +1783,71 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>134-47-135</t>
+          <t>140-66-660</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Fiqancial Inc. dba Trustee Corps</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(202) 202-0573</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Timothy L.</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Bea</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Kimberly M. Bea, husband and wife as community</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260564637.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568098.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260564637.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568098.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260564637.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568098.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260565020</t>
+          <t>20260568130</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1757,7 +1857,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1772,24 +1872,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eduardo Morgan</t>
+          <t>Angela M Snipes, an unmarried woman, 1382 South 222nd Drive, Buckeye, Az</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>225,000.00</t>
+          <t>58,500.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3707 East Southern Avenue</t>
+          <t>1382 South 222nd Drive</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1799,7 +1899,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1813,34 +1913,30 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>504-57-432</t>
+          <t>504-60-884</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Angela M Snipes, an unmarried woman, 1382 South 222nd Drive, Buckeye,</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>Az</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr"/>
@@ -1848,32 +1944,32 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565020.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568130.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565020.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568130.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565020.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568130.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260565021</t>
+          <t>20260568182</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1883,7 +1979,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1896,26 +1992,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Rattan Mansaor Marqus and Dalya Waleed Jameel, husband and wife, 6517 West</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>560,500.00</t>
+          <t>628,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6517 West Red Fox Road</t>
+          <t>or identifiable location: 5144 EAST AIRE LIBRE AVENUE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1925,7 +2017,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85083</t>
+          <t>85254</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1939,71 +2031,63 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>201-28-295</t>
+          <t>215-32-388</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Rattan Mansaor</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Marqus</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Dalya Waleed Jameel, husband and wife, 6517</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
+          <t>(800) 683-2468</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2007-04-06</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565021.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568182.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565021.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568182.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565021.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568182.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260565033</t>
+          <t>20260568210</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2013,7 +2097,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2028,24 +2112,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Patrick Kelly</t>
+          <t>Patricia Y. Reyes, an unmarried woman</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>327,000.00</t>
+          <t>183,121.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 12629 N 28TH WAY</t>
+          <t>11313 N. 81st Drive</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2055,7 +2139,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85032</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2069,34 +2153,34 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>166-05-381</t>
+          <t>142-07-065</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(200) 763-3028</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Patricia Y. Reyes, an unmarried</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -2104,12 +2188,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565033.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568210.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565033.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568210.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2122,14 +2206,14 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565033.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568210.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260565034</t>
+          <t>20260568221</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2139,7 +2223,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2154,24 +2238,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zeb Hanks Fullmer, a married man, as his Sole and Separate Property, 1460</t>
+          <t>Veronica Villanueva, an unmarried woman</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>480,000.00</t>
+          <t>276,892.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22948 East Desert Spoon Drive</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Queen Creek</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2181,7 +2265,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85142</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2195,71 +2279,67 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>314-11-431</t>
+          <t>500-04-058</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>(200) 762-1377</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Zeb Hanks Fullmer, a married man, as his</t>
+          <t>Veronica Villanueva, an unmarried</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Sole</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Separate Property,</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565034.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568221.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565034.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568221.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565034.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568221.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260565035</t>
+          <t>20260568227</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2269,7 +2349,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2282,26 +2362,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Karl Forsthoefel, a single person, 5005 East Adobe Street, Mesa, Az 85205</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>347,999.00</t>
+          <t>343,660.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5005 East Adobe Street</t>
+          <t>or identifiable location: 12510 W PARADISE DRIVE</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>El Mirage</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2311,7 +2387,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>85335</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2325,63 +2401,63 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>140-16-021</t>
+          <t>501-44-582</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Karl Forsthoefel, a single person, 5005 East Adobe Street, Mesa, Az</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>85205</t>
-        </is>
-      </c>
+          <t>(866) 539-4173</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565035.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568227.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565035.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568227.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565035.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568227.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260565036</t>
+          <t>20260568244</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2391,7 +2467,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2406,24 +2482,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Richard D. Howell and Diane N. Howell, husband and wife, 15268 North 63rd</t>
+          <t>Lori M. Russell, an unmarried woman</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>187,000.00</t>
+          <t>129,200.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15268 North 63rd Drive</t>
+          <t>17401 North Woodrose Court</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2433,7 +2509,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>85374</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2447,51 +2523,43 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>231-07-988</t>
+          <t>232-29-006</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
+          <t>(200) 752-2680</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Richard D.</t>
+          <t>Lori M. Russell, an unmarried</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Howell</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Diane N. Howell, husband and wife, 15268 North</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>63rd</t>
-        </is>
-      </c>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565036.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568244.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565036.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568244.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2504,14 +2572,14 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565036.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568244.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260565054</t>
+          <t>20260568246</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2521,7 +2589,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2534,38 +2602,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Danienne Johnson, an unmarried woman, 1024 East Frye Road Unit 1100, Phoenix</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>280,000.00</t>
+          <t>353,479.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1024 East Frye Road Unit 1100</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>85048</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2577,63 +2625,63 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>300-96-645</t>
+          <t>301-09-251</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Danienne Johnson, an unmarried woman, 1024 East Frye Road Unit 1100,</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+          <t>(866) 539-4173</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565054.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568246.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565054.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568246.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565054.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568246.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260565435</t>
+          <t>20260568268</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2643,7 +2691,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,22 +2704,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Genavieve Ferree, an unmarried woman</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>343,900.00</t>
+          <t>328,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29223 N 46TH PL</t>
+          <t>7930 E Camelback Road Unit 111</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Cave Creek</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2681,7 +2733,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85331</t>
+          <t>85251</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2693,57 +2745,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>173-76-548</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(201) 604-9023</t>
+          <t>(202) 404-7549</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Genavieve Ferree, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565435.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568268.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565435.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568268.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565435.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568268.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260565503</t>
+          <t>20260568332</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2753,7 +2817,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2766,22 +2830,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vincent Trokon Wannah and Christiana Gbeh Wannah, husband and wife, and James Korvah, a</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>373,117.00</t>
+          <t>301,439.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3900 E BASELINE RD 158</t>
+          <t>7780 N 58th Lane</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2791,7 +2859,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85042</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2803,57 +2871,73 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>147-20-074</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(200) 747-0621</t>
+          <t>(200) 759-6824</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Vincent Trokon</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Wannah</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Christiana Gbeh Wannah, husband and wife, and James Korvah,</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565503.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568332.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565503.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568332.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565503.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568332.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260565556</t>
+          <t>20260568438</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2863,7 +2947,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2878,24 +2962,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reed B. Hopkin And Janat Hopkin</t>
+          <t>Jacque Napier, an unmarried man</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>354,000.00</t>
+          <t>240,562.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 10818 W. CAMPANA DR.</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2905,7 +2989,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2919,34 +3003,30 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>230-02-624</t>
+          <t>108-16</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(200) 763-3115</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Reed B. Hopkin And Janat</t>
+          <t>Jacque Napier, an unmarried</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Hopkin</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -2954,32 +3034,32 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565556.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568438.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565556.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568438.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565556.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568438.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260565574</t>
+          <t>20260568450</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2989,7 +3069,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3004,24 +3084,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austin James Scott, single man</t>
+          <t>in favor of Fnancial Freedom Senior</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>301,536.00</t>
+          <t>334,224.31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8251 N 22nd Drive</t>
+          <t>14802 W YOSEMITE DR</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun West</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3031,7 +3111,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85021</t>
+          <t>85375</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3045,30 +3125,34 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>158-06-670</t>
+          <t>232-17-840</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Date: September 25, 2026 Clear Recon Corp</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(200) 749-7060</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Austin James Scott, single</t>
+          <t>in favor of Fnancial Freedom</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
@@ -3076,32 +3160,32 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565574.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568450.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565574.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568450.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565574.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568450.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260565579</t>
+          <t>20260568497</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3111,7 +3195,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3126,24 +3210,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Othoneil Baca and Candace M Marquez, husband and wife</t>
+          <t>Sergio Rodriguez</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>484,912.00</t>
+          <t>10,500.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>580 E Wilcox Drive</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sierra Vista</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3153,7 +3237,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85635</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3167,67 +3251,63 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>313-24-872</t>
+          <t>503-92-569</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(202) 012-3584</t>
+          <t>(520) 458-3500</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Othoneil</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Baca</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Candace M Marquez, husband and</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565579.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568497.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565579.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568497.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565579.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568497.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260565590</t>
+          <t>20260568503</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3237,7 +3317,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3252,24 +3332,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Angela Coleman</t>
+          <t>Deborah Dawson and Brandon Anger, wife and husband</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>419,210.00</t>
+          <t>141,000.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3707 East Southern Avenue</t>
+          <t>705 E. Vaughn Drive</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3279,7 +3359,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3293,18 +3373,18 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>220-80-710</t>
+          <t>301-47-206</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 605-6850</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3315,25 +3395,33 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Deborah</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Coleman</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+          <t>Dawson</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Brandon Anger, wife and</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565590.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568503.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565590.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568503.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3346,14 +3434,14 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565590.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568503.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260565613</t>
+          <t>20260568518</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3363,7 +3451,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3378,24 +3466,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Michael Winklepleck</t>
+          <t>David Galindo Perez, a single man</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>173,655.00</t>
+          <t>205,000.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3707 East Southern Avenue</t>
+          <t>3135 W Berkeley Rd</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3405,7 +3493,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3419,34 +3507,34 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>103-08</t>
+          <t>108-26-051</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 605-6851</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>David Galindo Perez, a single</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Winklepleck</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr"/>
@@ -3454,12 +3542,12 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565613.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568518.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565613.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568518.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3472,14 +3560,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565613.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568518.txt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260565712</t>
+          <t>20260568601</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3489,7 +3577,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3504,24 +3592,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Teresa J. Gutierrez, an unmarried woman</t>
+          <t>Manuel Velasco Vazquez &amp; Flor Olivas, (husband and wife)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>166,920.00</t>
+          <t>129,900.00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>258 E 9th Dr</t>
+          <t>3607 W. Melvin St.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3531,7 +3619,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>85210</t>
+          <t>85016</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3545,63 +3633,75 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>139-51-135</t>
+          <t>106-15-145</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>(202) 204-4183</t>
+          <t>(202) 303-0348</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Teresa J. Gutierrez, an unmarried</t>
+          <t>Manuel Velasco</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+          <t>Vazquez</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Flor Olivas, (husband and</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>wife)</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565712.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568601.pdf</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565712.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568601.pdf</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565712.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568601.txt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260565722</t>
+          <t>20260568608</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3611,7 +3711,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3626,24 +3726,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Juan Andrade and Alyssa Andrade, husband and wife</t>
+          <t>Elizabeth Aldaco (a single woman)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>185,000.00</t>
+          <t>342,000.00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>17833 W. Voltaire St.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3653,7 +3753,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85388</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3667,18 +3767,14 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>104-84-596</t>
+          <t>502-05-281</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>/Successor Trustee, is regulated by and</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>(201) 604-6356</t>
+          <t>(202) 207-4516</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3689,53 +3785,45 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Elizabeth Aldaco (a single</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Andrade</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Alyssa Andrade, husband and</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>woman)</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565722.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568608.pdf</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565722.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568608.pdf</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565722.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568608.txt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260565790</t>
+          <t>20260568611</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3745,7 +3833,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3760,24 +3848,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>R&amp;L Quality Llc (an Arizona Limited Liability Company)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>817,500.00</t>
+          <t>185,900.00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28725 North 210th Avenue</t>
+          <t>4226 N. 68th Ave.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Wittmann</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3787,7 +3875,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>85361</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3801,43 +3889,47 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>503-47-052</t>
+          <t>144-40-212</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>(672) 318-2409</t>
+          <t>(202) 406-4335</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>and</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr"/>
+          <t>R&amp;L Quality Llc (an Arizona Limited Liability</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Company)</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260565790.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568611.pdf</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260565790.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568611.pdf</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3850,14 +3942,14 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260565790.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568611.txt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260566139</t>
+          <t>20260568616</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3867,7 +3959,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3882,19 +3974,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(s): Mark Lawrence And Jennifer</t>
+          <t>Guillermo Meza and Angelica Meza, husband and wife, as community property with right of</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>209,817.49</t>
+          <t>364,000.00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4124 W TUCKEY LN</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3909,7 +4001,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>85019</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3923,67 +4015,71 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>152-31-097</t>
+          <t>214-01-513</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>(200) 745-2074</t>
+          <t>(202) 204-2562</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>(s): Mark Lawrence And</t>
+          <t>Guillermo</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Jennifer</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+          <t>Meza</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Angelica Meza, husband and wife, as community property with right</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566139.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568616.pdf</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566139.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568616.pdf</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566139.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568616.txt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260566141</t>
+          <t>20260568889</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3993,7 +4089,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4008,24 +4104,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(s)</t>
+          <t>Jose R. Ortiz Santos (a marriad man as his sole and separate property)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>225,000.00</t>
+          <t>217,000.00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1223 EAST SUNLAND AVENUE</t>
+          <t>6746 N. 43rd Ave.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4035,7 +4131,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4049,43 +4145,55 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>113-59-159</t>
+          <t>146-26-098</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>(200) 758-0628</t>
+          <t>(202) 506-8399</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>(s)</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+          <t>Jose R. Ortiz Santos (a marriad man as his</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>sole</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>property)</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566141.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568889.pdf</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566141.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568889.pdf</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4098,7 +4206,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566141.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568889.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -423,10 +423,10 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -441,13 +441,13 @@
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
     <col width="60" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="49" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260566403</t>
+          <t>20260569410</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -654,18 +654,18 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>397,500.00</t>
+          <t>374,130.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6145 WALVARADO ROAD</t>
+          <t>14214 W HACKAMORE DR</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85035</t>
+          <t>85387</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -689,18 +689,18 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>103-13-259</t>
+          <t>503-69-325</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 406-8845</t>
+          <t>(202) 300-9680</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -716,12 +716,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566403.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569410.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566403.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569410.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -734,14 +734,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566403.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569410.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260566575</t>
+          <t>20260569413</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -768,30 +768,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>716,750.00</t>
+          <t>125,446.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12755 W HIGHLAND AVE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Litchfield Park</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>85340</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -803,18 +787,18 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>508-07-775</t>
+          <t>109-33-039</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Mfc Fittancial Inc, dba Trustee Corps</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 505-8361</t>
+          <t>(200) 600-9894</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -830,32 +814,32 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566575.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569413.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566575.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569413.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566575.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569413.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260566584</t>
+          <t>20260569414</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -865,7 +849,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -882,18 +866,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>378,026.00</t>
+          <t>324,318.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10438 W ORCHID LN</t>
+          <t>24606 W WHYMAN AVE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -903,7 +887,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85345</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -917,23 +901,23 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>142-61-3943</t>
+          <t>504-65-045</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 405-4790</t>
+          <t>(202) 301-6234</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -944,12 +928,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260566584.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569414.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260566584.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569414.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -962,14 +946,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260566584.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569414.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260567413</t>
+          <t>20260569416</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,7 +963,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -994,24 +978,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>and Orange Coast Title Company, a licensed</t>
+          <t>Unofficial Document</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>273,000.00</t>
+          <t>359,900.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4442 W. SIERRA ST</t>
+          <t>15077 W VALE DR</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Goodyear</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1021,7 +1005,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1033,36 +1017,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>501-69-504</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>or Successor Trustee has occurred. The nature of such breach of non-performance is as</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(202) 205-0596</t>
+          <t>(202) 502-4836</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>and Orange Coast Title Company, a</t>
+          <t>Unofficial</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>licensed</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -1070,32 +1054,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260567413.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569416.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260567413.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569416.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260567413.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569416.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260567712</t>
+          <t>20260569419</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1105,7 +1089,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1118,26 +1102,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Robert Defrancesco And Jayme Defrancesco, 2508 East Villa Rita Drive, Phoenix</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>266,000.00</t>
+          <t>633,000.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2508 East Villa Rita Drive</t>
+          <t>914 S GEORGE DR</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1147,7 +1127,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85032</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1159,65 +1139,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>214-06-047</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
+          <t>(202) 209-0897</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Robert Defrancesco And Jayme Defrancesco, 2508 East Villa Rita Drive,</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260567712.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569419.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260567712.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569419.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260567712.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569419.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260567977</t>
+          <t>20260569443</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1227,7 +1199,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1240,22 +1212,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Matthew Hines, an unmarried man, 7950 East Starlight Way, Unit 235, Scottsdale</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>389,500.00</t>
+          <t>156,000.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5016 N 86TH AVE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85305</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1265,50 +1249,42 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>173-03-590</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
+          <t>(200) 758-0740</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Matthew Hines, an unmarried man, 7950 East Starlight Way, Unit 235,</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Scottsdale</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260567977.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569443.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260567977.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569443.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_auction_date</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1316,14 +1292,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260567977.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569443.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260568003</t>
+          <t>20260569547</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1333,7 +1309,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1348,24 +1324,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(s): Michael Nguyen and Anh Nguyet Ho, husband and</t>
+          <t>Rafael A Licea Diaz And Alondra Rivera-Torres</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>240,463.00</t>
+          <t>323,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8236 W ILLINI STREET</t>
+          <t>or IDENTIFIABLE LOCATION: 12758 WEST DREYFUS DRIVE</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>El Mirage</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1375,7 +1351,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85043</t>
+          <t>85335</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1389,55 +1365,47 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>104-52-586</t>
+          <t>509-09-740</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(201) 903-1710</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>(s): Michael</t>
+          <t>Rafael A Licea Diaz And Alondra</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Anh Nguyet Ho, husband</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
+          <t>Rivera-Torres</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568003.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569547.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568003.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569547.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1450,14 +1418,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568003.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569547.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260568004</t>
+          <t>20260569556</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1467,7 +1435,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1482,24 +1450,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malorie Magill, a single woman, as her Sole and Separate Property, 11073 West</t>
+          <t>Larry J Moyer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>75,000.00</t>
+          <t>572,000.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11073 West Coggins Drive</t>
+          <t>or IDENTIFIABLE LOCATION: 4510 E WEAVER RD</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1509,7 +1477,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1523,71 +1491,67 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>200-86</t>
+          <t>212-32-424</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Malorie Magill, a single woman, as her</t>
+          <t>Larry J</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Sole</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Separate Property, 11073</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
+          <t>Moyer</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568004.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569556.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568004.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569556.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568004.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569556.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260568035</t>
+          <t>20260570476</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1597,7 +1561,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1612,24 +1576,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pedro Cruz-Roman and Adrienne T Peshlakai-Cruz, husband and wife as</t>
+          <t>(s): Tina-Marie Smith, unmarried woman</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>349,000.00</t>
+          <t>167,684.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3005 West Claremont Street</t>
+          <t>3126 N FONTANA AVE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Tucson</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1639,7 +1603,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>85705</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1653,71 +1617,67 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>152-24-142</t>
+          <t>107-11</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
+          <t>(202) 418-0009</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>(s): Tina-Marie Smith, unmarried</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Cruz-Roman</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Adrienne T Peshlakai-Cruz, husband and wife</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568035.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570476.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568035.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570476.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568035.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570476.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260568098</t>
+          <t>20260570547</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1727,7 +1687,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1740,26 +1700,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Timothy L. Bea and Kimberly M. Bea, husband and wife as community property</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>145,500.00</t>
+          <t>189,000.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1822 South 39th Street Unit 45</t>
+          <t>2217 W SHADY GLEN AVE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1769,7 +1725,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1783,71 +1739,59 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>140-66-660</t>
+          <t>208-26-101</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>inancial inc. doa Trustee Corps</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
+          <t>(202) 108-7640</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Timothy L.</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Bea</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Kimberly M. Bea, husband and wife as community</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>property</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568098.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570547.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568098.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570547.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568098.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570547.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260568130</t>
+          <t>20260570909</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1857,7 +1801,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1870,26 +1814,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Angela M Snipes, an unmarried woman, 1382 South 222nd Drive, Buckeye, Az</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>58,500.00</t>
+          <t>227,950.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1382 South 222nd Drive</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1899,7 +1839,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1913,63 +1853,59 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>504-60-884</t>
+          <t>148-09-854</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
+          <t>(202) 404-7356</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Angela M Snipes, an unmarried woman, 1382 South 222nd Drive, Buckeye,</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Az</t>
-        </is>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568130.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570909.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568130.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570909.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568130.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570909.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260568182</t>
+          <t>20260570981</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1979,7 +1915,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1996,18 +1932,18 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>628,000.00</t>
+          <t>64,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>or identifiable location: 5144 EAST AIRE LIBRE AVENUE</t>
+          <t>636 N 69TH AVE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2017,7 +1953,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85254</t>
+          <t>85043</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2029,32 +1965,24 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>215-32-388</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(800) 683-2468</t>
+          <t>(200) 755-3464</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2007-04-06</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -2062,32 +1990,32 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568182.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570981.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568182.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570981.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568182.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570981.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260568210</t>
+          <t>20260571085</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2097,7 +2025,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2110,26 +2038,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Patricia Y. Reyes, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>183,121.00</t>
+          <t>355,010.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11313 N. 81st Drive</t>
+          <t>10926 W ATLANTIS WAY</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Tolleson</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2139,7 +2063,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85345</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2151,69 +2075,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>142-07-065</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>herein qualifies as Trustee of the Tritst’ Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(200) 763-3028</t>
+          <t>(202) 305-3315</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Patricia Y. Reyes, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568210.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571085.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568210.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571085.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568210.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571085.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260568221</t>
+          <t>20260571095</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2223,7 +2135,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2236,26 +2148,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Veronica Villanueva, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>276,892.00</t>
+          <t>128,700.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>701 E BUFFALO ST</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Chandler</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2265,7 +2173,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85225</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2277,69 +2185,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>500-04-058</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>herein qualifies as Trustee of f st Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(200) 762-1377</t>
+          <t>(200) 758-5689</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Veronica Villanueva, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568221.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571095.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568221.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571095.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568221.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571095.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260568227</t>
+          <t>20260571119</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2349,7 +2245,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2366,18 +2262,18 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>343,660.00</t>
+          <t>139,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>or identifiable location: 12510 W PARADISE DRIVE</t>
+          <t>11960 W MOUNTAIN VIEW DR</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>El Mirage</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2387,7 +2283,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2399,32 +2295,24 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>501-44-582</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+          <t>herein qualifies as Trustee of t!</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(866) 539-4173</t>
+          <t>(201) 108-5864</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -2432,32 +2320,32 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568227.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571119.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568227.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571119.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568227.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571119.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260568244</t>
+          <t>20260571633</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2467,7 +2355,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2482,24 +2370,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lori M. Russell, an unmarried woman</t>
+          <t>and the original beneficiary, as it may have been amended from time to time, and pursuant to</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>129,200.00</t>
+          <t>5,000,000.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17401 North Woodrose Court</t>
+          <t>or identifiable location: 1711 W BELL RD</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2509,7 +2397,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85374</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2523,63 +2411,79 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>232-29-006</t>
+          <t>208-13-949</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>may require entity or trust bidders at this trustee's sale to provide</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(200) 752-2680</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+          <t>(202) 102-5390</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Lori M. Russell, an unmarried</t>
+          <t>and the original beneficiary, as it may have been amended from time to</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+          <t>time,</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>pursuant</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568244.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571633.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568244.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571633.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568244.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571633.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260568246</t>
+          <t>20260571911</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2589,7 +2493,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2606,14 +2510,30 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>353,479.00</t>
+          <t>208,160.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5032 W MCLELLAN RD</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2623,32 +2543,24 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>301-09-251</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(866) 539-4173</t>
+          <t>(202) 007-7407</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -2656,32 +2568,32 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568246.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571911.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568246.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571911.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568246.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571911.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260568268</t>
+          <t>20260572021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2691,7 +2603,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2706,24 +2618,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Genavieve Ferree, an unmarried woman</t>
+          <t>Alfredo Perez Carillo, a single man and Jocelyn Montes, a single woman, as joint tenants with rights</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>328,000.00</t>
+          <t>331,877.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7930 E Camelback Road Unit 111</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2733,7 +2645,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85251</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2747,7 +2659,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>173-76-548</t>
+          <t>509-09-835</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2758,36 +2670,44 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 404-7549</t>
+          <t>(202) 302-2010</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Genavieve Ferree, an unmarried</t>
+          <t>Alfredo Perez Carillo, a single</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Jocelyn Montes, a single woman, as joint tenants with</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568268.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572021.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568268.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572021.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2800,14 +2720,14 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568268.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572021.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260568332</t>
+          <t>20260572042</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2817,7 +2737,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2830,26 +2750,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Vincent Trokon Wannah and Christiana Gbeh Wannah, husband and wife, and James Korvah, a</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>301,439.00</t>
+          <t>139,500.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7780 N 58th Lane</t>
+          <t>or identifiable location: 26732 NORTH 53RD LANE</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2859,7 +2775,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2873,71 +2789,63 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>147-20-074</t>
+          <t>201-40-860</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(200) 759-6824</t>
+          <t>(200) 748-3975</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Vincent Trokon</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Wannah</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Christiana Gbeh Wannah, husband and wife, and James Korvah,</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2016-10-31</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568332.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572042.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568332.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572042.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568332.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572042.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260568438</t>
+          <t>20260572194</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2947,7 +2855,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2962,19 +2870,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jacque Napier, an unmarried man</t>
+          <t>(s): Yvette Barrett, An Unmarried Man</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>240,562.00</t>
+          <t>152,605.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>5625 SOUTH 11TH PLACE</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2989,7 +2897,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3003,30 +2911,34 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>108-16</t>
+          <t>113-58</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(200) 763-3115</t>
+          <t>(201) 600-4964</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Jacque Napier, an unmarried</t>
+          <t>(s): Yvette Barrett, An Unmarried</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -3034,32 +2946,32 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568438.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572194.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568438.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572194.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568438.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572194.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260568450</t>
+          <t>20260572200</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3069,7 +2981,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3082,26 +2994,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>in favor of Fnancial Freedom Senior</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>334,224.31</t>
+          <t>135,200.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14802 W YOSEMITE DR</t>
+          <t>10139 E CABALLERO ST</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Sun West</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3111,7 +3019,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85375</t>
+          <t>85207</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3125,67 +3033,59 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>232-17-840</t>
+          <t>220-14-117</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Date: September 25, 2026 Clear Recon Corp</t>
+          <t>Mts, Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(200) 511-1767</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>in favor of Fnancial Freedom</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568450.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572200.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568450.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572200.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568450.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572200.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260568497</t>
+          <t>20260572288</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3195,7 +3095,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3210,36 +3110,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sergio Rodriguez</t>
+          <t>”), for the benefit of Starwood</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10,500.00</t>
+          <t>73,390,000.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>580 E Wilcox Drive</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Sierra Vista</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85635</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3249,32 +3133,28 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>503-92-569</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Qualification: The Trustee qualifies as a Trustee of the Trust Deed in the</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(520) 458-3500</t>
+          <t>(202) 204-6763</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>”), for the benefit of</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
+          <t>Starwood</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3282,32 +3162,32 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568497.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572288.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568497.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572288.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568497.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572288.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260568503</t>
+          <t>20260572355</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3317,7 +3197,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3330,26 +3210,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Deborah Dawson and Brandon Anger, wife and husband</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>141,000.00</t>
+          <t>1,087,500.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>705 E. Vaughn Drive</t>
+          <t>9362 W DALEY LANE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3359,7 +3235,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>85383</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3373,75 +3249,59 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>301-47-206</t>
+          <t>200-20-218</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(202) 605-6850</t>
+          <t>(202) 201-2551</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Deborah</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Dawson</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Brandon Anger, wife and</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>husband</t>
-        </is>
-      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568503.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572355.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568503.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572355.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568503.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572355.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260568518</t>
+          <t>20260572521</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3451,7 +3311,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3466,19 +3326,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>David Galindo Perez, a single man</t>
+          <t>Brian P. Tompsett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>205,000.00</t>
+          <t>285,000.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3135 W Berkeley Rd</t>
+          <t>201 W. Jefferson St.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3493,7 +3353,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3507,34 +3367,30 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>108-26-051</t>
+          <t>200-98-727</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+          <t>Robert C. Williams</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(202) 605-6851</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
+          <t>(201) 805-2668</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>David Galindo Perez, a single</t>
+          <t>Brian P.</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>Tompsett</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr"/>
@@ -3542,32 +3398,32 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568518.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572521.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568518.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572521.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568518.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572521.txt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260568601</t>
+          <t>20260572689</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3577,7 +3433,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3590,26 +3446,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Manuel Velasco Vazquez &amp; Flor Olivas, (husband and wife)</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>129,900.00</t>
+          <t>426,831.00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3607 W. Melvin St.</t>
+          <t>17332 WEST ACACIA DRIVE</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Goodyear</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3619,7 +3471,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>85016</t>
+          <t>85338</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3633,75 +3485,59 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>106-15-145</t>
+          <t>400-04-692</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>(202) 303-0348</t>
+          <t>(202) 403-8511</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Manuel Velasco</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Vazquez</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Flor Olivas, (husband and</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>wife)</t>
-        </is>
-      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568601.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572689.pdf</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568601.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572689.pdf</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568601.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572689.txt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260568608</t>
+          <t>20260572839</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3711,7 +3547,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3724,38 +3560,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Elizabeth Aldaco (a single woman)</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>342,000.00</t>
+          <t>368,207.00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>17833 W. Voltaire St.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>85388</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -3767,63 +3583,63 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>502-05-281</t>
+          <t>142-88-752</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>(202) 207-4516</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Elizabeth Aldaco (a single</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>woman)</t>
-        </is>
-      </c>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568608.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572839.pdf</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568608.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572839.pdf</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568608.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572839.txt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260568611</t>
+          <t>20260572930</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,7 +3649,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3846,26 +3662,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>R&amp;L Quality Llc (an Arizona Limited Liability Company)</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>185,900.00</t>
+          <t>322,500.00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4226 N. 68th Ave.</t>
+          <t>19176 N 115TH DR</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3875,7 +3687,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>85033</t>
+          <t>85378</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3889,77 +3701,69 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>144-40-212</t>
+          <t>507-05-237</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>(202) 406-4335</t>
+          <t>(202) 000-8878</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>R&amp;L Quality Llc (an Arizona Limited Liability</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Company)</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568611.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572930.pdf</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568611.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572930.pdf</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568611.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572930.txt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260568616</t>
+          <t>20260572955</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N/TR SALE</t>
+          <t>N/TR SALE+</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3974,36 +3778,20 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guillermo Meza and Angelica Meza, husband and wife, as community property with right of</t>
+          <t>’s Stated Name and Address: Tm Main St Llc, an Arizona limited liability company, 6803</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>364,000.00</t>
+          <t>475,000.00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -4015,71 +3803,71 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>214-01-513</t>
+          <t>130-11-394</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>(payable at the time of sale or as allowed by the Trustee under Arizona law), but without covenant</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>(202) 204-2562</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+          <t>(202) 404-9864</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Guillermo</t>
+          <t>’s Stated</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Meza</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Angelica Meza, husband and wife, as community property with right</t>
+          <t>Address: Tm Main St Llc, an Arizona limited liability company,</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568616.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572955.pdf</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568616.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572955.pdf</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_address, missing_auction_date</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568616.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572955.txt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260568889</t>
+          <t>20260572976</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4089,7 +3877,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4102,26 +3890,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Jose R. Ortiz Santos (a marriad man as his sole and separate property)</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>217,000.00</t>
+          <t>391,020.00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6746 N. 43rd Ave.</t>
+          <t>1899 N 140TH DR</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Goodyear</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4131,7 +3915,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4145,68 +3929,52 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>146-26-098</t>
+          <t>501-83-117</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>(202) 506-8399</t>
+          <t>(200) 746-3128</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Jose R. Ortiz Santos (a marriad man as his</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>sole</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>separate</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>property)</t>
-        </is>
-      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260568889.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572976.pdf</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260568889.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572976.pdf</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260568889.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572976.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH30"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -423,9 +423,9 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -441,8 +441,8 @@
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="54" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260569410</t>
+          <t>20260573151</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,34 +650,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(s): Eugene H. Pardi, an unmarried man</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>374,130.00</t>
+          <t>365,682.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>14214 W HACKAMORE DR</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>85387</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -687,61 +675,65 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>503-69-325</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 300-9680</t>
+          <t>(201) 800-7588</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>(s): Eugene H. Pardi, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569410.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573151.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569410.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573151.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address, missing_apn</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569410.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573151.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260569413</t>
+          <t>20260573156</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -751,7 +743,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -764,11 +756,15 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>125,446.06</t>
+          <t>289,656.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -785,61 +781,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>109-33-039</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(200) 600-9894</t>
+          <t>(202) 501-3817</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569413.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573156.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569413.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573156.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_address, missing_apn</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569413.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573156.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260569414</t>
+          <t>20260573157</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -849,7 +845,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -862,22 +858,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(s): Jorge Casas, An Unmarried Man</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>324,318.00</t>
+          <t>294,566.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24606 W WHYMAN AVE</t>
+          <t>3426 WEST MARICOPA STREET</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -901,59 +901,67 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>504-65-045</t>
+          <t>109-58-081</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 301-6234</t>
+          <t>(202) 506-4443</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>(s): Jorge Casas, An Unmarried</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569414.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573157.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569414.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573157.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569414.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573157.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260569416</t>
+          <t>20260573158</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -963,7 +971,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -978,24 +986,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unofficial Document</t>
+          <t>(s): Daniel Quintero, Jr. and Monica R Quintero</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>359,900.00</t>
+          <t>372,135.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15077 W VALE DR</t>
+          <t>9706 W FLORENCE AVE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Goodyear</t>
+          <t>Tolleson</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1005,7 +1013,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1019,47 +1027,55 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>501-69-504</t>
+          <t>101-26-249</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(202) 502-4836</t>
+          <t>(202) 506-8758</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Unofficial</t>
+          <t>(s): Daniel Quintero,</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Document</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+          <t>Jr.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Monica R</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569416.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573158.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569416.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573158.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1072,14 +1088,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569416.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573158.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260569419</t>
+          <t>20260573159</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1089,7 +1105,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1102,22 +1118,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(s): Edward E Fearing Ii and Whitney B Fearing as</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>633,000.00</t>
+          <t>359,400.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>914 S GEORGE DR</t>
+          <t>3850 E PALO VERDE ST</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1127,7 +1147,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85281</t>
+          <t>85296</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1139,57 +1159,77 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>304-19-426</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(202) 209-0897</t>
+          <t>(202) 107-4701</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>(s): Edward E Fearing</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Ii</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Whitney B Fearing</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569419.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573159.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569419.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573159.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569419.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573159.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260569443</t>
+          <t>20260573163</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1199,7 +1239,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1212,22 +1252,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(s): Lynn Hagen, a married woman as her sole and</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>156,000.00</t>
+          <t>282,600.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5016 N 86TH AVE</t>
+          <t>10214 E MINNESOTA AVE</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Sun Lake</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1237,7 +1281,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85305</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1249,57 +1293,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>200-88-043</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(200) 758-0740</t>
+          <t>(202) 503-0661</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>(s): Lynn Hagen, a married woman as her sole</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569443.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573163.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569443.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573163.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569443.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573163.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260569547</t>
+          <t>20260573799</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1309,7 +1365,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1324,24 +1380,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rafael A Licea Diaz And Alondra Rivera-Torres</t>
+          <t>and now or hereafter attached or affixed to the Real Property; together with</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>323,000.00</t>
+          <t>1,162,500.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 12758 WEST DREYFUS DRIVE</t>
+          <t>320 S. Arizona Ave. #115</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>El Mirage</t>
+          <t>Chandler</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1351,7 +1407,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>85225</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1365,34 +1421,34 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>509-09-740</t>
+          <t>303-19</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(672) 332-2022</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Rafael A Licea Diaz And Alondra</t>
+          <t>and now or hereafter attached or affixed to the Real Property; together</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Rivera-Torres</t>
+          <t>with</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>
@@ -1400,12 +1456,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569547.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573799.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569547.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573799.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1418,14 +1474,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569547.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573799.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260569556</t>
+          <t>20260574010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1435,7 +1491,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1450,19 +1506,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Larry J Moyer</t>
+          <t>Barbara A Hagerman, a single woman</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>572,000.00</t>
+          <t>255,000.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 4510 E WEAVER RD</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1477,7 +1533,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85050</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1491,34 +1547,34 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>212-32-424</t>
+          <t>301-76-353</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 202-7342</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Larry J</t>
+          <t>Barbara A Hagerman, a single</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Moyer</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -1526,12 +1582,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260569556.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574010.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260569556.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574010.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1544,14 +1600,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260569556.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574010.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260570476</t>
+          <t>20260574308</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1561,7 +1617,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1576,24 +1632,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(s): Tina-Marie Smith, unmarried woman</t>
+          <t>Aaron K. McClinton</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>167,684.00</t>
+          <t>74,500.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3126 N FONTANA AVE</t>
+          <t>Purported Street Address: 9348 W. Payson Rd</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tucson</t>
+          <t>Tolleson</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1603,7 +1659,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85705</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1617,34 +1673,30 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>107-11</t>
+          <t>101-27-499</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Robert C. Williams</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(202) 418-0009</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
+          <t>(202) 107-7347</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>(s): Tina-Marie Smith, unmarried</t>
+          <t>Aaron K.</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>McClinton</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -1652,32 +1704,32 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570476.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574308.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570476.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574308.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570476.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574308.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260570547</t>
+          <t>20260574523</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1687,7 +1739,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1700,17 +1752,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Valerie Horn, a single woman</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>189,000.00</t>
+          <t>139,500.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2217 W SHADY GLEN AVE</t>
+          <t>4707 E. Amberwood Drive</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1725,7 +1781,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85023</t>
+          <t>85048</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1739,59 +1795,67 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>208-26-101</t>
+          <t>307-03-554</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>inancial inc. doa Trustee Corps</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(202) 108-7640</t>
+          <t>(200) 752-2684</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Valerie Horn, a single</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570547.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574523.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570547.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574523.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570547.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574523.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260570909</t>
+          <t>20260574564</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1801,7 +1865,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1818,30 +1882,14 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>227,950.00</t>
+          <t>310,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1853,26 +1901,30 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>148-09-854</t>
+          <t>170-28-051</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(202) 404-7356</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2008-02-19</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1880,32 +1932,32 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570909.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574564.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570909.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574564.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570909.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574564.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260570981</t>
+          <t>20260574591</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1915,7 +1967,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1932,30 +1984,14 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>64,000.00</t>
+          <t>316,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>636 N 69TH AVE</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>85043</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1965,24 +2001,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>148-16-108</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(200) 755-3464</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2021-12-20</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1990,32 +2034,32 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260570981.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574591.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260570981.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574591.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260570981.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574591.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260571085</t>
+          <t>20260574761</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2025,7 +2069,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2042,30 +2086,14 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>355,010.00</t>
+          <t>292,500.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>10926 W ATLANTIS WAY</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Tolleson</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2075,21 +2103,25 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>312-04-028</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Tritst’ Deed in the Trustee’s capacity as a licensed</t>
+          <t>manciaLloc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 305-3315</t>
+          <t>(202) 111-3528</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -2100,32 +2132,32 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571085.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574761.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571085.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574761.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571085.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574761.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260571095</t>
+          <t>20260574885</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2135,7 +2167,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2148,22 +2180,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Clayton R Smith and Barbara B Smith, husband and wife</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>128,700.00</t>
+          <t>155,000.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>701 E BUFFALO ST</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2173,7 +2209,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2185,57 +2221,73 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>230-04</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of f st Deed in the Trustee’s capacity as a licensed</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(200) 758-5689</t>
+          <t>(202) 205-6627</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Clayton R</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Barbara B Smith, husband and</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571095.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574885.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571095.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574885.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571095.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574885.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260571119</t>
+          <t>20260574949</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2245,7 +2297,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2262,18 +2314,18 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>139,000.00</t>
+          <t>157,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11960 W MOUNTAIN VIEW DR</t>
+          <t>3525 WEST PERSHING AVENUE</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2283,7 +2335,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2295,24 +2347,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>149-25-223</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of t!</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(201) 108-5864</t>
+          <t>(818) 991-4600</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2007-05-02</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -2320,32 +2380,32 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571119.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574949.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571119.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574949.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571119.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574949.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260571633</t>
+          <t>20260574950</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2355,7 +2415,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2368,38 +2428,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>and the original beneficiary, as it may have been amended from time to time, and pursuant to</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5,000,000.00</t>
+          <t>292,300.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>or identifiable location: 1711 W BELL RD</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>85023</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -2411,79 +2451,63 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>208-13-949</t>
+          <t>102-17-870</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>may require entity or trust bidders at this trustee's sale to provide</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(202) 102-5390</t>
+          <t>(949) 427-2016</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>and the original beneficiary, as it may have been amended from time to</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>time,</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>pursuant</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571633.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574950.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571633.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574950.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571633.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574950.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260571911</t>
+          <t>20260574977</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2493,7 +2517,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2510,18 +2534,18 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>208,160.00</t>
+          <t>51,563.80</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5032 W MCLELLAN RD</t>
+          <t>5548 N 9TH AVE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2531,7 +2555,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85013</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2547,17 +2571,17 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 007-7407</t>
+          <t>(201) 500-0899</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2568,12 +2592,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260571911.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574977.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260571911.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574977.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2586,24 +2610,24 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260571911.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574977.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260572021</t>
+          <t>20260575037</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N/TR SALE</t>
+          <t>N/TR SALE+</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2618,36 +2642,20 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alfredo Perez Carillo, a single man and Jocelyn Montes, a single woman, as joint tenants with rights</t>
+          <t>’s Stated Name and Address: Hannah Chiu and On Chi Ng, 662 Korima Lane, Grand</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>331,877.00</t>
+          <t>703,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2657,77 +2665,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>509-09-835</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>(payable at the time of sale or as allowed by the Trustee under Arizona law)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 302-2010</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+          <t>(202) 402-6192</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Alfredo Perez Carillo, a single</t>
+          <t>’s Stated</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Jocelyn Montes, a single woman, as joint tenants with</t>
+          <t>Address: Hannah Chiu and On Chi Ng, 662 Korima Lane,</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>rights</t>
+          <t>Grand</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572021.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575037.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572021.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575037.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572021.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575037.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260572042</t>
+          <t>20260575064</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2754,13 +2754,13 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>139,500.00</t>
+          <t>67,700.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>or identifiable location: 26732 NORTH 53RD LANE</t>
+          <t>6925 W MCKINLEY ST</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85083</t>
+          <t>85043</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2789,28 +2789,28 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>201-40-860</t>
+          <t>102-41-266</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(200) 748-3975</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
+          <t>2022-04-05</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -2820,12 +2820,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572042.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575064.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572042.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575064.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2838,14 +2838,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572042.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575064.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260572194</t>
+          <t>20260575142</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2868,26 +2868,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>(s): Yvette Barrett, An Unmarried Man</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>152,605.00</t>
+          <t>239,152.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5625 SOUTH 11TH PLACE</t>
+          <t>410 NORTH 119TH LANE</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2897,7 +2893,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2909,69 +2905,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>113-58</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(201) 600-4964</t>
+          <t>(201) 706-8812</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>(s): Yvette Barrett, An Unmarried</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572194.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575142.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572194.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575142.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572194.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575142.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260572200</t>
+          <t>20260575191</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2981,7 +2965,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2998,18 +2982,18 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>135,200.00</t>
+          <t>455,280.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10139 E CABALLERO ST</t>
+          <t>6721 S LAKESHORE DR</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3019,7 +3003,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85207</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3031,25 +3015,21 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>220-14-117</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Mts, Financial Inc. dba Trustee Corps</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(200) 511-1767</t>
+          <t>(202) 200-3342</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -3060,32 +3040,32 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572200.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575191.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572200.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575191.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572200.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575191.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260572288</t>
+          <t>20260575205</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3095,7 +3075,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3108,22 +3088,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>”), for the benefit of Starwood</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>73,390,000.00</t>
+          <t>51,563.80</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5548 N 9TH AVE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85013</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3137,57 +3129,53 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Qualification: The Trustee qualifies as a Trustee of the Trust Deed in the</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(202) 204-6763</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>(201) 500-0899</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>”), for the benefit of</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Starwood</t>
-        </is>
-      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572288.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575205.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572288.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575205.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572288.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575205.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260572355</t>
+          <t>20260575239</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3197,7 +3185,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3210,22 +3198,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>N 2 Logistics Llc, a Wyoming limited liability</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1,087,500.00</t>
+          <t>246,000.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9362 W DALEY LANE</t>
+          <t>5420 W. Onyx Ave.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3235,7 +3227,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>85383</t>
+          <t>85302</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3249,732 +3241,56 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>200-20-218</t>
+          <t>148-20-338</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Western Progressive — Arizona, Inc.</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(202) 201-2551</t>
+          <t>(202) 604-3614</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>N 2 Logistics Llc, a Wyoming limited</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>liability</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572355.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575239.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572355.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575239.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572355.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20260572521</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Brian P. Tompsett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>285,000.00</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson St.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>200-98-727</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Robert C. Williams</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>(201) 805-2668</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Brian P.</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Tompsett</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572521.pdf</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572521.pdf</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_auction_date</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572521.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20260572689</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>426,831.00</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>17332 WEST ACACIA DRIVE</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Goodyear</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>85338</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>400-04-692</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Western Progressive — Arizona, Inc.</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>(202) 403-8511</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572689.pdf</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572689.pdf</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572689.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20260572839</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>368,207.00</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>142-88-752</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Prestige Default Services, Llc</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572839.pdf</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572839.pdf</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner, missing_address</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>45</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572839.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20260572930</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>322,500.00</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>19176 N 115TH DR</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85378</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>507-05-237</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>(202) 000-8878</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572930.pdf</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572930.pdf</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572930.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20260572955</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>N/TR SALE+</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>’s Stated Name and Address: Tm Main St Llc, an Arizona limited liability company, 6803</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>475,000.00</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>130-11-394</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>(payable at the time of sale or as allowed by the Trustee under Arizona law), but without covenant</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>(202) 404-9864</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>’s Stated</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Address: Tm Main St Llc, an Arizona limited liability company,</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>6803</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572955.pdf</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572955.pdf</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_address, missing_auction_date</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572955.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20260572976</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>391,020.00</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>1899 N 140TH DR</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Goodyear</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85395</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>501-83-117</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>(200) 746-3128</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260572976.pdf</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260572976.pdf</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260572976.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575239.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH24"/>
+  <dimension ref="A1:AH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -423,9 +423,9 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="53" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="53" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="54" customWidth="1" min="27" max="27"/>
+    <col width="46" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260573151</t>
+          <t>20260575403</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -652,20 +652,36 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(s): Eugene H. Pardi, an unmarried man</t>
+          <t>(s): Christopher Dudley And Amber Dudley</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>365,682.00</t>
+          <t>548,250.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3911 E JAGUAR AVENUE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Gilbert</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85298</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -675,32 +691,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>313-04-782</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Quality Loan Service Corporation</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(201) 800-7588</t>
+          <t>(202) 103-2432</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>(s): Eugene H. Pardi, an unmarried</t>
+          <t>(s): Christopher Dudley And Amber</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>Dudley</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
@@ -708,32 +728,32 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573151.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575403.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573151.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575403.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573151.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575403.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260573156</t>
+          <t>20260575541</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -743,7 +763,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -756,22 +776,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(s)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>289,656.00</t>
+          <t>216,015.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5047 N 40TH AVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -781,61 +813,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>145-27-554</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 501-3817</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>(s)</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573156.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575541.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573156.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575541.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573156.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575541.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260573157</t>
+          <t>20260575710</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,7 +877,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -858,26 +890,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(s): Jorge Casas, An Unmarried Man</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>294,566.00</t>
+          <t>339,845.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3426 WEST MARICOPA STREET</t>
+          <t>or identifiable location: 8900 W GREER AVE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -887,7 +915,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -901,67 +929,63 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>109-58-081</t>
+          <t>142-45-173</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 506-4443</t>
+          <t>(202) 202-3779</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>(s): Jorge Casas, An Unmarried</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2022-03-11</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573157.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575710.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573157.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575710.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573157.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575710.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260573158</t>
+          <t>20260575883</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -971,7 +995,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -984,26 +1008,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(s): Daniel Quintero, Jr. and Monica R Quintero</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>372,135.00</t>
+          <t>750,000.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9706 W FLORENCE AVE</t>
+          <t>2719 E SYLVIA ST</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Tolleson</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1013,7 +1033,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>85032</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1027,75 +1047,59 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>101-26-249</t>
+          <t>166-54-286</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Quality Loan Service Corporation</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(202) 506-8758</t>
+          <t>(200) 751-0358</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>(s): Daniel Quintero,</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Jr.</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Monica R</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Quintero</t>
-        </is>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573158.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575883.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573158.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575883.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573158.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575883.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260573159</t>
+          <t>20260575898</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1120,24 +1124,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(s): Edward E Fearing Ii and Whitney B Fearing as</t>
+          <t>/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>359,400.00</t>
+          <t>331,579.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3850 E PALO VERDE ST</t>
+          <t>24627 W ROMLEY RD</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85296</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,55 +1165,43 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>304-19-426</t>
+          <t>504-42-661</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(202) 107-4701</t>
+          <t>(202) 400-9257</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>(s): Edward E Fearing</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Ii</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Whitney B Fearing</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573159.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575898.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573159.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575898.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1222,14 +1214,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573159.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575898.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260573163</t>
+          <t>20260576045</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1239,7 +1231,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1254,36 +1246,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(s): Lynn Hagen, a married woman as her sole and</t>
+          <t>Nickolus Sierra, a single man</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>282,600.00</t>
+          <t>118,000.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>10214 E MINNESOTA AVE</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Sun Lake</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85248</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1295,34 +1271,34 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>200-88-043</t>
+          <t>508-05-622</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(202) 503-0661</t>
+          <t>(202) 605-7604</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>(s): Lynn Hagen, a married woman as her sole</t>
+          <t>Nickolus Sierra, a single</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -1330,32 +1306,32 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573163.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576045.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573163.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576045.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573163.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576045.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260573799</t>
+          <t>20260576108</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1365,7 +1341,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1380,24 +1356,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>and now or hereafter attached or affixed to the Real Property; together with</t>
+          <t>Magaly Ayala, an unmarried woman</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1,162,500.00</t>
+          <t>270,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>320 S. Arizona Ave. #115</t>
+          <t>6312 N 64th Dr</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1407,7 +1383,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1421,34 +1397,30 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>303-19</t>
+          <t>144-15</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(672) 332-2022</t>
+          <t>(202) 507-2852</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>and now or hereafter attached or affixed to the Real Property; together</t>
+          <t>Magaly Ayala, an unmarried</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>with</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>
@@ -1456,32 +1428,32 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260573799.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576108.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260573799.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576108.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260573799.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576108.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260574010</t>
+          <t>20260576112</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1491,7 +1463,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1506,36 +1478,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barbara A Hagerman, a single woman</t>
+          <t>Innovation Communities at Villas at South Mountain, Llc</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>255,000.00</t>
+          <t>460,000.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1547,34 +1503,34 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>301-76-353</t>
+          <t>300-61</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(202) 202-7342</t>
+          <t>(202) 605-7611</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Barbara A Hagerman, a single</t>
+          <t>Innovation Communities at Villas at South Mountain,</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>Llc</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -1582,32 +1538,32 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574010.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576112.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574010.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576112.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574010.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576112.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260574308</t>
+          <t>20260576193</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1617,7 +1573,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1632,24 +1588,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aaron K. McClinton</t>
+          <t>Oscar Ortiz Flores, an unmarried man and Rosalba Rivera Valdez, an unmarried woman as joint</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>74,500.00</t>
+          <t>265,007.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Purported Street Address: 9348 W. Payson Rd</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tolleson</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1659,7 +1615,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1673,63 +1629,75 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>101-27-499</t>
+          <t>303-63-042</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Robert C. Williams</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(202) 107-7347</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
+          <t>(202) 506-8301</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Aaron K.</t>
+          <t>Oscar Ortiz Flores, an unmarried</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>McClinton</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Rosalba Rivera Valdez, an unmarried woman as</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574308.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576193.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574308.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576193.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574308.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576193.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260574523</t>
+          <t>20260576349</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1739,7 +1707,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1754,24 +1722,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valerie Horn, a single woman</t>
+          <t>(s): Mauricio Vasquez and Virginia Vasquez, husband</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>139,500.00</t>
+          <t>245,717.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4707 E. Amberwood Drive</t>
+          <t>11705 W RIO VISTA LN</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1781,7 +1749,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85048</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1795,47 +1763,55 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>307-03-554</t>
+          <t>500-32-430</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(200) 752-2684</t>
+          <t>(201) 605-3018</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Valerie Horn, a single</t>
+          <t>(s): Mauricio</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+          <t>Vasquez</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Virginia Vasquez,</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574523.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576349.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574523.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576349.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1848,14 +1824,14 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574523.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576349.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260574564</t>
+          <t>20260576561</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1865,7 +1841,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1882,14 +1858,30 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>310,000.00</t>
+          <t>156,389.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10135 N 95TH DR APT B</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85345</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1899,32 +1891,24 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>170-28-051</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(200) 747-0656</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2008-02-19</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1932,32 +1916,32 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574564.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576561.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574564.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576561.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574564.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576561.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260574591</t>
+          <t>20260576794</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1967,7 +1951,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1980,18 +1964,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ike Paik</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>316,000.00</t>
+          <t>204,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 5531 W BARBARA AVE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85302</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -2003,63 +2007,67 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>148-16-108</t>
+          <t>148-19-164</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2021-12-20</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Ike</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Paik</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574591.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576794.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574591.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576794.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574591.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576794.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260574761</t>
+          <t>20260576867</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2069,7 +2077,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2082,18 +2090,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Orlando Moreno, an unmarried man</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>292,500.00</t>
+          <t>181,649.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2105,59 +2133,63 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>312-04-028</t>
+          <t>145-21-064</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>manciaLloc. dba Trustee Corps</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 111-3528</t>
+          <t>(200) 760-3585</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Orlando Moreno, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574761.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576867.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574761.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576867.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574761.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576867.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260574885</t>
+          <t>20260576883</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2167,7 +2199,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,21 +2212,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Clayton R Smith and Barbara B Smith, husband and wife</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>155,000.00</t>
+          <t>697,500.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>or identifiable location: 2421 WEST GLENROSA AVENUE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2209,7 +2237,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85015</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2223,71 +2251,63 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>230-04</t>
+          <t>154-28-024</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 205-6627</t>
+          <t>(202) 304-1624</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Clayton R</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Barbara B Smith, husband and</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574885.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576883.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574885.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576883.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574885.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576883.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260574949</t>
+          <t>20260576919</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2297,7 +2317,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2310,22 +2330,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sigurd Campbell</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>157,000.00</t>
+          <t>70,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3525 WEST PERSHING AVENUE</t>
+          <t>or IDENTIFIABLE LOCATION: 7534 W SHUMWAY FARM RD</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Laveen</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2335,7 +2359,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2349,63 +2373,67 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>149-25-223</t>
+          <t>104-87-295</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(818) 991-4600</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2007-05-02</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Sigurd</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Campbell</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574949.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576919.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574949.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576919.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574949.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576919.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260574950</t>
+          <t>20260576936</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2415,7 +2443,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2432,7 +2460,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>292,300.00</t>
+          <t>547,500.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2451,30 +2479,26 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>102-17-870</t>
+          <t>217-71-848</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>inancial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(949) 427-2016</t>
+          <t>(202) 102-0932</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -2482,12 +2506,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574950.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576936.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574950.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576936.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2500,14 +2524,14 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574950.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576936.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260574977</t>
+          <t>20260576938</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2517,7 +2541,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2534,18 +2558,18 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>51,563.80</t>
+          <t>391,900.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5548 N 9TH AVE</t>
+          <t>17803 N PALO VERDE DR</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2555,7 +2579,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85013</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2567,21 +2591,25 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>230-07-528</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+          <t>jnancial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(201) 500-0899</t>
+          <t>(202) 404-5669</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2592,42 +2620,42 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260574977.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576938.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260574977.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576938.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260574977.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576938.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260575037</t>
+          <t>20260576943</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N/TR SALE+</t>
+          <t>N/TR SALE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2640,22 +2668,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>’s Stated Name and Address: Hannah Chiu and On Chi Ng, 662 Korima Lane, Grand</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>703,000.00</t>
+          <t>883,470.04</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>P.LN.: 160-42-072</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85021</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2667,67 +2707,51 @@
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>(payable at the time of sale or as allowed by the Trustee under Arizona law)</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 402-6192</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
+          <t>(312) 357-1125</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>’s Stated</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Address: Hannah Chiu and On Chi Ng, 662 Korima Lane,</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Grand</t>
-        </is>
-      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575037.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576943.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575037.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576943.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
+          <t>ocr_used, missing_owner, missing_trustee, missing_apn</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575037.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576943.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260575064</t>
+          <t>20260576957</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2737,7 +2761,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2750,17 +2774,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tristan Demory, a single man</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>67,700.00</t>
+          <t>257,050.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6925 W MCKINLEY ST</t>
+          <t>4148 W Boca Raton Rd</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2775,7 +2803,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85043</t>
+          <t>85053</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2789,508 +2817,56 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>102-41-266</t>
+          <t>207-12-704</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Prestige Default Services, Llc</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(202) 405-8830</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>2022-04-05</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Tristan Demory, a single</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575064.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260576957.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575064.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260576957.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575064.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20260575142</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>239,152.00</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>410 NORTH 119TH LANE</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Avondale</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>85323</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>(201) 706-8812</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575142.pdf</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575142.pdf</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575142.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20260575191</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>455,280.00</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>6721 S LAKESHORE DR</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Tempe</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>85283</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>(202) 200-3342</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575191.pdf</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575191.pdf</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575191.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20260575205</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>51,563.80</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>5548 N 9TH AVE</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85013</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>(201) 500-0899</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575205.pdf</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575205.pdf</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575205.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20260575239</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>N 2 Logistics Llc, a Wyoming limited liability</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>246,000.00</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>5420 W. Onyx Ave.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>85302</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>148-20-338</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>(202) 604-3614</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>N 2 Logistics Llc, a Wyoming limited</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>liability</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260575239.pdf</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260575239.pdf</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_trustee</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260575239.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260576957.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,20 +413,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="57" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -436,20 +436,20 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +621,2166 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>raw_text_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260578063</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>339,140.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24840 N 184TH LN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Wittmann</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(202) 300-5067</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578063.pdf</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578063.pdf</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578063.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260578395</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>333,841.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>or identifiable location: 6509 W COLTER ST</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>144-63-002</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(202) 108-9822</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578395.pdf</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578395.pdf</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578395.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260578686</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Denise L. Cromwell, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>85,475.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>139-48-247</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(201) 309-8144</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Denise L. Cromwell, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578686.pdf</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578686.pdf</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578686.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260578689</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>60,800.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>or identifiable location: 4870 SOUTH ANVIL PLACE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85249</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>303-46-343</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(200) 612-8838</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2006-09-22</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578689.pdf</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578689.pdf</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578689.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260578691</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Robin Ramirez, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>401,591.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16648 N 30th Ave</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85053</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>207-42-041</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(200) 747-0628</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Robin Ramirez, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578691.pdf</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578691.pdf</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578691.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260578751</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Colleen Callahan, a single woman</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>144,000.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Purported from said tax sheet 16660 E Westby Dr 1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Fountain Hills</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85268</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>176-24-050</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Current Trustee</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(200) 758-1762</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Colleen Callahan, a single</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578751.pdf</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578751.pdf</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578751.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260578776</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Michele A. Moore and Lee M. Moore, Sr., wife and husband</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>303,000.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>28571 North 124th Drive</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>503-89-202</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(200) 764-9655</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Michele A.</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Moore</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Lee M. Moore, Sr., wife and</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578776.pdf</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578776.pdf</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578776.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260578792</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jose Daniel Perez Paez And Margarita Alamilla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>240,000.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 2138 E FILLMORE ST</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85006</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>116-08-113</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Jose Daniel Perez Paez And Margarita</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Alamilla</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578792.pdf</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578792.pdf</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578792.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260578795</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Richard E Dern And Linda R Dern</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>243,192.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 21436 N 262ND LN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85396</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>510-06-167</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Richard E Dern And Linda R</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Dern</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578795.pdf</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578795.pdf</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578795.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260578800</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brenda M Murphy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>111,000.00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 4730 W NORTHERN AVE UNIT 2082</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>148-12</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Brenda M</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Murphy</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578800.pdf</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578800.pdf</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578800.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260578802</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Joel Goldsmith</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>153,000.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 2070 S MCCLELLAND DR</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85286</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Goldsmith</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578802.pdf</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578802.pdf</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578802.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260578804</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Marcus A. Mel, an unmarried man, 6982 West Spur Drive, Peoria, Az 85383</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>466,350.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6982 West Spur Drive</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>201-29-452</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Marcus A. Mel, an unmarried man, 6982 West Spur Drive, Peoria, Az</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578804.pdf</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578804.pdf</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578804.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260578859</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>150,000.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5102 East Corrine Drive</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85254</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>167-22-357</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578859.pdf</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578859.pdf</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578859.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260578882</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Angela Gary and Timothy Michael Gary,wife and husband, as community property with right of</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>447,500.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>204-12-878</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(202) 207-6215</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Gary</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Timothy Michael Gary,wife and husband, as community property with right</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578882.pdf</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578882.pdf</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578882.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260578932</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>242,861.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13423 WEST COUNTRYSIDE DR</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Sun City West</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>232-03-898</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(202) 504-3306</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578932.pdf</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578932.pdf</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578932.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260579264</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>548,250.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>44 W FOOTHILL DR</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85021</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>159-54-0511</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(202) 105-6059</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579264.pdf</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579264.pdf</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579264.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260579398</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(s): Ryan Heathcoe, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>245,471.00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>35316 WEST STEINWAY ROAD</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Arlington</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85322</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(202) 110-0132</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>(s): Ryan Heathcoe, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579398.pdf</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579398.pdf</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579398.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260579546</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>s): Joseph L. Perkins And Debra K, Perkins</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>235,653.00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>142-82</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(200) 764-3931</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>s): Joseph L. Perkins And Debra K,</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Perkins</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579546.pdf</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579546.pdf</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579546.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="57" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,9 +440,9 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="45" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="48" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260578063</t>
+          <t>20260579857</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -652,24 +652,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(s)</t>
+          <t>(s): Black Financial Llc, An Arizona Limited</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>339,140.00</t>
+          <t>271,000.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24840 N 184TH LN</t>
+          <t>8392 E CHARTER OAK DR</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Wittmann</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85361</t>
+          <t>85260</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -700,32 +700,36 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 300-5067</t>
+          <t>(202) 206-0946</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>(s)</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+          <t>(s): Black Financial Llc, An Arizona</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578063.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579857.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578063.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579857.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -738,14 +742,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578063.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579857.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260578395</t>
+          <t>20260580305</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,18 +776,18 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>333,841.00</t>
+          <t>262,922.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>or identifiable location: 6509 W COLTER ST</t>
+          <t>or identifiable location: 654 N ELM ST</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Chandler</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -793,7 +797,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85226</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -807,30 +811,26 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>144-63-002</t>
+          <t>301-87-708</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 108-9822</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2021-08-17</t>
-        </is>
-      </c>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -838,12 +838,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578395.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580305.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578395.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580305.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -856,14 +856,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578395.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580305.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260578686</t>
+          <t>20260580330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -886,22 +886,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Denise L. Cromwell, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>85,475.00</t>
+          <t>170,000.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>14601 W MARCUS DR</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85374</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -913,63 +925,59 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>139-48-247</t>
+          <t>232-28-238</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(201) 309-8144</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
+          <t>(202) 306-0887</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Denise L. Cromwell, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578686.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580330.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578686.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580330.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578686.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580330.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260578689</t>
+          <t>20260580333</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,7 +987,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -996,18 +1004,18 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>60,800.00</t>
+          <t>201,286.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>or identifiable location: 4870 SOUTH ANVIL PLACE</t>
+          <t>or identifiable location: 25335 WEST MALDONADO COURT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1017,7 +1025,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1031,30 +1039,26 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>303-46-343</t>
+          <t>504-41-343</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(200) 612-8838</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2006-09-22</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1062,12 +1066,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578689.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580333.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578689.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580333.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1080,14 +1084,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578689.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580333.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260578691</t>
+          <t>20260580433</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1112,24 +1116,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Robin Ramirez, an unmarried woman</t>
+          <t>(s): Janet Hidalgo, An Unmarried Woman</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>401,591.00</t>
+          <t>357,930.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16648 N 30th Ave</t>
+          <t>1917 N 106TH LN</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1139,7 +1143,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85053</t>
+          <t>85392</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1153,34 +1157,34 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>207-42-041</t>
+          <t>102-31-423</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(200) 747-0628</t>
+          <t>(202) 500-3793</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Robin Ramirez, an unmarried</t>
+          <t>(s): Janet Hidalgo, An Unmarried</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>Woman</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
@@ -1188,12 +1192,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578691.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580433.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578691.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580433.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1206,14 +1210,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578691.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580433.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260578751</t>
+          <t>20260580630</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1236,26 +1240,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Colleen Callahan, a single woman</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>144,000.00</t>
+          <t>187,220.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Purported from said tax sheet 16660 E Westby Dr 1</t>
+          <t>116 N 86TH ST</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Fountain Hills</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85268</t>
+          <t>85207</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1279,63 +1279,59 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>176-24-050</t>
+          <t>218-39</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Current Trustee</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(200) 758-1762</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
+          <t>(844) 693-4761</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Colleen Callahan, a single</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578751.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580630.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578751.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580630.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578751.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580630.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260578776</t>
+          <t>20260580683</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1345,7 +1341,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1358,26 +1354,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Michele A. Moore and Lee M. Moore, Sr., wife and husband</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>303,000.00</t>
+          <t>380,650.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28571 North 124th Drive</t>
+          <t>or identifiable location: 16538 N 114TH DR</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1387,7 +1379,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85383</t>
+          <t>85378</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1401,71 +1393,63 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>503-89-202</t>
+          <t>200-57-823</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(200) 764-9655</t>
+          <t>(202) 501-6035</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Michele A.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Moore</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Lee M. Moore, Sr., wife and</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>husband</t>
-        </is>
-      </c>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578776.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580683.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578776.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580683.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578776.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580683.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260578792</t>
+          <t>20260580811</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1475,7 +1459,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1488,26 +1472,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Jose Daniel Perez Paez And Margarita Alamilla</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>240,000.00</t>
+          <t>208,525.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 2138 E FILLMORE ST</t>
+          <t>26618 S HOGAN DR</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun Lakes</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1517,7 +1497,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85006</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1531,67 +1511,59 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>116-08-113</t>
+          <t>303-64-161</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(200) 800-0614</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Jose Daniel Perez Paez And Margarita</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Alamilla</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578792.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580811.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578792.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580811.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578792.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580811.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260578795</t>
+          <t>20260581113</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1601,7 +1573,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1614,26 +1586,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Richard E Dern And Linda R Dern</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>243,192.00</t>
+          <t>208,000.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 21436 N 262ND LN</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1643,7 +1611,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1657,18 +1625,18 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>510-06-167</t>
+          <t>164-34-113</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(844) 693-4761</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1677,47 +1645,39 @@
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Richard E Dern And Linda R</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Dern</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578795.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581113.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578795.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581113.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578795.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581113.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260578800</t>
+          <t>20260581265</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1727,7 +1687,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1742,24 +1702,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brenda M Murphy</t>
+          <t>Ahmed Al-Marridi and Kelly Jean Al-Marridi, husband and wife, 22727 East</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>111,000.00</t>
+          <t>501,216.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 4730 W NORTHERN AVE UNIT 2082</t>
+          <t>22727 East Bonanza Way</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Queen Creek</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1769,7 +1729,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85142</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1783,67 +1743,71 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>148-12</t>
+          <t>314-15-069</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Brenda M</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Murphy</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+          <t>Al-Marridi</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Kelly Jean Al-Marridi, husband and wife, 22727</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578800.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581265.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578800.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581265.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578800.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581265.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260578802</t>
+          <t>20260581372</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,7 +1817,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1866,26 +1830,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Joel Goldsmith</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>153,000.00</t>
+          <t>520,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 2070 S MCCLELLAND DR</t>
+          <t>2150 S 217th Ln</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1895,7 +1855,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85286</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1907,65 +1867,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>504-61-204</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 403-2868</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Joel</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Goldsmith</t>
-        </is>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578802.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581372.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578802.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581372.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578802.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581372.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260578804</t>
+          <t>20260581517</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1975,7 +1931,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1990,24 +1946,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marcus A. Mel, an unmarried man, 6982 West Spur Drive, Peoria, Az 85383</t>
+          <t>Sandra Engelhardt, an unmarried woman</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>466,350.00</t>
+          <t>203,205.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6982 West Spur Drive</t>
+          <t>13702 N 98th Ave Unit P</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2017,7 +1973,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85383</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2031,30 +1987,30 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>201-29-452</t>
+          <t>200-80</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
+          <t>(202) 207-0062</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Marcus A. Mel, an unmarried man, 6982 West Spur Drive, Peoria, Az</t>
+          <t>Sandra Engelhardt, an unmarried</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>85383</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -2062,12 +2018,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578804.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581517.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578804.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581517.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2080,14 +2036,14 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578804.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581517.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260578859</t>
+          <t>20260581528</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2097,7 +2053,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2110,22 +2066,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bradley L Hagan, a single man</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>150,000.00</t>
+          <t>699,300.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5102 East Corrine Drive</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2135,7 +2095,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85254</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2149,55 +2109,63 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>167-22-357</t>
+          <t>303-27-269</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
+          <t>(202) 201-9213</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Bradley L Hagan, a single</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578859.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581528.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578859.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581528.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_auction_date</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578859.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581528.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260578882</t>
+          <t>20260581529</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2207,7 +2175,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2222,13 +2190,13 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Angela Gary and Timothy Michael Gary,wife and husband, as community property with right of</t>
+          <t>Aundrae K Harris, an unmarried man</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>447,500.00</t>
+          <t>350,000.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2263,71 +2231,59 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>204-12-878</t>
+          <t>301-64-253</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 207-6215</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+          <t>(202) 110-6928</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Aundrae K Harris, an unmarried</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Gary</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Timothy Michael Gary,wife and husband, as community property with right</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>of</t>
-        </is>
-      </c>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578882.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581529.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578882.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581529.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578882.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581529.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260578932</t>
+          <t>20260581624</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2337,7 +2293,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2350,22 +2306,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(s): Charlotte Crawford And Ivory</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>242,861.00</t>
+          <t>314,250.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13423 WEST COUNTRYSIDE DR</t>
+          <t>17576 WEST VIA DE LUNA DR</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Sun City West</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2375,7 +2335,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85375</t>
+          <t>85387</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2387,61 +2347,65 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>232-03-898</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(202) 504-3306</t>
+          <t>(202) 100-9500</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>(s): Charlotte Crawford And</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Ivory</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260578932.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581624.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260578932.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581624.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260578932.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581624.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260579264</t>
+          <t>20260581625</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2451,7 +2415,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2464,22 +2428,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(s): Mark R. Glasgow and Karen E. Glasgow, husband</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>548,250.00</t>
+          <t>244,000.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>44 W FOOTHILL DR</t>
+          <t>8665 W ADAM AVE</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2489,7 +2457,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85021</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2501,61 +2469,73 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>159-54-0511</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(202) 105-6059</t>
+          <t>(201) 407-8036</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>(s): Mark R.</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Karen E. Glasgow,</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579264.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581625.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579264.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581625.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579264.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581625.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260579398</t>
+          <t>20260581634</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2565,7 +2545,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2578,26 +2558,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>(s): Ryan Heathcoe, an unmarried man</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>245,471.00</t>
+          <t>394,250.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35316 WEST STEINWAY ROAD</t>
+          <t>25952 W YUKON DR</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Arlington</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2607,7 +2583,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85322</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2619,65 +2595,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>5803-85-090</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 110-0132</t>
+          <t>(202) 105-7079</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>(s): Ryan Heathcoe, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579398.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581634.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579398.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581634.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579398.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581634.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260579546</t>
+          <t>20260581663</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2687,7 +2659,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2700,22 +2672,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>s): Joseph L. Perkins And Debra K, Perkins</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>235,653.00</t>
+          <t>373,150.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>12709 N ELFRIO ST</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>El Mirage</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2727,60 +2711,780 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>142-82</t>
+          <t>509-06-006</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Mtc alloc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(200) 764-3931</t>
+          <t>(200) 753-5830</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>s): Joseph L. Perkins And Debra K,</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Perkins</t>
-        </is>
-      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579546.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581663.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579546.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581663.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579546.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581663.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260581747</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>324,950.00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1638 EAST DONNER DRIVE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tempe</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>85282</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>133-39-379</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(202) 208-5241</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581747.pdf</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581747.pdf</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581747.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260581766</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>72,000.00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>325 N COLONY COVE DR</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Gilbert</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85234</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>309-01-061</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(202) 304-7598</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581766.pdf</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581766.pdf</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581766.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260581830</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>481,410.00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1410 E HORSESHOE DR</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85249</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(201) 906-8175</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581830.pdf</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581830.pdf</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581830.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260581906</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>William R. Czech, a married man as his sole and</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>807,500.00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2355 W. Pinnacle Peak Rd</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85027</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Statewide Foreclosure Services, Inc., a</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>(632) 938-4917</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>William R. Czech, a married man as his sole</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581906.pdf</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581906.pdf</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581906.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260581911</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Michael Johnson, an unmarried man, 2251 W. Isabella</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>200,000.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2150 E. Brown Road, Ste 2 61</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85213</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>131-49-119</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Statewide Foreclosure Services, Inc., a</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(202) 505-5047</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Michael Johnson, an unmarried man, 2251 W.</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581911.pdf</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581911.pdf</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581911.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260581969</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>(s): Jose A Rios and Marlenne K Chavez, husband and</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>624,589.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>8512 W RANCHO DR</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85305</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>102-11-918</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(202) 300-8878</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>(s): Jose A</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Rios</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Marlenne K Chavez, husband</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581969.pdf</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581969.pdf</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581969.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH25"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="54" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="53" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="45" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="48" customWidth="1" min="27" max="27"/>
+    <col width="50" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="49" customWidth="1" min="32" max="32"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260579857</t>
+          <t>20260582075</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -652,19 +652,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(s): Black Financial Llc, An Arizona Limited</t>
+          <t>(s): Black Rock Elite Properties, Llc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>271,000.00</t>
+          <t>420,000.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8392 E CHARTER OAK DR</t>
+          <t>8659 E ROANOKE AVENUE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85260</t>
+          <t>85257</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -691,7 +691,11 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>131-41-063</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
@@ -700,23 +704,23 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 206-0946</t>
+          <t>(202) 206-0862</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>(s): Black Financial Llc, An Arizona</t>
+          <t>(s): Black Rock Elite Properties,</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>Llc</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
@@ -724,32 +728,32 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260579857.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582075.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260579857.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582075.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260579857.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582075.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260580305</t>
+          <t>20260582119</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -759,7 +763,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -776,18 +780,18 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>262,922.00</t>
+          <t>294,880.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>or identifiable location: 654 N ELM ST</t>
+          <t>3029 W PARADISE DR</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -797,7 +801,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85226</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -811,23 +815,23 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>301-87-708</t>
+          <t>149-20-074</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(844) 093-4761</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -838,12 +842,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580305.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582119.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580305.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582119.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -856,14 +860,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580305.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582119.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260580330</t>
+          <t>20260582301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -873,7 +877,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -890,18 +894,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>170,000.00</t>
+          <t>338,402.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14601 W MARCUS DR</t>
+          <t>or identifiable location: 4946 W CHARLESTON AVE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -911,7 +915,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85374</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -925,23 +929,23 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>232-28-238</t>
+          <t>207-23-349</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(202) 306-0887</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -952,12 +956,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580330.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582301.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580330.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582301.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -970,14 +974,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580330.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582301.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260580333</t>
+          <t>20260582308</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -987,7 +991,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1004,13 +1008,13 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>201,286.00</t>
+          <t>473,398.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>or identifiable location: 25335 WEST MALDONADO COURT</t>
+          <t>or identifiable location: 30182 WEST MULBERRY DRIVE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1025,7 +1029,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1039,13 +1043,13 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>504-41-343</t>
+          <t>504-74-542</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1055,7 +1059,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1066,12 +1070,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580333.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582308.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580333.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582308.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1084,14 +1088,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580333.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582308.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260580433</t>
+          <t>20260582345</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1114,38 +1118,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>(s): Janet Hidalgo, An Unmarried Woman</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>357,930.00</t>
+          <t>518,059.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1917 N 106TH LN</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Avondale</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>85392</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1157,67 +1141,63 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>102-31-423</t>
+          <t>102-56-439</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(202) 500-3793</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>(s): Janet Hidalgo, An Unmarried</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Woman</t>
-        </is>
-      </c>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580433.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582345.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580433.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582345.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580433.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582345.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260580630</t>
+          <t>20260582458</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1227,7 +1207,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1244,18 +1224,18 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>187,220.00</t>
+          <t>459,685.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>116 N 86TH ST</t>
+          <t>or identifiable location: 1015 S 150TH DR</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Goodyear</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1265,7 +1245,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85207</t>
+          <t>85338</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1279,23 +1259,23 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>218-39</t>
+          <t>500-10-327</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(844) 693-4761</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1306,12 +1286,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580630.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582458.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580630.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582458.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1324,14 +1304,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580630.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582458.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260580683</t>
+          <t>20260582614</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1341,7 +1321,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1358,18 +1338,18 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>380,650.00</t>
+          <t>525,299.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>or identifiable location: 16538 N 114TH DR</t>
+          <t>or identifiable location: 9441 W HEATHERBRAE DR</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1379,7 +1359,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85378</t>
+          <t>85037</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1393,30 +1373,26 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>200-57-823</t>
+          <t>102-25-549</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(202) 501-6035</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1424,12 +1400,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580683.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582614.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580683.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582614.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1442,14 +1418,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580683.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582614.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260580811</t>
+          <t>20260582829</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1459,7 +1435,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1472,34 +1448,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>(s): Phyllis White-Robbins, unmarried woman</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>208,525.00</t>
+          <t>376,322.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>26618 S HOGAN DR</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Sun Lakes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>85248</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1511,59 +1475,67 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>303-64-161</t>
+          <t>220-36-137</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(200) 800-0614</t>
+          <t>(202) 402-9442</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>(s): Phyllis White-Robbins, unmarried</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260580811.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582829.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260580811.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582829.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260580811.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582829.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260581113</t>
+          <t>20260582840</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1573,7 +1545,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1590,18 +1562,18 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>208,000.00</t>
+          <t>473,259.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>or identifiable location: 12540 W TRUMBULL RD</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1611,7 +1583,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1625,23 +1597,23 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>164-34-113</t>
+          <t>500-72-135</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(844) 693-4761</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1652,12 +1624,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581113.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582840.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581113.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582840.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1670,14 +1642,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581113.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582840.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260581265</t>
+          <t>20260583065</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1687,7 +1659,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1702,24 +1674,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ahmed Al-Marridi and Kelly Jean Al-Marridi, husband and wife, 22727 East</t>
+          <t>(s): Michelle Marie Devine, an unmarried woman</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>501,216.00</t>
+          <t>117,978.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22727 East Bonanza Way</t>
+          <t>4742 W LAURIE LANE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Queen Creek</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1729,7 +1701,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85142</t>
+          <t>85302</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1743,71 +1715,67 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>314-15-069</t>
+          <t>148-12-120-1</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
+          <t>(201) 000-6444</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>(s): Michelle Marie Devine, an unmarried</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Al-Marridi</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Kelly Jean Al-Marridi, husband and wife, 22727</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581265.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583065.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581265.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583065.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581265.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583065.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260581372</t>
+          <t>20260583066</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1817,7 +1785,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1830,22 +1798,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>(s): Janet Monahan, an unmarried person</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>520,000.00</t>
+          <t>335,620.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2150 S 217th Ln</t>
+          <t>6530 W NORTH LN</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1855,7 +1827,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85302</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1869,59 +1841,67 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>504-61-204</t>
+          <t>143-49-486</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(202) 403-2868</t>
+          <t>(202) 201-9784</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>(s): Janet Monahan, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581372.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583066.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581372.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583066.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581372.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583066.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260581517</t>
+          <t>20260583178</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1931,7 +1911,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1944,26 +1924,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Sandra Engelhardt, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>203,205.00</t>
+          <t>248,500.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13702 N 98th Ave Unit P</t>
+          <t>832 S 79TH WAY</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1973,7 +1949,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1987,63 +1963,59 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>200-80</t>
+          <t>218-54</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(202) 207-0062</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
+          <t>(202) 501-6905</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Sandra Engelhardt, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581517.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583178.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581517.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583178.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581517.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583178.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260581528</t>
+          <t>20260583265</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2053,7 +2025,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2068,13 +2040,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bradley L Hagan, a single man</t>
+          <t>Dalton Etherton, a single man, and Caitlin Elizabeth Gillis, a single woman, as joint tenants with</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>699,300.00</t>
+          <t>551,610.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2109,43 +2081,51 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>303-27-269</t>
+          <t>303-27-788</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 201-9213</t>
+          <t>(202) 404-5715</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Bradley L Hagan, a single</t>
+          <t>Dalton Etherton, a single</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+          <t>man,</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Caitlin Elizabeth Gillis, a single woman, as joint tenants</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>with</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581528.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583265.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581528.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583265.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2158,14 +2138,14 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581528.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583265.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260581529</t>
+          <t>20260583391</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2175,7 +2155,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2190,24 +2170,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aundrae K Harris, an unmarried man</t>
+          <t>(s): David Andrae De La O and Valerie P De La O</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>350,000.00</t>
+          <t>466,396.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>12614 W ALEGRE DR</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Litchfield Park</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2217,7 +2197,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85340</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2231,59 +2211,75 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>301-64-253</t>
+          <t>508-07-495</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 110-6928</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>(202) 306-1359</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Aundrae K Harris, an unmarried</t>
+          <t>(s): David Andrae De La</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Valerie P De La</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581529.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583391.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581529.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583391.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581529.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583391.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260581624</t>
+          <t>20260583392</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2293,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2308,24 +2304,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(s): Charlotte Crawford And Ivory</t>
+          <t>(s): Thomas G. Harrington &amp; Maryellen B. Harrington</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>314,250.00</t>
+          <t>417,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17576 WEST VIA DE LUNA DR</t>
+          <t>36707 N 24TH STREET</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2335,7 +2331,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2347,7 +2343,11 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>211-67</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
@@ -2356,56 +2356,64 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(202) 100-9500</t>
+          <t>(200) 710-5325</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>(s): Charlotte Crawford And</t>
+          <t>(s): Thomas G.</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Ivory</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+          <t>Harrington</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Maryellen B.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Harrington</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581624.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583392.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581624.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583392.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581624.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583392.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260581625</t>
+          <t>20260583632</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2415,7 +2423,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2430,24 +2438,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(s): Mark R. Glasgow and Karen E. Glasgow, husband</t>
+          <t>(s): Richard May and Jacqueline Rose Vasquez-May</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>244,000.00</t>
+          <t>429,322.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8665 W ADAM AVE</t>
+          <t>11020 W PIERCE ST</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2457,7 +2465,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85382</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2469,7 +2477,11 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>102-56-456</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
@@ -2478,7 +2490,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(201) 407-8036</t>
+          <t>(202) 202-6798</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2489,53 +2501,53 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>(s): Mark R.</t>
+          <t>(s): Richard</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>May</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Karen E. Glasgow,</t>
+          <t>Jacqueline Rose</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>husband</t>
+          <t>Vasquez-May</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581625.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583632.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581625.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583632.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581625.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583632.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260581634</t>
+          <t>20260583633</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2545,7 +2557,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2558,22 +2570,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(s): Alexis Blandimir Mendez Rovelo And</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>394,250.00</t>
+          <t>359,370.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25952 W YUKON DR</t>
+          <t>11197 W CORONADO RD</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2583,7 +2599,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>85392</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2597,59 +2613,67 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>5803-85-090</t>
+          <t>102-30-590</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 105-7079</t>
+          <t>(202) 503-1941</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>(s): Alexis Blandimir Mendez Rovelo</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>And</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581634.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583633.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581634.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583633.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581634.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583633.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260581663</t>
+          <t>20260583688</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2659,7 +2683,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2672,22 +2696,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Luis Orozco, an single man</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>373,150.00</t>
+          <t>51,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12709 N ELFRIO ST</t>
+          <t>513 W Colgate Dr</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>El Mirage</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2697,7 +2725,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>85283</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2711,59 +2739,67 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>509-06-006</t>
+          <t>301-04-388</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Mtc alloc. dba Trustee Corps</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(200) 753-5830</t>
+          <t>(202) 306-5003</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Luis Orozco, an single</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581663.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583688.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581663.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583688.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581663.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583688.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260581747</t>
+          <t>20260583698</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2773,7 +2809,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2786,22 +2822,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Miguel Aguirre, an unmarried man</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>324,950.00</t>
+          <t>330,382.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1638 EAST DONNER DRIVE</t>
+          <t>201 W. Jefferson Street</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2811,7 +2851,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85282</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2825,59 +2865,67 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>133-39-379</t>
+          <t>116-12</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(202) 208-5241</t>
+          <t>(202) 303-8193</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Miguel Aguirre, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581747.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583698.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581747.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583698.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581747.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583698.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260581766</t>
+          <t>20260583912</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2935,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2900,22 +2948,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>(s): Jessica Raffle And Lee Raffle, Wife And</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>72,000.00</t>
+          <t>126,750.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>325 N COLONY COVE DR</t>
+          <t>3050 W WETHERSFIELD RD</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2925,7 +2977,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85234</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2939,59 +2991,67 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>309-01-061</t>
+          <t>149-41-118</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(202) 304-7598</t>
+          <t>(200) 767-2276</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>(s): Jessica Raffle And Lee Raffle, Wife</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>And</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581766.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583912.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581766.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583912.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581766.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583912.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260581830</t>
+          <t>20260583913</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3001,7 +3061,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3022,18 +3082,18 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>481,410.00</t>
+          <t>298,400.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1410 E HORSESHOE DR</t>
+          <t>6402 WEST DEVONSHIRE AVENUE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3043,7 +3103,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3055,7 +3115,11 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>144-85-068</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
@@ -3064,12 +3128,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(201) 906-8175</t>
+          <t>(202) 406-8541</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -3084,32 +3148,32 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581830.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583913.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581830.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583913.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581830.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583913.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260581906</t>
+          <t>20260583914</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3119,7 +3183,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3134,24 +3198,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>William R. Czech, a married man as his sole and</t>
+          <t>(s): Therese Margaret Brosnahan, A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>807,500.00</t>
+          <t>215,000.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2355 W. Pinnacle Peak Rd</t>
+          <t>4335 W CARSON RD</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Laveen</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3161,7 +3225,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85027</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3173,32 +3237,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>104-90-183</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Statewide Foreclosure Services, Inc., a</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(632) 938-4917</t>
+          <t>(202) 201-0047</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>William R. Czech, a married man as his sole</t>
+          <t>(s): Therese Margaret Brosnahan,</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3206,32 +3274,32 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581906.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583914.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581906.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583914.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581906.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583914.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260581911</t>
+          <t>20260583917</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3241,7 +3309,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3256,24 +3324,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Michael Johnson, an unmarried man, 2251 W. Isabella</t>
+          <t>(s): Barbara Jeanette Cowled, a married woman as her</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>200,000.00</t>
+          <t>385,000.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2150 E. Brown Road, Ste 2 61</t>
+          <t>3510 EAST KESLER LANE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3283,7 +3351,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>85213</t>
+          <t>85295</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3297,34 +3365,34 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>131-49-119</t>
+          <t>138-14</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Statewide Foreclosure Services, Inc., a</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(202) 505-5047</t>
+          <t>(202) 204-9634</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Michael Johnson, an unmarried man, 2251 W.</t>
+          <t>(s): Barbara Jeanette Cowled, a married woman as</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>her</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr"/>
@@ -3332,12 +3400,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581911.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583917.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581911.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583917.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3350,14 +3418,14 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581911.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583917.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260581969</t>
+          <t>20260584023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3367,7 +3435,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3380,38 +3448,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>(s): Jose A Rios and Marlenne K Chavez, husband and</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>624,589.00</t>
+          <t>168,884.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>8512 W RANCHO DR</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85305</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3423,68 +3471,642 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>102-11-918</t>
+          <t>144-15</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(202) 300-8878</t>
+          <t>(202) 501-5569</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>(s): Jose A</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Rios</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Marlenne K Chavez, husband</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260581969.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584023.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260581969.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584023.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584023.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260584072</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dbcs Inc., an Arizona Corporation</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>700,000.00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5420 W. Onyx Ave.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85302</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>219-38</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arizona Dept. of Real Estate.</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(202) 500-0435</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Dbcs Inc., an Arizona</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Corporation</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584072.pdf</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584072.pdf</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>ocr_used</t>
         </is>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG26" t="n">
         <v>100</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260581969.txt</t>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584072.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260584073</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Maria G Reyes Santillano, a single woman</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>158,950.00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6208 S 12th St</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85042</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>105-70-047</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(202) 402-7620</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Maria G Reyes Santillano, a single</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584073.pdf</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584073.pdf</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584073.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260584074</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Juan M Martinez Quintana, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>228,450.00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3 S 28th Dr</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>109-44-054</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(202) 404-7149</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Juan M Martinez Quintana, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584074.pdf</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584074.pdf</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584074.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260584175</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>262,500.00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2424 N 114TH LN</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85392</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(270) 058-1504</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584175.pdf</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584175.pdf</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584175.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260584191</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>124,500.00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>17631 N. 114TH LANE</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85378</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(201) 604-2675</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584191.pdf</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584191.pdf</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584191.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH30"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -423,10 +423,10 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="53" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="50" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="52" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="58" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="42" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260582075</t>
+          <t>20260584393</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,11 +650,7 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>(s): Black Rock Elite Properties, Llc</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -664,12 +660,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8659 E ROANOKE AVENUE</t>
+          <t>9457 N 110TH AVENUE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -679,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85257</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,67 +689,59 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>131-41-063</t>
+          <t>142-70-631</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>NanciaNnc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 206-0862</t>
+          <t>(202) 200-7558</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>(s): Black Rock Elite Properties,</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Llc</t>
-        </is>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582075.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584393.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582075.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584393.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582075.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584393.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260582119</t>
+          <t>20260584463</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -763,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -776,17 +764,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Charles Morrison</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>294,880.00</t>
+          <t>281,898.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3029 W PARADISE DR</t>
+          <t>or IDENTIFIABLE LOCATION: 3307 W PALM LN</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -801,7 +793,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -815,59 +807,67 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>149-20-074</t>
+          <t>108-25-008</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>will require any entity or trust bidder at this trustee's sale to provide beneficial</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(844) 093-4761</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Charles</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Morrison</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582119.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584463.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582119.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584463.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582119.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584463.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260582301</t>
+          <t>20260584464</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -890,22 +890,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(s)) in favor of Wells</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>338,402.00</t>
+          <t>371,692.04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>or identifiable location: 4946 W CHARLESTON AVE</t>
+          <t>9427 W. Willowbrook Dr</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -915,7 +919,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85308</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -927,61 +931,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>207-23-349</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2024-02-08</t>
-        </is>
-      </c>
+          <t>(200) 910-1998</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>(s)) in favor of</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Wells</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582301.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584464.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582301.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584464.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_trustee, missing_apn, missing_auction_date</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582301.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584464.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260582308</t>
+          <t>20260584471</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1008,18 +1008,18 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>473,398.00</t>
+          <t>411,391.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>or identifiable location: 30182 WEST MULBERRY DRIVE</t>
+          <t>1545 W CARMEN ST</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>85041</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1043,23 +1043,23 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>504-74-542</t>
+          <t>300-52-205</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 112-6760</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582308.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584471.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582308.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584471.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1088,14 +1088,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582308.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584471.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260582345</t>
+          <t>20260584512</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1122,14 +1122,30 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>518,059.00</t>
+          <t>318,500.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2035 E BETHANY HOME RD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85016</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1141,30 +1157,26 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>102-56-439</t>
+          <t>164-48</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(201) 106-0203</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1172,32 +1184,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582345.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584512.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582345.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584512.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582345.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584512.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260582458</t>
+          <t>20260584595</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1207,7 +1219,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1224,18 +1236,18 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>459,685.00</t>
+          <t>88,000.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>or identifiable location: 1015 S 150TH DR</t>
+          <t>5220 S 20TH PL</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Goodyear</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1245,7 +1257,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85338</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1259,18 +1271,18 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>500-10-327</t>
+          <t>122-52</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(200) 911-9990</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1286,12 +1298,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582458.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584595.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582458.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584595.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1304,14 +1316,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582458.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584595.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260582614</t>
+          <t>20260584762</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1321,7 +1333,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1334,22 +1346,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>John A. Jamieson and Ellen Jamieson, husband and wife</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>525,299.00</t>
+          <t>210,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>or identifiable location: 9441 W HEATHERBRAE DR</t>
+          <t>20473 North 105th Avenue</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1359,7 +1375,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85037</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1373,59 +1389,75 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>102-25-549</t>
+          <t>200-14-058</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 207-6822</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>John A.</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Jamieson</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Ellen Jamieson, husband and</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582614.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584762.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582614.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584762.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582614.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584762.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260582829</t>
+          <t>20260584844</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1435,7 +1467,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1450,20 +1482,36 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(s): Phyllis White-Robbins, unmarried woman</t>
+          <t>Edward R Hamm Jr, Barbara Hamm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>376,322.00</t>
+          <t>50,000.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4554 E Paradise Village Pkwy N, #254</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1475,34 +1523,26 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>220-36-137</t>
+          <t>167-15-124</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(202) 402-9442</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
+          <t>(201) 906-1706</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>(s): Phyllis White-Robbins, unmarried</t>
+          <t>Edward R Hamm Jr, Barbara</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>Hamm</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -1510,17 +1550,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582829.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584844.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582829.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584844.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1528,14 +1568,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582829.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584844.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260582840</t>
+          <t>20260585088</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1545,7 +1585,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1562,18 +1602,18 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>473,259.00</t>
+          <t>343,660.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>or identifiable location: 12540 W TRUMBULL RD</t>
+          <t>or identifiable location: 2821 North 52nd Avenue</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1583,7 +1623,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1597,13 +1637,13 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>500-72-135</t>
+          <t>103-54-079</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1613,7 +1653,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1624,12 +1664,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260582840.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585088.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260582840.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585088.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1642,14 +1682,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260582840.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585088.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260583065</t>
+          <t>20260585129</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1659,7 +1699,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1674,24 +1714,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(s): Michelle Marie Devine, an unmarried woman</t>
+          <t>Sbl Real Estate, Llc, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>117,978.00</t>
+          <t>5,295,795.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4742 W LAURIE LANE</t>
+          <t>The Deed of Trust and/or Beneficiary provide the following Purported property location: 715 E Beloat Road</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1701,7 +1741,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85302</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1713,36 +1753,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>148-12-120-1</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>First American Title Insurance Company, 9255 Towne</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(201) 000-6444</t>
+          <t>(202) 403-1117</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>(s): Michelle Marie Devine, an unmarried</t>
+          <t>Sbl Real Estate, Llc, an Arizona limited liability</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>company</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -1750,32 +1786,32 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583065.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585129.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583065.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585129.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583065.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585129.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260583066</t>
+          <t>20260585286</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1785,7 +1821,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1798,26 +1834,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>(s): Janet Monahan, an unmarried person</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>335,620.00</t>
+          <t>729,969.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6530 W NORTH LN</t>
+          <t>24534 W MARK LANE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Wittmann</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1827,7 +1859,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85302</t>
+          <t>85361</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1841,67 +1873,59 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>143-49-486</t>
+          <t>503-32-143-6</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(202) 201-9784</t>
+          <t>(202) 500-7006</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>(s): Janet Monahan, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583066.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585286.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583066.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585286.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583066.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585286.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260583178</t>
+          <t>20260585409</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1911,7 +1935,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1924,22 +1948,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(s): Velta Leanna Swindle, and Billy Perry Swindle, wife</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>248,500.00</t>
+          <t>121,600.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>832 S 79TH WAY</t>
+          <t>30 W OVERLIN LN</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1949,7 +1977,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1963,59 +1991,75 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>218-54</t>
+          <t>500-50-005</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(202) 501-6905</t>
+          <t>(202) 605-8540</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>(s): Velta Leanna</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Swindle,</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Billy Perry Swindle,</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583178.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585409.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583178.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585409.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583178.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585409.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260583265</t>
+          <t>20260585499</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2025,7 +2069,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2040,36 +2084,20 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dalton Etherton, a single man, and Caitlin Elizabeth Gillis, a single woman, as joint tenants with</t>
+          <t>’s Stated Name and Address: 3518 W Dunlap Llc, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>551,610.00</t>
+          <t>6,026,000.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2081,71 +2109,71 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>303-27-788</t>
+          <t>149-39-466</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 404-5715</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
+          <t>(202) 002-1982</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Dalton Etherton, a single</t>
+          <t>’s Stated</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>man,</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Caitlin Elizabeth Gillis, a single woman, as joint tenants</t>
+          <t>Address: 3518 W Dunlap Llc, an Arizona limited liability</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>with</t>
+          <t>company</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583265.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585499.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583265.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585499.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_address, missing_auction_date</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583265.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585499.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260583391</t>
+          <t>20260585677</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2155,7 +2183,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2170,24 +2198,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(s): David Andrae De La O and Valerie P De La O</t>
+          <t>(s): Crystal Blackstock, an unmarried woman and Joseph</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>466,396.00</t>
+          <t>459,523.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12614 W ALEGRE DR</t>
+          <t>4001 W WOODRIDGE DR</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Litchfield Park</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2197,7 +2225,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85340</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2211,7 +2239,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>508-07-495</t>
+          <t>207-18-012</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2222,44 +2250,40 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 306-1359</t>
+          <t>(202) 500-6173</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>(s): David Andrae De La</t>
+          <t>(s): Crystal Blackstock, an unmarried</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Valerie P De La</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583391.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585677.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583391.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585677.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2272,14 +2296,14 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583391.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585677.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260583392</t>
+          <t>20260585683</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2289,7 +2313,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2304,24 +2328,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(s): Thomas G. Harrington &amp; Maryellen B. Harrington</t>
+          <t>(s): Christopher Russell Knope, Husband</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>417,000.00</t>
+          <t>50,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36707 N 24TH STREET</t>
+          <t>12016 W MORNING DOVE DR</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2331,7 +2355,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85086</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2345,55 +2369,47 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>211-67</t>
+          <t>503-88-808</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(200) 710-5325</t>
+          <t>(200) 762-9564</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>(s): Thomas G.</t>
+          <t>(s): Christopher Russell Knope,</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Harrington</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Maryellen B.</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Harrington</t>
-        </is>
-      </c>
+          <t>Husband</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583392.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585683.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583392.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585683.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2406,14 +2422,14 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583392.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585683.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260583632</t>
+          <t>20260585699</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2423,7 +2439,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2438,24 +2454,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(s): Richard May and Jacqueline Rose Vasquez-May</t>
+          <t>1417 W. Rose Lane</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>429,322.00</t>
+          <t>373,500.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11020 W PIERCE ST</t>
+          <t>Original Trustor: 1417 W. Rose Lane</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2465,7 +2481,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85013</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2479,55 +2495,47 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>102-56-456</t>
+          <t>110-27-075</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Burch &amp; Cracchiolo, P.A.</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(202) 202-6798</t>
+          <t>(202) 605-8569</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>(s): Richard</t>
+          <t>1417 W. Rose</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Jacqueline Rose</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Vasquez-May</t>
-        </is>
-      </c>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583632.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585699.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583632.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585699.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2540,14 +2548,14 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583632.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585699.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260583633</t>
+          <t>20260585720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2557,7 +2565,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2570,26 +2578,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>(s): Alexis Blandimir Mendez Rovelo And</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>359,370.00</t>
+          <t>280,321.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11197 W CORONADO RD</t>
+          <t>or identifiable location: 11275 N 99TH AVE LOT 102</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2599,7 +2603,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85392</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2613,67 +2617,63 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>102-30-590</t>
+          <t>142-52-141</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 503-1941</t>
+          <t>(202) 203-0809</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>(s): Alexis Blandimir Mendez Rovelo</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>And</t>
-        </is>
-      </c>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583633.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585720.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583633.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585720.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583633.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585720.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260583688</t>
+          <t>20260585721</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2696,26 +2696,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Luis Orozco, an single man</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>51,000.00</t>
+          <t>232,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>513 W Colgate Dr</t>
+          <t>2133 W MONROE ST</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2725,7 +2721,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2739,67 +2735,59 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>301-04-388</t>
+          <t>109-32-079</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Mtc Financial inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 306-5003</t>
+          <t>(202) 304-6572</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Luis Orozco, an single</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583688.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585721.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583688.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585721.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583688.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585721.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260583698</t>
+          <t>20260585749</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2809,7 +2797,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2822,26 +2810,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Miguel Aguirre, an unmarried man</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>330,382.00</t>
+          <t>412,392.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>or identifiable location: 18037 W ENCINAS LN</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Goodyear</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2851,7 +2835,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85338</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2865,67 +2849,63 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>116-12</t>
+          <t>502-45-535</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(202) 303-8193</t>
+          <t>(202) 403-2208</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Miguel Aguirre, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583698.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585749.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583698.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585749.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583698.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585749.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260583912</t>
+          <t>20260585935</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2935,7 +2915,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2950,19 +2930,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(s): Jessica Raffle And Lee Raffle, Wife And</t>
+          <t>Brett M. Biegler and Amber Mitchell-Biegler, husband and wife</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>126,750.00</t>
+          <t>580,000.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3050 W WETHERSFIELD RD</t>
+          <t>1815 W Cottonwood Lane</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2977,7 +2957,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>85045</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2991,47 +2971,55 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>149-41-118</t>
+          <t>311-02-876</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(200) 767-2276</t>
+          <t>(202) 204-2400</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>(s): Jessica Raffle And Lee Raffle, Wife</t>
+          <t>Brett M.</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>And</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+          <t>Biegler</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Amber Mitchell-Biegler, husband and</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583912.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585935.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583912.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585935.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3044,14 +3032,14 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583912.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585935.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260583913</t>
+          <t>20260586083</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3061,7 +3049,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3076,19 +3064,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(s)</t>
+          <t>Pgf Holdings Llc, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>298,400.00</t>
+          <t>195,500.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6402 WEST DEVONSHIRE AVENUE</t>
+          <t>6068 W Mulberry Dr</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3117,63 +3105,63 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>144-85-068</t>
+          <t>103-44-029</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(202) 406-8541</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2024-12-16</t>
-        </is>
-      </c>
+          <t>(202) 602-4037</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>(s)</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr"/>
+          <t>Pgf Holdings Llc, an Arizona limited liability</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583913.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586083.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583913.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586083.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_auction_date</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583913.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586083.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260583914</t>
+          <t>20260586090</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3183,7 +3171,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3198,24 +3186,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(s): Therese Margaret Brosnahan, A</t>
+          <t>(s): Emeline Ayuni And Olivier Maimo, Wife</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>215,000.00</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4335 W CARSON RD</t>
+          <t>2822 E CLIFTON CT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Laveen</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3225,7 +3213,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>85295</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3239,7 +3227,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>104-90-183</t>
+          <t>304-47-129</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3250,23 +3238,23 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(202) 201-0047</t>
+          <t>(202) 501-6560</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>(s): Therese Margaret Brosnahan,</t>
+          <t>(s): Emeline Ayuni And Olivier Maimo,</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3274,12 +3262,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583914.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586090.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583914.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586090.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3292,14 +3280,14 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583914.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586090.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260583917</t>
+          <t>20260586101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3309,7 +3297,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3322,38 +3310,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>(s): Barbara Jeanette Cowled, a married woman as her</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>385,000.00</t>
+          <t>540,000.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>3510 EAST KESLER LANE</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Gilbert</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>85295</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -3365,67 +3333,63 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>138-14</t>
+          <t>143-01-137</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Prestige Default Services, Llc</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(202) 204-9634</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>(s): Barbara Jeanette Cowled, a married woman as</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>her</t>
-        </is>
-      </c>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2022-05-18</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260583917.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586101.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260583917.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586101.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260583917.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586101.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260584023</t>
+          <t>20260586112</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3435,7 +3399,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3448,18 +3412,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>(s): Edward Guzman, A Single Man And</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>168,884.00</t>
+          <t>412,391.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>7138 W SUNNYSLOPE LN</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85345</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3471,59 +3455,67 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>144-15</t>
+          <t>143-10-244</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(202) 501-5569</t>
+          <t>(202) 500-3110</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>(s): Edward Guzman, A Single Man</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>And</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584023.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586112.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584023.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586112.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584023.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586112.txt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260584072</t>
+          <t>20260586113</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3533,7 +3525,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3548,24 +3540,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dbcs Inc., an Arizona Corporation</t>
+          <t>(s): Steven Nephi Smith and Devin Smith, Husband and</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>700,000.00</t>
+          <t>358,388.00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5420 W. Onyx Ave.</t>
+          <t>16835 W MANCHESTER DR</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3575,7 +3567,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>85302</t>
+          <t>85374</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3589,47 +3581,55 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>219-38</t>
+          <t>232-39-258</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Arizona Dept. of Real Estate.</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>(202) 500-0435</t>
+          <t>(202) 302-4833</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Dbcs Inc., an Arizona</t>
+          <t>(s): Steven Nephi</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Corporation</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Devin Smith, Husband</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584072.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586113.pdf</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584072.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586113.pdf</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584072.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586113.txt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260584073</t>
+          <t>20260586118</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3672,38 +3672,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Maria G Reyes Santillano, a single woman</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>158,950.00</t>
+          <t>344,760.00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>6208 S 12th St</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>85042</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -3715,63 +3695,63 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>105-70-047</t>
+          <t>502-84-781</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>(202) 402-7620</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Maria G Reyes Santillano, a single</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584073.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586118.pdf</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584073.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586118.pdf</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584073.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586118.txt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260584074</t>
+          <t>20260586126</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3781,7 +3761,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3794,38 +3774,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Juan M Martinez Quintana, an unmarried man</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>228,450.00</t>
+          <t>188,500.00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>3 S 28th Dr</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -3837,63 +3797,63 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>109-44-054</t>
+          <t>304-51-253</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>(202) 404-7149</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Juan M Martinez Quintana, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2020-01-13</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584074.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586126.pdf</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584074.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586126.pdf</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584074.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586126.txt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260584175</t>
+          <t>20260586153</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3903,7 +3863,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3920,18 +3880,18 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>262,500.00</t>
+          <t>323,380.00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2424 N 114TH LN</t>
+          <t>14356 W JENAN DR</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3941,7 +3901,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>85392</t>
+          <t>85379</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3962,12 +3922,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>(270) 058-1504</t>
+          <t>(201) 910-6068</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -3978,12 +3938,12 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584175.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586153.pdf</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584175.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586153.pdf</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3996,117 +3956,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584175.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20260584191</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>124,500.00</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>17631 N. 114TH LANE</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85378</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>(201) 604-2675</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584191.pdf</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584191.pdf</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584191.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586153.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH29"/>
+  <dimension ref="A1:AH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="52" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="58" customWidth="1" min="27" max="27"/>
+    <col width="49" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260584393</t>
+          <t>20260586590</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -654,18 +654,18 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>420,000.00</t>
+          <t>249,287.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9457 N 110TH AVENUE</t>
+          <t>10926 W DAVIS LN</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85351</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -689,18 +689,18 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>142-70-631</t>
+          <t>101-20-657</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>NanciaNnc. dba Trustee Corps</t>
+          <t>inangial|nc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 200-7558</t>
+          <t>(202) 002-0621</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -716,12 +716,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584393.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586590.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584393.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586590.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -734,14 +734,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584393.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586590.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260584463</t>
+          <t>20260586677</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,24 +766,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Charles Morrison</t>
+          <t>Dylan Guynn, an unmarried man and Madeleine Girouard, an unmarried woman</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>281,898.00</t>
+          <t>262,870.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 3307 W PALM LN</t>
+          <t>925 N College Ave Unit G225</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -807,67 +807,67 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>108-25-008</t>
+          <t>132-03-030</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
+          <t>(202) 113-2355</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Dylan Guynn, an unmarried</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Morrison</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Madeleine Girouard, an unmarried</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584463.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586677.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584463.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586677.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_trustee, missing_auction_date</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584463.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586677.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260584464</t>
+          <t>20260586806</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -890,26 +890,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(s)) in favor of Wells</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>371,692.04</t>
+          <t>197,047.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9427 W. Willowbrook Dr</t>
+          <t>or identifiable location: | 4828 WORANGEWOOD AVE 214</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sun City</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -919,7 +915,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85373</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -931,57 +927,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>147-03-616</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(200) 910-1998</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>(s)) in favor of</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Wells</t>
-        </is>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584464.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586806.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584464.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586806.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_apn, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584464.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586806.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260584471</t>
+          <t>20260586980</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1004,34 +1004,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tlh 98" Llc, an Arizona limited liability company</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>411,391.00</t>
+          <t>198,750.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1545 W CARMEN ST</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1043,59 +1031,67 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>300-52-205</t>
+          <t>200-55-282</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(202) 112-6760</t>
+          <t>(202) 605-8698</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Tlh 98" Llc, an Arizona limited liability</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584471.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586980.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584471.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586980.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584471.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586980.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260584512</t>
+          <t>20260587096</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1122,30 +1118,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>318,500.00</t>
+          <t>405,307.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2035 E BETHANY HOME RD</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>85016</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1157,18 +1137,18 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>164-48</t>
+          <t>101-41-467</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(201) 106-0203</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1184,32 +1164,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584512.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587096.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584512.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587096.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584512.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587096.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260584595</t>
+          <t>20260587208</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1219,7 +1199,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1236,13 +1216,13 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>88,000.00</t>
+          <t>382,580.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5220 S 20TH PL</t>
+          <t>or identifiable location: | 9346 West Willow Bend Ln</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1257,7 +1237,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85037</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1271,18 +1251,18 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>122-52</t>
+          <t>102-25-192</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(200) 911-9990</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1298,12 +1278,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584595.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587208.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584595.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587208.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1316,14 +1296,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584595.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587208.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260584762</t>
+          <t>20260587224</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1333,7 +1313,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1346,26 +1326,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>John A. Jamieson and Ellen Jamieson, husband and wife</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>210,000.00</t>
+          <t>395,996.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20473 North 105th Avenue</t>
+          <t>or identifiable location: 240 W JUNIPER AVE, UNIT 1012</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1375,7 +1351,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85382</t>
+          <t>85233</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1389,75 +1365,59 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>200-14-058</t>
+          <t>302-15-090</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(202) 207-6822</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>John A.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Jamieson</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Ellen Jamieson, husband and</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584762.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587224.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584762.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587224.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584762.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587224.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260584844</t>
+          <t>20260587269</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1467,7 +1427,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1480,26 +1440,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Edward R Hamm Jr, Barbara Hamm</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50,000.00</t>
+          <t>355,946.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4554 E Paradise Village Pkwy N, #254</t>
+          <t>or identifiable location: 18527 W CINNABAR AVE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Waddell</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1509,7 +1465,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85032</t>
+          <t>85355</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1523,59 +1479,59 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>167-15-124</t>
+          <t>502-90-461</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(201) 906-1706</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Edward R Hamm Jr, Barbara</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Hamm</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260584844.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587269.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260584844.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587269.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260584844.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587269.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260585088</t>
+          <t>20260587272</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1585,7 +1541,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1602,18 +1558,18 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>343,660.00</t>
+          <t>417,500.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>or identifiable location: 2821 North 52nd Avenue</t>
+          <t>or identifiable location: 19341 W ANNIKA DR</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Litchfield Park</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1623,7 +1579,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85035</t>
+          <t>85340</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1637,13 +1593,13 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>103-54-079</t>
+          <t>502-40-573</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1653,7 +1609,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1664,12 +1620,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585088.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587272.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585088.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587272.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1682,14 +1638,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585088.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587272.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260585129</t>
+          <t>20260587305</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1699,7 +1655,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1712,26 +1668,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sbl Real Estate, Llc, an Arizona limited liability company</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5,295,795.00</t>
+          <t>221,000.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>The Deed of Trust and/or Beneficiary provide the following Purported property location: 715 E Beloat Road</t>
+          <t>10909 W KAIBAB DR</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1741,7 +1693,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1753,65 +1705,61 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>230-05-419</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>First American Title Insurance Company, 9255 Towne</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(202) 403-1117</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Sbl Real Estate, Llc, an Arizona limited liability</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585129.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587305.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585129.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587305.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used, missing_apn</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585129.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587305.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260585286</t>
+          <t>20260587406</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1821,7 +1769,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1838,18 +1786,18 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>729,969.00</t>
+          <t>308,312.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24534 W MARK LANE</t>
+          <t>or identifiable location: 4707 NORTH 23RD DRIVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wittmann</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1859,7 +1807,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85361</t>
+          <t>85015</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1873,23 +1821,23 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>503-32-143-6</t>
+          <t>154-03-007</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>before a trustee’s deed will be issued for covered</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(202) 500-7006</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1900,12 +1848,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585286.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587406.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585286.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587406.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1918,14 +1866,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585286.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587406.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260585409</t>
+          <t>20260587441</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1935,7 +1883,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1950,24 +1898,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(s): Velta Leanna Swindle, and Billy Perry Swindle, wife</t>
+          <t>1417 W. Rose Lane</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>121,600.00</t>
+          <t>373,500.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30 W OVERLIN LN</t>
+          <t>Original Trustor: 1417 W. Rose Lane</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1977,7 +1925,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85013</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1991,55 +1939,47 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>500-50-005</t>
+          <t>110-27-075</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Burch &amp; Cracchiolo, P.A.</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(202) 605-8540</t>
+          <t>(202) 605-8744</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>(s): Velta Leanna</t>
+          <t>1417 W. Rose</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Swindle,</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Billy Perry Swindle,</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>wife</t>
-        </is>
-      </c>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585409.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587441.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585409.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587441.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2052,14 +1992,14 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585409.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587441.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260585499</t>
+          <t>20260587482</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2069,7 +2009,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2084,13 +2024,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>’s Stated Name and Address: 3518 W Dunlap Llc, an Arizona limited liability company</t>
+          <t>Plv Steel, Llc, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6,026,000.00</t>
+          <t>110,000.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2109,71 +2049,67 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>149-39-466</t>
+          <t>401-40</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(202) 002-1982</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
+          <t>(202) 605-8748</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>’s Stated</t>
+          <t>Plv Steel, Llc, an Arizona limited liability</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Address: 3518 W Dunlap Llc, an Arizona limited liability</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
           <t>company</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585499.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587482.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585499.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587482.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_auction_date</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585499.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587482.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260585677</t>
+          <t>20260587483</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2183,7 +2119,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2198,36 +2134,20 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(s): Crystal Blackstock, an unmarried woman and Joseph</t>
+          <t>Pfg Holdings, Llc, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>459,523.00</t>
+          <t>270,000.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>4001 W WOODRIDGE DR</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>85308</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2239,71 +2159,67 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>207-18-012</t>
+          <t>142-90-164</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 500-6173</t>
+          <t>(202) 605-8748</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>(s): Crystal Blackstock, an unmarried</t>
+          <t>Pfg Holdings, Llc, an Arizona limited liability</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585677.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587483.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585677.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587483.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585677.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587483.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260585683</t>
+          <t>20260587500</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2313,7 +2229,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2328,36 +2244,20 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(s): Christopher Russell Knope, Husband</t>
+          <t>Ezequiel Felix, an unmarried man</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>50,000.00</t>
+          <t>155,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>12016 W MORNING DOVE DR</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Sun City</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>85373</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -2369,34 +2269,34 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>503-88-808</t>
+          <t>144-24-375</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(200) 762-9564</t>
+          <t>(202) 605-8750</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>(s): Christopher Russell Knope,</t>
+          <t>Ezequiel Felix, an unmarried</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>man</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
@@ -2404,32 +2304,32 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585683.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587500.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585683.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587500.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585683.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587500.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260585699</t>
+          <t>20260587585</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2439,7 +2339,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2454,24 +2354,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1417 W. Rose Lane</t>
+          <t>Kathleen Semder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>373,500.00</t>
+          <t>128,050.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Original Trustor: 1417 W. Rose Lane</t>
+          <t>or IDENTIFIABLE LOCATION: 8623 WEST KEIM DRIVE</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2481,7 +2381,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85013</t>
+          <t>85305</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2495,34 +2395,34 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>110-27-075</t>
+          <t>102-04-621</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Burch &amp; Cracchiolo, P.A.</t>
+          <t>/Sucdessor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(202) 605-8569</t>
+          <t>(200) 908-0419</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1417 W. Rose</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Semder</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2530,12 +2430,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585699.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587585.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585699.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587585.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2548,14 +2448,14 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585699.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587585.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260585720</t>
+          <t>20260587685</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2565,7 +2465,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2578,34 +2478,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Alis G Ramirez and Alba Aldama, a married couple</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>280,321.00</t>
+          <t>51,900.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>or identifiable location: 11275 N 99TH AVE LOT 102</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Peoria</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>85345</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2617,63 +2505,75 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>142-52-141</t>
+          <t>506-40</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>(202) 203-0809</t>
+          <t>(202) 605-8768</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2022-04-05</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Alis G</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Alba Aldama, a married</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>couple</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585720.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587685.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585720.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587685.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585720.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587685.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260585721</t>
+          <t>20260587710</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2683,7 +2583,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2696,34 +2596,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Alis G Ramirez and Alba Aldama, a married couple</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>232,000.00</t>
+          <t>99,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2133 W MONROE ST</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2735,59 +2623,75 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>109-32-079</t>
+          <t>506-40</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Mtc Financial inc. dba Trustee Corps</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(202) 304-6572</t>
+          <t>(202) 605-8771</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Alis G</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Alba Aldama, a married</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>couple</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585721.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587710.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585721.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587710.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585721.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587710.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260585749</t>
+          <t>20260587746</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2797,7 +2701,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2810,22 +2714,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Alan M Figura And Zena-Alicia Y Rosa</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>412,392.00</t>
+          <t>342,359.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>or identifiable location: 18037 W ENCINAS LN</t>
+          <t>3707 East Southern Avenue</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Goodyear</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2835,7 +2743,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85338</t>
+          <t>85206</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2849,63 +2757,67 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>502-45-535</t>
+          <t>503-56-620</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>(202) 403-2208</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Alan M Figura And Zena-Alicia Y</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585749.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587746.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585749.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587746.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585749.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587746.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260585935</t>
+          <t>20260587816</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2915,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2930,36 +2842,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brett M. Biegler and Amber Mitchell-Biegler, husband and wife</t>
+          <t>Alis G Ramirez and Alba Aldama, a married couple</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>580,000.00</t>
+          <t>99,000.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1815 W Cottonwood Lane</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>85045</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -2971,75 +2867,75 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>311-02-876</t>
+          <t>506-40</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(202) 204-2400</t>
+          <t>(202) 605-8781</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Brett M.</t>
+          <t>Alis G</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Biegler</t>
+          <t>Ramirez</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Amber Mitchell-Biegler, husband and</t>
+          <t>Alba Aldama, a married</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>wife</t>
+          <t>couple</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260585935.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587816.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260585935.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587816.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260585935.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587816.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260586083</t>
+          <t>20260587819</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3049,7 +2945,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3064,19 +2960,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pgf Holdings Llc, an Arizona limited liability company</t>
+          <t>Colin Kane</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>195,500.00</t>
+          <t>315,980.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6068 W Mulberry Dr</t>
+          <t>or IDENTIFIABLE LOCATION: 1920 E BELL ROAD UNIT 1053</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3091,7 +2987,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85033</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3105,30 +3001,34 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>103-44-029</t>
+          <t>214-09-781</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>(202) 602-4037</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Pgf Holdings Llc, an Arizona limited liability</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
@@ -3136,32 +3036,32 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586083.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587819.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586083.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587819.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586083.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587819.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260586090</t>
+          <t>20260587831</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3171,7 +3071,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3186,24 +3086,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(s): Emeline Ayuni And Olivier Maimo, Wife</t>
+          <t>Douglas Mcfarland And Sherry Moore-Adams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>350,000.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2822 E CLIFTON CT</t>
+          <t>or IDENTIFIABLE LOCATION: 8925 E STONEY VISTA DR</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Sun Lakes</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3213,7 +3113,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85295</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3227,34 +3127,34 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>304-47-129</t>
+          <t>303-78-445</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>(202) 501-6560</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>(s): Emeline Ayuni And Olivier Maimo,</t>
+          <t>Douglas Mcfarland And Sherry</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Moore-Adams</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3262,12 +3162,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586090.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587831.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586090.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587831.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3280,14 +3180,14 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586090.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587831.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260586101</t>
+          <t>20260587846</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3297,7 +3197,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3310,11 +3210,15 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Alis G Ramirez and Alba Aldama, a married couple</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>540,000.00</t>
+          <t>58,500.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3333,63 +3237,75 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>143-01-137</t>
+          <t>506-40</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(202) 605-8784</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Alis G</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Alba Aldama, a married</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>couple</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586101.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587846.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586101.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587846.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586101.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587846.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260586112</t>
+          <t>20260587848</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3399,7 +3315,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3414,36 +3330,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(s): Edward Guzman, A Single Man And</t>
+          <t>Alisa G Ramirez and Alba Aldama, a married couple</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>412,391.00</t>
+          <t>81,000.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>7138 W SUNNYSLOPE LN</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Peoria</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85345</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3455,67 +3355,75 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>143-10-244</t>
+          <t>506-40</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(202) 500-3110</t>
+          <t>(202) 605-8784</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>(s): Edward Guzman, A Single Man</t>
+          <t>Alisa G</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>And</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Alba Aldama, a married</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>couple</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586112.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587848.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586112.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587848.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_address</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586112.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587848.txt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260586113</t>
+          <t>20260587863</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3525,7 +3433,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3540,24 +3448,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(s): Steven Nephi Smith and Devin Smith, Husband and</t>
+          <t>(s): Devon Gage Martin Gage H Wife And</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>358,388.00</t>
+          <t>50,000.00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>16835 W MANCHESTER DR</t>
+          <t>15308 N PABLO CT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>El Mirage</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3567,7 +3475,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>85374</t>
+          <t>85335</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3581,7 +3489,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>232-39-258</t>
+          <t>501-25-648</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3592,44 +3500,36 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>(202) 302-4833</t>
+          <t>(200) 765-7862</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>(s): Steven Nephi</t>
+          <t>(s): Devon Gage Martin Gage H Wife</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Devin Smith, Husband</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
+          <t>And</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586113.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587863.pdf</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586113.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587863.pdf</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3642,14 +3542,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586113.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587863.txt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260586118</t>
+          <t>20260587866</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3659,7 +3559,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3672,18 +3572,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>(s): Brent R Bengtson, An Unmarried Man</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>344,760.00</t>
+          <t>99,000.00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4521 E JOAN DE ARC AVE</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -3693,65 +3613,65 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>502-84-781</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(200) 765-7863</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>(s): Brent R Bengtson, An Unmarried</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586118.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587866.pdf</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586118.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587866.pdf</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586118.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587866.txt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260586126</t>
+          <t>20260587931</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3761,7 +3681,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3778,14 +3698,30 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>188,500.00</t>
+          <t>35,000.00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>or identifiable location: 722 W KINGS AVE</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85023</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -3797,28 +3733,28 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>304-51-253</t>
+          <t>208-13-625</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Prestige Default Services, Llc</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>(949) 427-2010</t>
+          <t>(200) 755-0954</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2020-01-13</t>
+          <t>2023-02-16</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -3828,32 +3764,32 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586126.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260587931.pdf</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586126.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260587931.pdf</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586126.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260587931.txt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260586153</t>
+          <t>20260588153</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3863,7 +3799,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3876,22 +3812,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bruce Anson</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>323,380.00</t>
+          <t>1,724,737.50</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14356 W JENAN DR</t>
+          <t>or IDENTIFIABLE LOCATION: 8218 E GRAY ROAD</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3901,7 +3841,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>85260</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3913,50 +3853,778 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>215-54</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>(201) 910-6068</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Anson</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260586153.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260588153.pdf</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260586153.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260588153.pdf</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260588153.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260588297</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Cindy Greenwood, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>177,045.00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>218-18-028</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, i is regulated by and</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(200) 760-9765</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Cindy Greenwood, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260588297.pdf</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260588297.pdf</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>60</v>
       </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260586153.txt</t>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260588297.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260588304</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Anna R Divich, a single woman</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>299,000.00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2207 E Donald Dr</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85024</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>213-03-271</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(202) 103-4590</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Anna R Divich, a single</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260588304.pdf</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260588304.pdf</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260588304.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260588313</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ignacio Natael Castaneda, a married man</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>220,914.00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>505 Cahan Drive</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Morristown</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85342</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>503-86-133</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(202) 202-9172</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Ignacio Natael Castaneda, a married</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260588313.pdf</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260588313.pdf</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260588313.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260588358</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jeanette D Villines</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>123,619.00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 4560 N 29TH AVE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>85017</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>154-10-043</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Jeanette D</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Villines</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260588358.pdf</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260588358.pdf</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260588358.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260588361</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>James Rudd, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>208,000.00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>16631 South 22nd Street</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85048</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>308-18-085</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(202) 007-5477</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>James Rudd, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260588361.pdf</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260588361.pdf</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260588361.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260588567</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>104,900.00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>10436 W DEANNE DR</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Sun City</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>142-82-374</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kinancial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>(202) 300-9464</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260588567.pdf</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260588567.pdf</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260588567.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,20 +413,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -436,20 +436,20 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +621,1328 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>raw_text_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260589337</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>423,990.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>or identifiable location: 24413 W RAYMOND STREET</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>504-24-709</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(888) 403-4115</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260589337.pdf</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260589337.pdf</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260589337.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260590066</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Julie Sinykin and Jason W Sinykin, 505 West Knox Road, Chandler, Az 85225</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24,400.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>505 West Knox Road</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85225</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>302-44-327</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Sinykin</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Jason W Sinykin, 505 West Knox Road, Chandler, Az</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>85225</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590066.pdf</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590066.pdf</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590066.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260590233</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>586,500.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 10221 EAST SPRING CREEK ROAD</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sun Lakes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85248</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>303-60-894</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590233.pdf</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590233.pdf</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590233.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260590330</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>346,606.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>or identifiable location: 15263 W BANFF LN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85379</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>501-95-153</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(202) 402-8720</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590330.pdf</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590330.pdf</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590330.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260590337</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Maria Dolores Ballesteros Montano, Estefani Montano And Melissa Sanchez</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>336,787.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 16681 W TASHA DR</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85388</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>509-04-434</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Maria Dolores Ballesteros Montano, Estefani Montano And Melissa</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Sanchez</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590337.pdf</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590337.pdf</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590337.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260590362</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>William Carter</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>504,000.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 5316 N 186TH DR</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Litchfield Park</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85340</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>502-27-716</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Carter</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590362.pdf</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590362.pdf</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590362.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260590572</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>750,000.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>or identifiable location: 1421 E HUBBELL ST</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85006</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>117-18-087</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(202) 532-8040</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590572.pdf</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590572.pdf</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590572.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260590736</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ike S Paik, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>300,000.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14532 West Crocus Drive</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85379</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>509-03-398</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>/Successor Trustee, is regulated by and</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(202) 300-9095</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Ike S Paik, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590736.pdf</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590736.pdf</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590736.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260591015</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>265,109.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17881 W HUBBARD DR</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Goodyear</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>400-52-810</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>inancial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(202) 001-1780</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591015.pdf</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591015.pdf</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591015.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260591046</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Joan L. Tylitzki</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>502,500.00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 14228 N 26TH LN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85023</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>208-32-691</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Joan L.</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Tylitzki</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591046.pdf</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591046.pdf</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591046.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260591047</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/TR SALE+</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>’s Stated Name and Address: CRH-Tempe, Llc, 901 S. 70th Street, West Allis, Wi 53214</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1,472,250.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>(201) 800-8286</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>’s Stated</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Address: CRH-Tempe, Llc, 901 S. 70th Street, West Allis, Wi</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>53214</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591047.pdf</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591047.pdf</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591047.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,7 +425,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="51" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -442,7 +442,7 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="60" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260589337</t>
+          <t>20260591378</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -654,18 +654,18 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>423,990.00</t>
+          <t>369,000.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>or identifiable location: 24413 W RAYMOND STREET</t>
+          <t>526 S NORFOLK CIR</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85206</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -689,18 +689,18 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>504-24-709</t>
+          <t>140-37-152</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 011-5833</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -716,12 +716,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260589337.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591378.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260589337.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591378.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -734,14 +734,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260589337.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591378.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260590066</t>
+          <t>20260591424</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,24 +766,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Julie Sinykin and Jason W Sinykin, 505 West Knox Road, Chandler, Az 85225</t>
+          <t>Regina L Castaneda, an unmarried woman</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24,400.00</t>
+          <t>358,388.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>505 West Knox Road</t>
+          <t>23799 W Magnolia Dr</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -807,51 +807,43 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>302-44-327</t>
+          <t>504-28-586</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+          <t>/Successor Trustee, is regulated by and</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
+          <t>(202) 200-5973</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Regina L Castaneda, an unmarried</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Sinykin</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Jason W Sinykin, 505 West Knox Road, Chandler, Az</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>85225</t>
-        </is>
-      </c>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590066.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591424.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590066.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591424.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -864,14 +856,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590066.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591424.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260590233</t>
+          <t>20260591439</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -881,7 +873,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -898,18 +890,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>586,500.00</t>
+          <t>263,145.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 10221 EAST SPRING CREEK ROAD</t>
+          <t>17227 N 16TH DR, UNIT 12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sun Lakes</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -919,7 +911,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85248</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -933,23 +925,23 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>303-60-894</t>
+          <t>208-08-504</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -960,12 +952,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590233.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591439.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590233.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591439.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -978,14 +970,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590233.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591439.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260590330</t>
+          <t>20260591906</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -995,7 +987,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1008,22 +1000,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Richard Montemayor Jr, a single man</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>346,606.00</t>
+          <t>226,816.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>or identifiable location: 15263 W BANFF LN</t>
+          <t>680 North Delaware Street</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Chandler</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1033,7 +1029,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>85225</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1047,63 +1043,63 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>501-95-153</t>
+          <t>302-66-100</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(202) 402-8720</t>
+          <t>(200) 775-0839</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Richard Montemayor Jr, a single</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590330.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591906.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590330.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591906.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590330.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591906.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260590337</t>
+          <t>20260591920</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1113,7 +1109,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1126,38 +1122,18 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Maria Dolores Ballesteros Montano, Estefani Montano And Melissa Sanchez</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>336,787.00</t>
+          <t>235,873.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>or IDENTIFIABLE LOCATION: 16681 W TASHA DR</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>85388</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1169,67 +1145,59 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>509-04-434</t>
+          <t>304-23-450</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Maria Dolores Ballesteros Montano, Estefani Montano And Melissa</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Sanchez</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590337.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591920.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590337.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591920.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_address</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590337.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591920.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260590362</t>
+          <t>20260591994</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1239,7 +1207,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1252,26 +1220,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>William Carter</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>504,000.00</t>
+          <t>305,000.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 5316 N 186TH DR</t>
+          <t>or identifiable location: 1610 W VILLAGE WAY</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Litchfield Park</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1281,7 +1245,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85340</t>
+          <t>85282</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1293,69 +1257,57 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>502-27-716</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>William</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Carter</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590362.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591994.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590362.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591994.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner, missing_apn</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590362.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591994.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260590572</t>
+          <t>20260592053</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1365,7 +1317,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1382,18 +1334,18 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>750,000.00</t>
+          <t>473,000.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>or identifiable location: 1421 E HUBBELL ST</t>
+          <t>or identifiable location: | 4015 W SOFT WIND DR</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1403,7 +1355,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85006</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1417,7 +1369,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>117-18-087</t>
+          <t>205-11-090</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1428,19 +1380,15 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(202) 532-8040</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1448,12 +1396,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590572.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592053.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590572.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592053.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1466,14 +1414,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590572.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592053.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260590736</t>
+          <t>20260592191</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1483,7 +1431,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1496,26 +1444,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ike S Paik, an unmarried man</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>300,000.00</t>
+          <t>350,834.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14532 West Crocus Drive</t>
+          <t>or identifiable location: 10628 W ANGELS LN</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1525,7 +1469,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>85383</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1539,67 +1483,59 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>509-03-398</t>
+          <t>200-10-252</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(202) 300-9095</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Ike S Paik, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260590736.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592191.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260590736.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592191.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260590736.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592191.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260591015</t>
+          <t>20260592314</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1609,7 +1545,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1626,18 +1562,18 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>265,109.00</t>
+          <t>372,362.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17881 W HUBBARD DR</t>
+          <t>or identifiable location: 24519 W ILLINI STREET</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Goodyear</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1647,7 +1583,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85338</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1661,23 +1597,23 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>400-52-810</t>
+          <t>504-24-570</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>inancial Inc. dba Trustee Corps</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(202) 001-1780</t>
+          <t>(888) 403-4115</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1688,12 +1624,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591015.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592314.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591015.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592314.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1706,14 +1642,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591015.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592314.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260591046</t>
+          <t>20260592447</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1723,7 +1659,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1736,26 +1672,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Joan L. Tylitzki</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>502,500.00</t>
+          <t>200,000.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 14228 N 26TH LN</t>
+          <t>or identifiable location: 5396 N 82nd Ave</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1765,7 +1697,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85023</t>
+          <t>85303</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1779,77 +1711,73 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>208-32-691</t>
+          <t>102-09-250</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(226) 081-3118</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Joan L.</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Tylitzki</t>
-        </is>
-      </c>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591046.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592447.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591046.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592447.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591046.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592447.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260591047</t>
+          <t>20260592456</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>N/TR SALE+</t>
+          <t>N/TR SALE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1862,22 +1790,34 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>’s Stated Name and Address: CRH-Tempe, Llc, 901 S. 70th Street, West Allis, Wi 53214</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1,472,250.00</t>
+          <t>35,000.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>or identifiable 13135 W CARIBBEAN LN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85379</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1887,62 +1827,2634 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>501-94-099</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+          <t>may require entity or trust bidders at this trustee's sale to provide</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(201) 800-8286</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>’s Stated</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Address: CRH-Tempe, Llc, 901 S. 70th Street, West Allis, Wi</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>53214</t>
-        </is>
-      </c>
+          <t>(226) 092-5136</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2006-07-17</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591047.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592456.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591047.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592456.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_used, missing_address, missing_apn, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592456.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260592710</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Erik Alejandro Maldonado And Vanessa Elizabeth</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>940,006.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 3816 W WHITE FEATHER LN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85083</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>205-05-048</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Erik Alejandro Maldonado And Vanessa</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592710.pdf</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592710.pdf</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592710.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260592771</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jose O. Reyes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>525,000.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 366 W ELGIN STREET</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85225</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>303-19-0401</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Jose O.</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592771.pdf</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592771.pdf</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592771.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260592785</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>305,620.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19613 W MORNING GLORY ST</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>502-35-748</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(202) 204-0942</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592785.pdf</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592785.pdf</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592785.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260593126</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>238,843.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>200-82-462</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(202) 301-8541</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593126.pdf</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593126.pdf</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>45</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591047.txt</t>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593126.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260593144</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(s): Joseph Grunhut, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2,210,000.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>7240 E SWEETWATER AVE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85260</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>175-04-042</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(202) 400-4568</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>(s): Joseph Grunhut, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593144.pdf</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593144.pdf</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593144.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260593186</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jeremy Sario, an unmarried man, 15612 North 8th Street, Phoenix, Az 85022</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>335,047.00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>15612 North 8th Street</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>214-17-173</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jason P. Sherman, 2390 E. Camelback Road, Suite 130, Pmb</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Jeremy Sario, an unmarried man, 15612 North 8th Street, Phoenix, Az</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593186.pdf</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593186.pdf</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593186.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260593222</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(s): Delilah Martinez, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>178,703.00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1124 W PAMPA AVE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85210</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>302-77-236</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(201) 208-0917</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>(s): Delilah Martinez, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593222.pdf</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593222.pdf</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593222.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260593225</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>(s): Jose Gregorio Herrera Solorzano and Yennifer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>534,340.00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1643 E WILDHORSE PL</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>85286</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>303-29-429</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(202) 402-2441</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>(s): Jose Gregorio Herrera</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Solorzano</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Yennifer</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593225.pdf</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593225.pdf</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593225.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260593269</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>493,000.00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>304-90-226</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(800) 683-2468</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2019-07-23</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593269.pdf</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593269.pdf</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593269.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260593279</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>137,464.00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6618 W Flower Street</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85033</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>103-50-078</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(800) 280-2832</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2017-10-02</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593279.pdf</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593279.pdf</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593279.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260593430</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>335,000.00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15604 S 7TH ST</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85048</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>(200) 766-5333</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593430.pdf</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593430.pdf</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593430.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260593499</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>546,840.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>13319 W STELLA LN</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Litchfield Park</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85340</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(202) 405-8879</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593499.pdf</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593499.pdf</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593499.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260593562</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>339,845.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>or identifiable location: 8900 W GREER AVE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85345</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>142-453-173</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(202) 202-3779</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2022-03-11</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593562.pdf</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593562.pdf</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593562.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260593664</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>368,207.00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4213 W NICOLET AVE</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(200) 736-8197</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593664.pdf</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593664.pdf</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593664.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260593677</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>518,925.00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1850 E CONCORDA DR</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Tempe</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85282</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee’s capacity as a licensed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(202) 402-9348</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593677.pdf</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593677.pdf</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593677.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260593780</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(s): Dorian Reyes, An Unmarried Man</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>255,290.00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5554 W NORTHVIEW AVE</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>147-24-064</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(202) 110-8357</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>(s): Dorian Reyes, An Unmarried</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593780.pdf</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593780.pdf</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593780.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260593781</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>(s): Alonso Lopez, An Unmarried Man</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>306,176.00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>9927 W WHYMAN AVE</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Tolleson</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>101-15-683</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(200) 767-1008</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>(s): Alonso Lopez, An Unmarried</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593781.pdf</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593781.pdf</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593781.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260593782</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Maribel Howard, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>700,000.00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>303-90-222</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(202) 605-9378</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Maribel Howard, an unmarried</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593782.pdf</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593782.pdf</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593782.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260593890</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>for the</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>120,000.00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>335 E. Palm Lane</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85004</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(602) 274-9417</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>the</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593890.pdf</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593890.pdf</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee, missing_apn, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593890.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260593899</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>400,000.00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>335 E. PALM LANE</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85004</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(602) 274-9417</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260593899.pdf</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260593899.pdf</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_trustee, missing_apn, missing_auction_date</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260593899.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260594076</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>166,900.00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>11108 W CONNECTICUT AVE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Youngtown</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>85363</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/A gent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>(202) 107-2553</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>(s)</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260594076.pdf</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260594076.pdf</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260594076.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260594080</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(s): Stephanie Johnson, An Unmarried</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>245,471.00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>7825 N 49TH AVE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>147-03-282</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(202) 301-5592</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>(s): Stephanie Johnson, An</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Unmarried</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260594080.pdf</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260594080.pdf</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260594080.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH34"/>
+  <dimension ref="A1:AH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="51" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -440,14 +440,14 @@
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260591378</t>
+          <t>20260594218</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,22 +650,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Joe C. Olibarria</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>369,000.00</t>
+          <t>120,000.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>526 S NORFOLK CIR</t>
+          <t>or IDENTIFIABLE LOCATION: 7341 W YUCCA ST</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,7 +679,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -689,59 +693,67 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>140-37-152</t>
+          <t>143-07-111</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Western Progressive — Arizona, Inc.</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>(202) 011-5833</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Joe C.</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Olibarria</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591378.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260594218.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591378.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260594218.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591378.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260594218.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260591424</t>
+          <t>20260594685</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -751,7 +763,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -764,21 +776,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Regina L Castaneda, an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>358,388.00</t>
+          <t>180,775.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23799 W Magnolia Dr</t>
+          <t>23820 W HIDALGO AVE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -807,63 +815,59 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>504-28-586</t>
+          <t>504-75-369</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>/Successor Trustee, is regulated by and</t>
+          <t>Mtg Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>(202) 200-5973</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
+          <t>(201) 607-1890</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Regina L Castaneda, an unmarried</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591424.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260594685.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591424.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260594685.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_used, missing_auction_date</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591424.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260594685.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260591439</t>
+          <t>20260594967</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -873,7 +877,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -890,13 +894,13 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>263,145.00</t>
+          <t>250,635.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17227 N 16TH DR, UNIT 12</t>
+          <t>2533 West Hazelwood Street Unit 3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -911,7 +915,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85023</t>
+          <t>85017</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -925,7 +929,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>208-08-504</t>
+          <t>154-12-108</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -952,12 +956,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591439.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260594967.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591439.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260594967.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -970,14 +974,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591439.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260594967.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260591906</t>
+          <t>20260595025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -987,7 +991,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1002,24 +1006,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Richard Montemayor Jr, a single man</t>
+          <t>Sbl Real Estate, Llc, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>226,816.00</t>
+          <t>5,295,795.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>680 North Delaware Street</t>
+          <t>The Deed of Trust and/or Beneficiary provide the following purported property location: 71&amp; &amp; Beloat Road</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1029,7 +1033,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1041,32 +1045,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>302-66-100</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>First American Title Insurance Company, 9255 Towne</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(200) 775-0839</t>
+          <t>(202) 403-1117</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Richard Montemayor Jr, a single</t>
+          <t>Sbl Real Estate, Llc, an Arizona limited liability</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>company</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -1074,32 +1078,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591906.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595025.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591906.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595025.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_used, missing_trustee</t>
+          <t>ocr_used, missing_apn</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591906.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595025.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260591920</t>
+          <t>20260595169</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1109,7 +1113,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1126,14 +1130,30 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>235,873.00</t>
+          <t>2,700,000.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1515 E BUCKEYE RD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85012</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1145,23 +1165,19 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>304-23-450</t>
+          <t>115-41</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 501-7724</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1172,32 +1188,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591920.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595169.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591920.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595169.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_address</t>
+          <t>ocr_used, missing_owner, missing_trustee</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591920.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595169.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260591994</t>
+          <t>20260595490</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1207,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1220,22 +1236,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Domingo Ortiz Orozco and Leonor Cruz Lopez, husband and wife</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>305,000.00</t>
+          <t>254,308.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>or identifiable location: 1610 W VILLAGE WAY</t>
+          <t>11039 W Salem Dr</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Sun City</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1245,7 +1265,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85282</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1257,57 +1277,73 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>142-70-190</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(200) 763-3201</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Domingo Ortiz</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Orozco</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Leonor Cruz Lopez, husband and</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260591994.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595490.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260591994.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595490.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner, missing_apn</t>
+          <t>ocr_used, missing_trustee</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260591994.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595490.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260592053</t>
+          <t>20260595505</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1317,7 +1353,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1334,18 +1370,18 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>473,000.00</t>
+          <t>1,237,500.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>or identifiable location: | 4015 W SOFT WIND DR</t>
+          <t>or identifiable location: 1224 EAST DUNLAP AVENUE</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1355,7 +1391,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85310</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1369,26 +1405,30 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>205-11-090</t>
+          <t>159-34-145</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(202) 303-9550</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1396,12 +1436,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592053.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595505.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592053.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595505.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1414,14 +1454,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592053.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595505.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260592191</t>
+          <t>20260595531</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1431,7 +1471,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1444,22 +1484,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>in favor of Fnancial Freedom Senior</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>350,834.00</t>
+          <t>335,174.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>or identifiable location: 10628 W ANGELS LN</t>
+          <t>14802 WEST YOSEMITE DRIVE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Peoria</t>
+          <t>Sun West</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1469,7 +1513,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85383</t>
+          <t>85375</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1483,59 +1527,67 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>200-10-252</t>
+          <t>232-17-840</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File An</t>
+          <t>Date: October 12, 2026 Clear Recon Corp</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>in favor of Fnancial Freedom</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592191.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595531.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592191.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595531.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592191.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595531.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260592314</t>
+          <t>20260595535</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1545,7 +1597,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1558,22 +1610,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Natascha S Henline</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>372,362.00</t>
+          <t>276,000.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>or identifiable location: 24519 W ILLINI STREET</t>
+          <t>3707 East Southern Avenue</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1583,7 +1639,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85206</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1597,59 +1653,67 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>504-24-570</t>
+          <t>219-18-045</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>(888) 403-4115</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Natascha S</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Henline</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592314.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595535.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592314.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595535.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592314.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595535.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260592447</t>
+          <t>20260595611</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1659,7 +1723,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1676,18 +1740,18 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>200,000.00</t>
+          <t>378,026.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>or identifiable location: 5396 N 82nd Ave</t>
+          <t>or identifiable location: 5015 W VERNON AVE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1697,7 +1761,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85303</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1711,28 +1775,28 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>102-09-250</t>
+          <t>103-19-422</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Sale Or If You Have An Objection To The Trustee Sale, You</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(226) 081-3118</t>
+          <t>(202) 204-4369</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1742,12 +1806,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592447.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595611.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592447.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595611.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1760,14 +1824,14 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592447.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595611.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260592456</t>
+          <t>20260595626</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1777,7 +1841,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1794,18 +1858,18 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35,000.00</t>
+          <t>186,558.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>or identifiable 13135 W CARIBBEAN LN</t>
+          <t>or identifiable location: 1130 E BUTLER DR</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1815,7 +1879,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1829,28 +1893,28 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>501-94-099</t>
+          <t>160-05-184</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>may require entity or trust bidders at this trustee's sale to provide</t>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>(226) 092-5136</t>
+          <t>(202) 303-9607</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2006-07-17</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -1860,12 +1924,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592456.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595626.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592456.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595626.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1878,14 +1942,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592456.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595626.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260592710</t>
+          <t>20260595971</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1895,7 +1959,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1908,26 +1972,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Erik Alejandro Maldonado And Vanessa Elizabeth</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>940,006.00</t>
+          <t>470,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 3816 W WHITE FEATHER LN</t>
+          <t>or identifiable location: 3076 N 309TH DR</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1937,7 +1997,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85083</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1951,67 +2011,63 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>205-05-048</t>
+          <t>504-77-377</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>appointed here qualifies as a Trustee of the trust deed</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 205-7003</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Erik Alejandro Maldonado And Vanessa</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Elizabeth</t>
-        </is>
-      </c>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592710.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595971.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592710.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595971.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592710.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595971.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260592771</t>
+          <t>20260595972</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2021,7 +2077,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2034,26 +2090,22 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Jose O. Reyes</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>525,000.00</t>
+          <t>385,600.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>or IDENTIFIABLE LOCATION: 366 W ELGIN STREET</t>
+          <t>or identifiable location: 3022 N 17TH AVE</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2063,7 +2115,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>85015</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2077,67 +2129,63 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>303-19-0401</t>
+          <t>110-33-025</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Sale Or If You Have An Objection To The Trustee Sale, You Must File</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(202) 202-2572</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Jose O.</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Reyes</t>
-        </is>
-      </c>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2022-03-08</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592771.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260595972.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592771.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260595972.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_used</t>
+          <t>ocr_used, missing_owner</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592771.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260595972.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260592785</t>
+          <t>20260596112</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2147,7 +2195,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2160,22 +2208,26 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(s): Cliofas R. Almanza and Maria Guadalupe Camarena</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>305,620.00</t>
+          <t>181,804.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19613 W MORNING GLORY ST</t>
+          <t>4807 W WINDSOR AVENUE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2185,7 +2237,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2199,59 +2251,75 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>502-35-748</t>
+          <t>103-51-007</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(202) 204-0942</t>
+          <t>(202) 000-3257</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>(s): Cliofas R.</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Almanza</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Maria Guadalupe</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Camarena</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260592785.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260596112.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260592785.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260596112.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_used, missing_owner</t>
+          <t>ocr_used</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260592785.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260596112.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260593126</t>
+          <t>20260596113</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2261,7 +2329,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2274,18 +2342,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(s): Bruce A. Peterson, a married man as his sole and</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>238,843.00</t>
+          <t>407,000.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>226 N 96TH ST</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85207</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -2297,59 +2385,67 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>200-82-462</t>
+          <t>220-26</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Mtc Financial Inc. dba Trustee Corps</t>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>(202) 301-8541</t>
+          <t>(202) 209-1067</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>(s): Bruce A. Peterson,